--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="中证500" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,9 +23,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="+0%"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="+0.00%;-0.00%;0.00%"/>
   </numFmts>
@@ -113,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,32 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -176,22 +197,22 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,6 +245,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1008,8 +1042,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="16" t="n"/>
+      <c r="A5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A5,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1030,7 +1070,9 @@
         <f>IFERROR(IF(M5="增量阶段",H5,SUMPRODUCT(MAX(C5,0),1)+SUMPRODUCT(MAX(D5,0),1)+SUMPRODUCT(MAX(E5,0),1)+SUMPRODUCT(MAX(F5,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H5" s="17" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="7">
         <f>IFERROR(MAX(-C5,0)+MAX(-D5,0)+MAX(-E5,0)+MAX(-F5,0),"")</f>
         <v/>
@@ -1054,7 +1096,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n"/>
-      <c r="B6" s="16" t="n"/>
+      <c r="B6" s="32" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A6,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1099,7 +1141,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="32" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A7,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1144,7 +1186,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
-      <c r="B8" s="16" t="n"/>
+      <c r="B8" s="32" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A8,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1189,7 +1231,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n"/>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="32" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A9,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1234,7 +1276,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n"/>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="32" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A10,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1279,7 +1321,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="16" t="n"/>
+      <c r="B11" s="32" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A11,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1324,7 +1366,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="32" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A12,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1369,7 +1411,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="32" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A13,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1414,7 +1456,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="32" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A14,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1459,7 +1501,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n"/>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="32" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A15,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1504,7 +1546,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="32" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A16,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1549,7 +1591,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n"/>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="32" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A17,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1594,7 +1636,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n"/>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="32" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A18,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1639,7 +1681,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n"/>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="32" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A19,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1684,7 +1726,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
-      <c r="B20" s="16" t="n"/>
+      <c r="B20" s="32" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A20,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1729,7 +1771,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n"/>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="32" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A21,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1774,7 +1816,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="32" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A22,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1819,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n"/>
-      <c r="B23" s="16" t="n"/>
+      <c r="B23" s="32" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A23,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1864,7 +1906,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="32" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A24,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1909,7 +1951,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n"/>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="32" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A25,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1954,7 +1996,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
-      <c r="B26" s="16" t="n"/>
+      <c r="B26" s="32" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A26,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1999,7 +2041,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n"/>
-      <c r="B27" s="16" t="n"/>
+      <c r="B27" s="32" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A27,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2044,7 +2086,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n"/>
-      <c r="B28" s="16" t="n"/>
+      <c r="B28" s="32" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A28,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2089,7 +2131,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="32" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A29,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2134,7 +2176,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
-      <c r="B30" s="16" t="n"/>
+      <c r="B30" s="32" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A30,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2179,7 +2221,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n"/>
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="32" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A31,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2224,7 +2266,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n"/>
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="32" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A32,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2269,7 +2311,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n"/>
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="32" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A33,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2314,7 +2356,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n"/>
-      <c r="B34" s="16" t="n"/>
+      <c r="B34" s="32" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A34,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2359,7 +2401,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n"/>
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="32" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A35,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2404,7 +2446,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n"/>
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="32" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A36,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2449,7 +2491,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n"/>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="32" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A37,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2494,7 +2536,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n"/>
-      <c r="B38" s="16" t="n"/>
+      <c r="B38" s="32" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A38,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2539,7 +2581,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n"/>
-      <c r="B39" s="16" t="n"/>
+      <c r="B39" s="32" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A39,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2584,7 +2626,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="32" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A40,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2629,7 +2671,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n"/>
-      <c r="B41" s="16" t="n"/>
+      <c r="B41" s="32" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A41,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2674,7 +2716,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n"/>
-      <c r="B42" s="16" t="n"/>
+      <c r="B42" s="32" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A42,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2719,7 +2761,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n"/>
-      <c r="B43" s="16" t="n"/>
+      <c r="B43" s="32" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A43,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2764,7 +2806,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n"/>
-      <c r="B44" s="16" t="n"/>
+      <c r="B44" s="32" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A44,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2809,7 +2851,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n"/>
-      <c r="B45" s="16" t="n"/>
+      <c r="B45" s="32" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A45,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2854,7 +2896,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n"/>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="32" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A46,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2899,7 +2941,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n"/>
-      <c r="B47" s="16" t="n"/>
+      <c r="B47" s="32" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A47,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2944,7 +2986,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n"/>
-      <c r="B48" s="16" t="n"/>
+      <c r="B48" s="32" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A48,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2989,7 +3031,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n"/>
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="32" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A49,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3034,7 +3076,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n"/>
-      <c r="B50" s="16" t="n"/>
+      <c r="B50" s="32" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A50,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3079,7 +3121,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n"/>
-      <c r="B51" s="16" t="n"/>
+      <c r="B51" s="32" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A51,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3124,7 +3166,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n"/>
-      <c r="B52" s="16" t="n"/>
+      <c r="B52" s="32" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A52,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3169,7 +3211,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n"/>
-      <c r="B53" s="16" t="n"/>
+      <c r="B53" s="32" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A53,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3214,7 +3256,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n"/>
-      <c r="B54" s="16" t="n"/>
+      <c r="B54" s="32" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A54,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3259,7 +3301,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n"/>
-      <c r="B55" s="16" t="n"/>
+      <c r="B55" s="32" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A55,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3304,7 +3346,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n"/>
-      <c r="B56" s="16" t="n"/>
+      <c r="B56" s="32" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A56,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3349,7 +3391,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n"/>
-      <c r="B57" s="16" t="n"/>
+      <c r="B57" s="32" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A57,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3394,7 +3436,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n"/>
-      <c r="B58" s="16" t="n"/>
+      <c r="B58" s="32" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A58,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3439,7 +3481,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n"/>
-      <c r="B59" s="16" t="n"/>
+      <c r="B59" s="32" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A59,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3484,7 +3526,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n"/>
-      <c r="B60" s="16" t="n"/>
+      <c r="B60" s="32" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A60,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3529,7 +3571,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n"/>
-      <c r="B61" s="16" t="n"/>
+      <c r="B61" s="32" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A61,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3574,7 +3616,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n"/>
-      <c r="B62" s="16" t="n"/>
+      <c r="B62" s="32" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A62,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3619,7 +3661,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n"/>
-      <c r="B63" s="16" t="n"/>
+      <c r="B63" s="32" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A63,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3664,7 +3706,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n"/>
-      <c r="B64" s="16" t="n"/>
+      <c r="B64" s="32" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A64,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3709,7 +3751,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n"/>
-      <c r="B65" s="16" t="n"/>
+      <c r="B65" s="32" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A65,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3754,7 +3796,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n"/>
-      <c r="B66" s="16" t="n"/>
+      <c r="B66" s="32" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A66,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3799,7 +3841,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n"/>
-      <c r="B67" s="16" t="n"/>
+      <c r="B67" s="32" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A67,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3844,7 +3886,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n"/>
-      <c r="B68" s="16" t="n"/>
+      <c r="B68" s="32" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A68,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3889,7 +3931,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n"/>
-      <c r="B69" s="16" t="n"/>
+      <c r="B69" s="32" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A69,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3934,7 +3976,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n"/>
-      <c r="B70" s="16" t="n"/>
+      <c r="B70" s="32" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A70,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3979,7 +4021,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n"/>
-      <c r="B71" s="16" t="n"/>
+      <c r="B71" s="32" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A71,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4024,7 +4066,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n"/>
-      <c r="B72" s="16" t="n"/>
+      <c r="B72" s="32" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A72,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4069,7 +4111,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n"/>
-      <c r="B73" s="16" t="n"/>
+      <c r="B73" s="32" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A73,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4114,7 +4156,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n"/>
-      <c r="B74" s="16" t="n"/>
+      <c r="B74" s="32" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A74,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4159,7 +4201,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n"/>
-      <c r="B75" s="16" t="n"/>
+      <c r="B75" s="32" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A75,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4204,7 +4246,7 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n"/>
-      <c r="B76" s="16" t="n"/>
+      <c r="B76" s="32" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A76,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4249,7 +4291,7 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n"/>
-      <c r="B77" s="16" t="n"/>
+      <c r="B77" s="32" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A77,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4294,7 +4336,7 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n"/>
-      <c r="B78" s="16" t="n"/>
+      <c r="B78" s="32" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A78,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4339,7 +4381,7 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n"/>
-      <c r="B79" s="16" t="n"/>
+      <c r="B79" s="32" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A79,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4384,7 +4426,7 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n"/>
-      <c r="B80" s="16" t="n"/>
+      <c r="B80" s="32" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A80,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4429,7 +4471,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n"/>
-      <c r="B81" s="16" t="n"/>
+      <c r="B81" s="32" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A81,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4474,7 +4516,7 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n"/>
-      <c r="B82" s="16" t="n"/>
+      <c r="B82" s="32" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A82,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4519,7 +4561,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n"/>
-      <c r="B83" s="16" t="n"/>
+      <c r="B83" s="32" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A83,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4564,7 +4606,7 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n"/>
-      <c r="B84" s="16" t="n"/>
+      <c r="B84" s="32" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A84,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4609,7 +4651,7 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n"/>
-      <c r="B85" s="16" t="n"/>
+      <c r="B85" s="32" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A85,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4654,7 +4696,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n"/>
-      <c r="B86" s="16" t="n"/>
+      <c r="B86" s="32" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A86,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4699,7 +4741,7 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n"/>
-      <c r="B87" s="16" t="n"/>
+      <c r="B87" s="32" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A87,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4744,7 +4786,7 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n"/>
-      <c r="B88" s="16" t="n"/>
+      <c r="B88" s="32" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A88,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4789,7 +4831,7 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n"/>
-      <c r="B89" s="16" t="n"/>
+      <c r="B89" s="32" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A89,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4834,7 +4876,7 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n"/>
-      <c r="B90" s="16" t="n"/>
+      <c r="B90" s="32" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A90,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4879,7 +4921,7 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n"/>
-      <c r="B91" s="16" t="n"/>
+      <c r="B91" s="32" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A91,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4924,7 +4966,7 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n"/>
-      <c r="B92" s="16" t="n"/>
+      <c r="B92" s="32" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A92,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4969,7 +5011,7 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n"/>
-      <c r="B93" s="16" t="n"/>
+      <c r="B93" s="32" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A93,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5014,7 +5056,7 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n"/>
-      <c r="B94" s="16" t="n"/>
+      <c r="B94" s="32" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A94,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5059,7 +5101,7 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n"/>
-      <c r="B95" s="16" t="n"/>
+      <c r="B95" s="32" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A95,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5104,7 +5146,7 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n"/>
-      <c r="B96" s="16" t="n"/>
+      <c r="B96" s="32" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A96,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5149,7 +5191,7 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n"/>
-      <c r="B97" s="16" t="n"/>
+      <c r="B97" s="32" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A97,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5194,7 +5236,7 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n"/>
-      <c r="B98" s="16" t="n"/>
+      <c r="B98" s="32" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A98,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5239,7 +5281,7 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n"/>
-      <c r="B99" s="16" t="n"/>
+      <c r="B99" s="32" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A99,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5284,7 +5326,7 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n"/>
-      <c r="B100" s="16" t="n"/>
+      <c r="B100" s="32" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A100,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5329,7 +5371,7 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n"/>
-      <c r="B101" s="16" t="n"/>
+      <c r="B101" s="32" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A101,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5374,7 +5416,7 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n"/>
-      <c r="B102" s="16" t="n"/>
+      <c r="B102" s="32" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A102,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5419,7 +5461,7 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n"/>
-      <c r="B103" s="16" t="n"/>
+      <c r="B103" s="32" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A103,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5464,7 +5506,7 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n"/>
-      <c r="B104" s="16" t="n"/>
+      <c r="B104" s="32" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A104,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5587,7 +5629,7 @@
       <c r="C5" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="33" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5605,7 +5647,7 @@
       <c r="C6" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="33" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5623,7 +5665,7 @@
       <c r="C7" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="33" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5641,7 +5683,7 @@
       <c r="C8" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="33" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -5656,7 +5698,7 @@
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="34">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
@@ -5749,7 +5791,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="35" t="n">
         <v>0.15</v>
       </c>
       <c r="D15" s="22" t="n">
@@ -5768,7 +5810,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="35" t="n">
         <v>0.22</v>
       </c>
       <c r="D16" s="22" t="n">
@@ -5787,7 +5829,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="35" t="n">
         <v>0.28</v>
       </c>
       <c r="D17" s="22" t="n">
@@ -5806,7 +5848,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="35" t="n">
         <v>0.4</v>
       </c>
       <c r="D18" s="22" t="n">
@@ -5924,6 +5966,7 @@
           <t>达到后切换为增量阶段，买卖均走储备金池</t>
         </is>
       </c>
+      <c r="E26" s="36" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5940,6 +5983,7 @@
           <t>每期向储备金池注入的新增资金</t>
         </is>
       </c>
+      <c r="E27" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6113,19 +6157,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$5*B5,"")</f>
         <v/>
       </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
+      <c r="D5" s="26" t="n">
+        <v>4.774</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>4.3435</v>
+      </c>
       <c r="F5" s="27">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="n"/>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -6142,8 +6198,12 @@
         <f>IFERROR(IF(F5&gt;=参数配置!$C$18,-(H5),IF(F5&gt;=参数配置!$C$17,-((H5-C5)*参数配置!$D$17),IF(F5&gt;=参数配置!$C$16,-((H5-C5)*参数配置!$D$16),IF(F5&gt;=参数配置!$C$15,-((H5-C5)*参数配置!$D$15),IF(F5&lt;=参数配置!$C$23,I5+参数配置!$C$5*参数配置!$D$23,IF(F5&lt;=参数配置!$C$22,I5+参数配置!$C$5*参数配置!$D$22,IF(F5&lt;=参数配置!$C$21,I5+参数配置!$C$5*参数配置!$D$21,I5))))))),"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="26" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>1432.2</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <v>300</v>
+      </c>
       <c r="N5" s="30">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -6159,7 +6219,7 @@
       <c r="Q5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="32" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$5*B6,"")</f>
@@ -6205,7 +6265,7 @@
       <c r="Q6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="32" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$5*B7,"")</f>
@@ -6251,7 +6311,7 @@
       <c r="Q7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="32" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$5*B8,"")</f>
@@ -6297,7 +6357,7 @@
       <c r="Q8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="32" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$5*B9,"")</f>
@@ -6343,7 +6403,7 @@
       <c r="Q9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="32" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$5*B10,"")</f>
@@ -6389,7 +6449,7 @@
       <c r="Q10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$5*B11,"")</f>
@@ -6435,7 +6495,7 @@
       <c r="Q11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="32" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$5*B12,"")</f>
@@ -6481,7 +6541,7 @@
       <c r="Q12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="32" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$5*B13,"")</f>
@@ -6527,7 +6587,7 @@
       <c r="Q13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="32" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$5*B14,"")</f>
@@ -6573,7 +6633,7 @@
       <c r="Q14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$5*B15,"")</f>
@@ -6619,7 +6679,7 @@
       <c r="Q15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="32" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$5*B16,"")</f>
@@ -6665,7 +6725,7 @@
       <c r="Q16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="32" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$5*B17,"")</f>
@@ -6711,7 +6771,7 @@
       <c r="Q17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$5*B18,"")</f>
@@ -6757,7 +6817,7 @@
       <c r="Q18" s="31" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="32" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$5*B19,"")</f>
@@ -6803,7 +6863,7 @@
       <c r="Q19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="32" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$5*B20,"")</f>
@@ -6849,7 +6909,7 @@
       <c r="Q20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="32" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$5*B21,"")</f>
@@ -6895,7 +6955,7 @@
       <c r="Q21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="32" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$5*B22,"")</f>
@@ -6941,7 +7001,7 @@
       <c r="Q22" s="31" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="32" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$5*B23,"")</f>
@@ -6987,7 +7047,7 @@
       <c r="Q23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="32" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$5*B24,"")</f>
@@ -7033,7 +7093,7 @@
       <c r="Q24" s="31" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="32" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$5*B25,"")</f>
@@ -7079,7 +7139,7 @@
       <c r="Q25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="32" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$5*B26,"")</f>
@@ -7125,7 +7185,7 @@
       <c r="Q26" s="31" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="32" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$5*B27,"")</f>
@@ -7171,7 +7231,7 @@
       <c r="Q27" s="31" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="32" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$5*B28,"")</f>
@@ -7217,7 +7277,7 @@
       <c r="Q28" s="31" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="32" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$5*B29,"")</f>
@@ -7263,7 +7323,7 @@
       <c r="Q29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="32" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$5*B30,"")</f>
@@ -7309,7 +7369,7 @@
       <c r="Q30" s="31" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="32" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$5*B31,"")</f>
@@ -7355,7 +7415,7 @@
       <c r="Q31" s="31" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="32" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$5*B32,"")</f>
@@ -7401,7 +7461,7 @@
       <c r="Q32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="32" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$5*B33,"")</f>
@@ -7447,7 +7507,7 @@
       <c r="Q33" s="31" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="32" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$5*B34,"")</f>
@@ -7493,7 +7553,7 @@
       <c r="Q34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="32" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$5*B35,"")</f>
@@ -7539,7 +7599,7 @@
       <c r="Q35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="32" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$5*B36,"")</f>
@@ -7585,7 +7645,7 @@
       <c r="Q36" s="31" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="32" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$5*B37,"")</f>
@@ -7631,7 +7691,7 @@
       <c r="Q37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="32" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$5*B38,"")</f>
@@ -7677,7 +7737,7 @@
       <c r="Q38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="32" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$5*B39,"")</f>
@@ -7723,7 +7783,7 @@
       <c r="Q39" s="31" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="32" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$5*B40,"")</f>
@@ -7769,7 +7829,7 @@
       <c r="Q40" s="31" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="32" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$5*B41,"")</f>
@@ -7815,7 +7875,7 @@
       <c r="Q41" s="31" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="32" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$5*B42,"")</f>
@@ -7861,7 +7921,7 @@
       <c r="Q42" s="31" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="32" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$5*B43,"")</f>
@@ -7907,7 +7967,7 @@
       <c r="Q43" s="31" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="32" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$5*B44,"")</f>
@@ -7953,7 +8013,7 @@
       <c r="Q44" s="31" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="32" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$5*B45,"")</f>
@@ -7999,7 +8059,7 @@
       <c r="Q45" s="31" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="32" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$5*B46,"")</f>
@@ -8045,7 +8105,7 @@
       <c r="Q46" s="31" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="32" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$5*B47,"")</f>
@@ -8091,7 +8151,7 @@
       <c r="Q47" s="31" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="32" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$5*B48,"")</f>
@@ -8137,7 +8197,7 @@
       <c r="Q48" s="31" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="32" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$5*B49,"")</f>
@@ -8183,7 +8243,7 @@
       <c r="Q49" s="31" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="32" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$5*B50,"")</f>
@@ -8229,7 +8289,7 @@
       <c r="Q50" s="31" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="32" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$5*B51,"")</f>
@@ -8275,7 +8335,7 @@
       <c r="Q51" s="31" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="32" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$5*B52,"")</f>
@@ -8321,7 +8381,7 @@
       <c r="Q52" s="31" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="32" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$5*B53,"")</f>
@@ -8367,7 +8427,7 @@
       <c r="Q53" s="31" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="32" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$5*B54,"")</f>
@@ -8413,7 +8473,7 @@
       <c r="Q54" s="31" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="32" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$5*B55,"")</f>
@@ -8459,7 +8519,7 @@
       <c r="Q55" s="31" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="32" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$5*B56,"")</f>
@@ -8505,7 +8565,7 @@
       <c r="Q56" s="31" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="32" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$5*B57,"")</f>
@@ -8551,7 +8611,7 @@
       <c r="Q57" s="31" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="32" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$5*B58,"")</f>
@@ -8597,7 +8657,7 @@
       <c r="Q58" s="31" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="32" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$5*B59,"")</f>
@@ -8643,7 +8703,7 @@
       <c r="Q59" s="31" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="32" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$5*B60,"")</f>
@@ -8689,7 +8749,7 @@
       <c r="Q60" s="31" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="32" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$5*B61,"")</f>
@@ -8735,7 +8795,7 @@
       <c r="Q61" s="31" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="32" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$5*B62,"")</f>
@@ -8781,7 +8841,7 @@
       <c r="Q62" s="31" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="32" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$5*B63,"")</f>
@@ -8827,7 +8887,7 @@
       <c r="Q63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="32" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$5*B64,"")</f>
@@ -8873,7 +8933,7 @@
       <c r="Q64" s="31" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="32" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$5*B65,"")</f>
@@ -8919,7 +8979,7 @@
       <c r="Q65" s="31" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="32" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$5*B66,"")</f>
@@ -8965,7 +9025,7 @@
       <c r="Q66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="32" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$5*B67,"")</f>
@@ -9011,7 +9071,7 @@
       <c r="Q67" s="31" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="32" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$5*B68,"")</f>
@@ -9057,7 +9117,7 @@
       <c r="Q68" s="31" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="32" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$5*B69,"")</f>
@@ -9103,7 +9163,7 @@
       <c r="Q69" s="31" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="32" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$5*B70,"")</f>
@@ -9149,7 +9209,7 @@
       <c r="Q70" s="31" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="32" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$5*B71,"")</f>
@@ -9195,7 +9255,7 @@
       <c r="Q71" s="31" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="32" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$5*B72,"")</f>
@@ -9241,7 +9301,7 @@
       <c r="Q72" s="31" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="32" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$5*B73,"")</f>
@@ -9287,7 +9347,7 @@
       <c r="Q73" s="31" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="32" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$5*B74,"")</f>
@@ -9333,7 +9393,7 @@
       <c r="Q74" s="31" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="32" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$5*B75,"")</f>
@@ -9379,7 +9439,7 @@
       <c r="Q75" s="31" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="32" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$5*B76,"")</f>
@@ -9425,7 +9485,7 @@
       <c r="Q76" s="31" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="32" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$5*B77,"")</f>
@@ -9471,7 +9531,7 @@
       <c r="Q77" s="31" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="32" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$5*B78,"")</f>
@@ -9517,7 +9577,7 @@
       <c r="Q78" s="31" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="32" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$5*B79,"")</f>
@@ -9563,7 +9623,7 @@
       <c r="Q79" s="31" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="32" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$5*B80,"")</f>
@@ -9609,7 +9669,7 @@
       <c r="Q80" s="31" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="32" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$5*B81,"")</f>
@@ -9655,7 +9715,7 @@
       <c r="Q81" s="31" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="32" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$5*B82,"")</f>
@@ -9701,7 +9761,7 @@
       <c r="Q82" s="31" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="32" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$5*B83,"")</f>
@@ -9747,7 +9807,7 @@
       <c r="Q83" s="31" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="32" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$5*B84,"")</f>
@@ -9793,7 +9853,7 @@
       <c r="Q84" s="31" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="32" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$5*B85,"")</f>
@@ -9839,7 +9899,7 @@
       <c r="Q85" s="31" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="32" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$5*B86,"")</f>
@@ -9885,7 +9945,7 @@
       <c r="Q86" s="31" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="32" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$5*B87,"")</f>
@@ -9931,7 +9991,7 @@
       <c r="Q87" s="31" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="32" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$5*B88,"")</f>
@@ -9977,7 +10037,7 @@
       <c r="Q88" s="31" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="32" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$5*B89,"")</f>
@@ -10023,7 +10083,7 @@
       <c r="Q89" s="31" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="32" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$5*B90,"")</f>
@@ -10069,7 +10129,7 @@
       <c r="Q90" s="31" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="32" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$5*B91,"")</f>
@@ -10115,7 +10175,7 @@
       <c r="Q91" s="31" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="32" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$5*B92,"")</f>
@@ -10161,7 +10221,7 @@
       <c r="Q92" s="31" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="32" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$5*B93,"")</f>
@@ -10207,7 +10267,7 @@
       <c r="Q93" s="31" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="32" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$5*B94,"")</f>
@@ -10253,7 +10313,7 @@
       <c r="Q94" s="31" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="32" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$5*B95,"")</f>
@@ -10299,7 +10359,7 @@
       <c r="Q95" s="31" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="32" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$5*B96,"")</f>
@@ -10345,7 +10405,7 @@
       <c r="Q96" s="31" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="32" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$5*B97,"")</f>
@@ -10391,7 +10451,7 @@
       <c r="Q97" s="31" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="32" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$5*B98,"")</f>
@@ -10437,7 +10497,7 @@
       <c r="Q98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="32" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$5*B99,"")</f>
@@ -10483,7 +10543,7 @@
       <c r="Q99" s="31" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="32" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$5*B100,"")</f>
@@ -10529,7 +10589,7 @@
       <c r="Q100" s="31" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="32" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$5*B101,"")</f>
@@ -10575,7 +10635,7 @@
       <c r="Q101" s="31" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="32" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$5*B102,"")</f>
@@ -10621,7 +10681,7 @@
       <c r="Q102" s="31" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="32" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$5*B103,"")</f>
@@ -10667,7 +10727,7 @@
       <c r="Q103" s="31" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="32" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$5*B104,"")</f>
@@ -10882,19 +10942,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$6*B5,"")</f>
         <v/>
       </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
+      <c r="D5" s="26" t="n">
+        <v>8.302</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>7.0208</v>
+      </c>
       <c r="F5" s="27">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="n"/>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -10911,8 +10983,12 @@
         <f>IFERROR(IF(F5&gt;=参数配置!$C$18,-(H5),IF(F5&gt;=参数配置!$C$17,-((H5-C5)*参数配置!$D$17),IF(F5&gt;=参数配置!$C$16,-((H5-C5)*参数配置!$D$16),IF(F5&gt;=参数配置!$C$15,-((H5-C5)*参数配置!$D$15),IF(F5&lt;=参数配置!$C$23,I5+参数配置!$C$6*参数配置!$D$23,IF(F5&lt;=参数配置!$C$22,I5+参数配置!$C$6*参数配置!$D$22,IF(F5&lt;=参数配置!$C$21,I5+参数配置!$C$6*参数配置!$D$21,I5))))))),"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="26" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>830.2</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <v>100</v>
+      </c>
       <c r="N5" s="30">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -10928,7 +11004,7 @@
       <c r="Q5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="32" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$6*B6,"")</f>
@@ -10974,7 +11050,7 @@
       <c r="Q6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="32" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$6*B7,"")</f>
@@ -11020,7 +11096,7 @@
       <c r="Q7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="32" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$6*B8,"")</f>
@@ -11066,7 +11142,7 @@
       <c r="Q8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="32" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$6*B9,"")</f>
@@ -11112,7 +11188,7 @@
       <c r="Q9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="32" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$6*B10,"")</f>
@@ -11158,7 +11234,7 @@
       <c r="Q10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$6*B11,"")</f>
@@ -11204,7 +11280,7 @@
       <c r="Q11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="32" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$6*B12,"")</f>
@@ -11250,7 +11326,7 @@
       <c r="Q12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="32" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$6*B13,"")</f>
@@ -11296,7 +11372,7 @@
       <c r="Q13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="32" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$6*B14,"")</f>
@@ -11342,7 +11418,7 @@
       <c r="Q14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$6*B15,"")</f>
@@ -11388,7 +11464,7 @@
       <c r="Q15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="32" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$6*B16,"")</f>
@@ -11434,7 +11510,7 @@
       <c r="Q16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="32" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$6*B17,"")</f>
@@ -11480,7 +11556,7 @@
       <c r="Q17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$6*B18,"")</f>
@@ -11526,7 +11602,7 @@
       <c r="Q18" s="31" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="32" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$6*B19,"")</f>
@@ -11572,7 +11648,7 @@
       <c r="Q19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="32" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$6*B20,"")</f>
@@ -11618,7 +11694,7 @@
       <c r="Q20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="32" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$6*B21,"")</f>
@@ -11664,7 +11740,7 @@
       <c r="Q21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="32" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$6*B22,"")</f>
@@ -11710,7 +11786,7 @@
       <c r="Q22" s="31" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="32" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$6*B23,"")</f>
@@ -11756,7 +11832,7 @@
       <c r="Q23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="32" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$6*B24,"")</f>
@@ -11802,7 +11878,7 @@
       <c r="Q24" s="31" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="32" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$6*B25,"")</f>
@@ -11848,7 +11924,7 @@
       <c r="Q25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="32" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$6*B26,"")</f>
@@ -11894,7 +11970,7 @@
       <c r="Q26" s="31" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="32" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$6*B27,"")</f>
@@ -11940,7 +12016,7 @@
       <c r="Q27" s="31" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="32" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$6*B28,"")</f>
@@ -11986,7 +12062,7 @@
       <c r="Q28" s="31" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="32" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$6*B29,"")</f>
@@ -12032,7 +12108,7 @@
       <c r="Q29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="32" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$6*B30,"")</f>
@@ -12078,7 +12154,7 @@
       <c r="Q30" s="31" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="32" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$6*B31,"")</f>
@@ -12124,7 +12200,7 @@
       <c r="Q31" s="31" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="32" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$6*B32,"")</f>
@@ -12170,7 +12246,7 @@
       <c r="Q32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="32" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$6*B33,"")</f>
@@ -12216,7 +12292,7 @@
       <c r="Q33" s="31" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="32" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$6*B34,"")</f>
@@ -12262,7 +12338,7 @@
       <c r="Q34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="32" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$6*B35,"")</f>
@@ -12308,7 +12384,7 @@
       <c r="Q35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="32" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$6*B36,"")</f>
@@ -12354,7 +12430,7 @@
       <c r="Q36" s="31" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="32" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$6*B37,"")</f>
@@ -12400,7 +12476,7 @@
       <c r="Q37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="32" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$6*B38,"")</f>
@@ -12446,7 +12522,7 @@
       <c r="Q38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="32" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$6*B39,"")</f>
@@ -12492,7 +12568,7 @@
       <c r="Q39" s="31" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="32" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$6*B40,"")</f>
@@ -12538,7 +12614,7 @@
       <c r="Q40" s="31" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="32" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$6*B41,"")</f>
@@ -12584,7 +12660,7 @@
       <c r="Q41" s="31" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="32" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$6*B42,"")</f>
@@ -12630,7 +12706,7 @@
       <c r="Q42" s="31" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="32" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$6*B43,"")</f>
@@ -12676,7 +12752,7 @@
       <c r="Q43" s="31" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="32" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$6*B44,"")</f>
@@ -12722,7 +12798,7 @@
       <c r="Q44" s="31" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="32" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$6*B45,"")</f>
@@ -12768,7 +12844,7 @@
       <c r="Q45" s="31" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="32" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$6*B46,"")</f>
@@ -12814,7 +12890,7 @@
       <c r="Q46" s="31" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="32" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$6*B47,"")</f>
@@ -12860,7 +12936,7 @@
       <c r="Q47" s="31" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="32" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$6*B48,"")</f>
@@ -12906,7 +12982,7 @@
       <c r="Q48" s="31" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="32" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$6*B49,"")</f>
@@ -12952,7 +13028,7 @@
       <c r="Q49" s="31" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="32" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$6*B50,"")</f>
@@ -12998,7 +13074,7 @@
       <c r="Q50" s="31" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="32" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$6*B51,"")</f>
@@ -13044,7 +13120,7 @@
       <c r="Q51" s="31" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="32" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$6*B52,"")</f>
@@ -13090,7 +13166,7 @@
       <c r="Q52" s="31" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="32" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$6*B53,"")</f>
@@ -13136,7 +13212,7 @@
       <c r="Q53" s="31" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="32" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$6*B54,"")</f>
@@ -13182,7 +13258,7 @@
       <c r="Q54" s="31" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="32" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$6*B55,"")</f>
@@ -13228,7 +13304,7 @@
       <c r="Q55" s="31" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="32" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$6*B56,"")</f>
@@ -13274,7 +13350,7 @@
       <c r="Q56" s="31" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="32" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$6*B57,"")</f>
@@ -13320,7 +13396,7 @@
       <c r="Q57" s="31" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="32" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$6*B58,"")</f>
@@ -13366,7 +13442,7 @@
       <c r="Q58" s="31" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="32" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$6*B59,"")</f>
@@ -13412,7 +13488,7 @@
       <c r="Q59" s="31" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="32" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$6*B60,"")</f>
@@ -13458,7 +13534,7 @@
       <c r="Q60" s="31" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="32" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$6*B61,"")</f>
@@ -13504,7 +13580,7 @@
       <c r="Q61" s="31" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="32" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$6*B62,"")</f>
@@ -13550,7 +13626,7 @@
       <c r="Q62" s="31" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="32" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$6*B63,"")</f>
@@ -13596,7 +13672,7 @@
       <c r="Q63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="32" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$6*B64,"")</f>
@@ -13642,7 +13718,7 @@
       <c r="Q64" s="31" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="32" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$6*B65,"")</f>
@@ -13688,7 +13764,7 @@
       <c r="Q65" s="31" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="32" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$6*B66,"")</f>
@@ -13734,7 +13810,7 @@
       <c r="Q66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="32" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$6*B67,"")</f>
@@ -13780,7 +13856,7 @@
       <c r="Q67" s="31" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="32" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$6*B68,"")</f>
@@ -13826,7 +13902,7 @@
       <c r="Q68" s="31" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="32" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$6*B69,"")</f>
@@ -13872,7 +13948,7 @@
       <c r="Q69" s="31" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="32" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$6*B70,"")</f>
@@ -13918,7 +13994,7 @@
       <c r="Q70" s="31" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="32" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$6*B71,"")</f>
@@ -13964,7 +14040,7 @@
       <c r="Q71" s="31" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="32" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$6*B72,"")</f>
@@ -14010,7 +14086,7 @@
       <c r="Q72" s="31" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="32" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$6*B73,"")</f>
@@ -14056,7 +14132,7 @@
       <c r="Q73" s="31" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="32" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$6*B74,"")</f>
@@ -14102,7 +14178,7 @@
       <c r="Q74" s="31" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="32" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$6*B75,"")</f>
@@ -14148,7 +14224,7 @@
       <c r="Q75" s="31" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="32" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$6*B76,"")</f>
@@ -14194,7 +14270,7 @@
       <c r="Q76" s="31" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="32" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$6*B77,"")</f>
@@ -14240,7 +14316,7 @@
       <c r="Q77" s="31" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="32" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$6*B78,"")</f>
@@ -14286,7 +14362,7 @@
       <c r="Q78" s="31" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="32" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$6*B79,"")</f>
@@ -14332,7 +14408,7 @@
       <c r="Q79" s="31" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="32" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$6*B80,"")</f>
@@ -14378,7 +14454,7 @@
       <c r="Q80" s="31" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="32" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$6*B81,"")</f>
@@ -14424,7 +14500,7 @@
       <c r="Q81" s="31" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="32" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$6*B82,"")</f>
@@ -14470,7 +14546,7 @@
       <c r="Q82" s="31" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="32" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$6*B83,"")</f>
@@ -14516,7 +14592,7 @@
       <c r="Q83" s="31" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="32" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$6*B84,"")</f>
@@ -14562,7 +14638,7 @@
       <c r="Q84" s="31" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="32" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$6*B85,"")</f>
@@ -14608,7 +14684,7 @@
       <c r="Q85" s="31" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="32" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$6*B86,"")</f>
@@ -14654,7 +14730,7 @@
       <c r="Q86" s="31" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="32" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$6*B87,"")</f>
@@ -14700,7 +14776,7 @@
       <c r="Q87" s="31" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="32" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$6*B88,"")</f>
@@ -14746,7 +14822,7 @@
       <c r="Q88" s="31" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="32" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$6*B89,"")</f>
@@ -14792,7 +14868,7 @@
       <c r="Q89" s="31" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="32" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$6*B90,"")</f>
@@ -14838,7 +14914,7 @@
       <c r="Q90" s="31" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="32" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$6*B91,"")</f>
@@ -14884,7 +14960,7 @@
       <c r="Q91" s="31" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="32" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$6*B92,"")</f>
@@ -14930,7 +15006,7 @@
       <c r="Q92" s="31" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="32" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$6*B93,"")</f>
@@ -14976,7 +15052,7 @@
       <c r="Q93" s="31" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="32" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$6*B94,"")</f>
@@ -15022,7 +15098,7 @@
       <c r="Q94" s="31" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="32" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$6*B95,"")</f>
@@ -15068,7 +15144,7 @@
       <c r="Q95" s="31" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="32" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$6*B96,"")</f>
@@ -15114,7 +15190,7 @@
       <c r="Q96" s="31" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="32" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$6*B97,"")</f>
@@ -15160,7 +15236,7 @@
       <c r="Q97" s="31" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="32" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$6*B98,"")</f>
@@ -15206,7 +15282,7 @@
       <c r="Q98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="32" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$6*B99,"")</f>
@@ -15252,7 +15328,7 @@
       <c r="Q99" s="31" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="32" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$6*B100,"")</f>
@@ -15298,7 +15374,7 @@
       <c r="Q100" s="31" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="32" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$6*B101,"")</f>
@@ -15344,7 +15420,7 @@
       <c r="Q101" s="31" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="32" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$6*B102,"")</f>
@@ -15390,7 +15466,7 @@
       <c r="Q102" s="31" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="32" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$6*B103,"")</f>
@@ -15436,7 +15512,7 @@
       <c r="Q103" s="31" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="32" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$6*B104,"")</f>
@@ -15651,19 +15727,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$7*B5,"")</f>
         <v/>
       </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
+      <c r="D5" s="26" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>1.5383</v>
+      </c>
       <c r="F5" s="27">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="n"/>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -15680,8 +15768,12 @@
         <f>IFERROR(IF(F5&gt;=参数配置!$C$18,-(H5),IF(F5&gt;=参数配置!$C$17,-((H5-C5)*参数配置!$D$17),IF(F5&gt;=参数配置!$C$16,-((H5-C5)*参数配置!$D$16),IF(F5&gt;=参数配置!$C$15,-((H5-C5)*参数配置!$D$15),IF(F5&lt;=参数配置!$C$23,I5+参数配置!$C$7*参数配置!$D$23,IF(F5&lt;=参数配置!$C$22,I5+参数配置!$C$7*参数配置!$D$22,IF(F5&lt;=参数配置!$C$21,I5+参数配置!$C$7*参数配置!$D$21,I5))))))),"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="26" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <v>300</v>
+      </c>
       <c r="N5" s="30">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -15697,7 +15789,7 @@
       <c r="Q5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="32" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$7*B6,"")</f>
@@ -15743,7 +15835,7 @@
       <c r="Q6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="32" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$7*B7,"")</f>
@@ -15789,7 +15881,7 @@
       <c r="Q7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="32" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$7*B8,"")</f>
@@ -15835,7 +15927,7 @@
       <c r="Q8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="32" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$7*B9,"")</f>
@@ -15881,7 +15973,7 @@
       <c r="Q9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="32" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$7*B10,"")</f>
@@ -15927,7 +16019,7 @@
       <c r="Q10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$7*B11,"")</f>
@@ -15973,7 +16065,7 @@
       <c r="Q11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="32" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$7*B12,"")</f>
@@ -16019,7 +16111,7 @@
       <c r="Q12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="32" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$7*B13,"")</f>
@@ -16065,7 +16157,7 @@
       <c r="Q13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="32" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$7*B14,"")</f>
@@ -16111,7 +16203,7 @@
       <c r="Q14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$7*B15,"")</f>
@@ -16157,7 +16249,7 @@
       <c r="Q15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="32" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$7*B16,"")</f>
@@ -16203,7 +16295,7 @@
       <c r="Q16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="32" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$7*B17,"")</f>
@@ -16249,7 +16341,7 @@
       <c r="Q17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$7*B18,"")</f>
@@ -16295,7 +16387,7 @@
       <c r="Q18" s="31" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="32" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$7*B19,"")</f>
@@ -16341,7 +16433,7 @@
       <c r="Q19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="32" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$7*B20,"")</f>
@@ -16387,7 +16479,7 @@
       <c r="Q20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="32" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$7*B21,"")</f>
@@ -16433,7 +16525,7 @@
       <c r="Q21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="32" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$7*B22,"")</f>
@@ -16479,7 +16571,7 @@
       <c r="Q22" s="31" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="32" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$7*B23,"")</f>
@@ -16525,7 +16617,7 @@
       <c r="Q23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="32" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$7*B24,"")</f>
@@ -16571,7 +16663,7 @@
       <c r="Q24" s="31" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="32" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$7*B25,"")</f>
@@ -16617,7 +16709,7 @@
       <c r="Q25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="32" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$7*B26,"")</f>
@@ -16663,7 +16755,7 @@
       <c r="Q26" s="31" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="32" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$7*B27,"")</f>
@@ -16709,7 +16801,7 @@
       <c r="Q27" s="31" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="32" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$7*B28,"")</f>
@@ -16755,7 +16847,7 @@
       <c r="Q28" s="31" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="32" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$7*B29,"")</f>
@@ -16801,7 +16893,7 @@
       <c r="Q29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="32" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$7*B30,"")</f>
@@ -16847,7 +16939,7 @@
       <c r="Q30" s="31" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="32" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$7*B31,"")</f>
@@ -16893,7 +16985,7 @@
       <c r="Q31" s="31" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="32" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$7*B32,"")</f>
@@ -16939,7 +17031,7 @@
       <c r="Q32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="32" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$7*B33,"")</f>
@@ -16985,7 +17077,7 @@
       <c r="Q33" s="31" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="32" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$7*B34,"")</f>
@@ -17031,7 +17123,7 @@
       <c r="Q34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="32" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$7*B35,"")</f>
@@ -17077,7 +17169,7 @@
       <c r="Q35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="32" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$7*B36,"")</f>
@@ -17123,7 +17215,7 @@
       <c r="Q36" s="31" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="32" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$7*B37,"")</f>
@@ -17169,7 +17261,7 @@
       <c r="Q37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="32" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$7*B38,"")</f>
@@ -17215,7 +17307,7 @@
       <c r="Q38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="32" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$7*B39,"")</f>
@@ -17261,7 +17353,7 @@
       <c r="Q39" s="31" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="32" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$7*B40,"")</f>
@@ -17307,7 +17399,7 @@
       <c r="Q40" s="31" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="32" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$7*B41,"")</f>
@@ -17353,7 +17445,7 @@
       <c r="Q41" s="31" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="32" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$7*B42,"")</f>
@@ -17399,7 +17491,7 @@
       <c r="Q42" s="31" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="32" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$7*B43,"")</f>
@@ -17445,7 +17537,7 @@
       <c r="Q43" s="31" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="32" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$7*B44,"")</f>
@@ -17491,7 +17583,7 @@
       <c r="Q44" s="31" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="32" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$7*B45,"")</f>
@@ -17537,7 +17629,7 @@
       <c r="Q45" s="31" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="32" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$7*B46,"")</f>
@@ -17583,7 +17675,7 @@
       <c r="Q46" s="31" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="32" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$7*B47,"")</f>
@@ -17629,7 +17721,7 @@
       <c r="Q47" s="31" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="32" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$7*B48,"")</f>
@@ -17675,7 +17767,7 @@
       <c r="Q48" s="31" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="32" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$7*B49,"")</f>
@@ -17721,7 +17813,7 @@
       <c r="Q49" s="31" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="32" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$7*B50,"")</f>
@@ -17767,7 +17859,7 @@
       <c r="Q50" s="31" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="32" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$7*B51,"")</f>
@@ -17813,7 +17905,7 @@
       <c r="Q51" s="31" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="32" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$7*B52,"")</f>
@@ -17859,7 +17951,7 @@
       <c r="Q52" s="31" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="32" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$7*B53,"")</f>
@@ -17905,7 +17997,7 @@
       <c r="Q53" s="31" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="32" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$7*B54,"")</f>
@@ -17951,7 +18043,7 @@
       <c r="Q54" s="31" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="32" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$7*B55,"")</f>
@@ -17997,7 +18089,7 @@
       <c r="Q55" s="31" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="32" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$7*B56,"")</f>
@@ -18043,7 +18135,7 @@
       <c r="Q56" s="31" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="32" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$7*B57,"")</f>
@@ -18089,7 +18181,7 @@
       <c r="Q57" s="31" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="32" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$7*B58,"")</f>
@@ -18135,7 +18227,7 @@
       <c r="Q58" s="31" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="32" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$7*B59,"")</f>
@@ -18181,7 +18273,7 @@
       <c r="Q59" s="31" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="32" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$7*B60,"")</f>
@@ -18227,7 +18319,7 @@
       <c r="Q60" s="31" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="32" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$7*B61,"")</f>
@@ -18273,7 +18365,7 @@
       <c r="Q61" s="31" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="32" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$7*B62,"")</f>
@@ -18319,7 +18411,7 @@
       <c r="Q62" s="31" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="32" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$7*B63,"")</f>
@@ -18365,7 +18457,7 @@
       <c r="Q63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="32" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$7*B64,"")</f>
@@ -18411,7 +18503,7 @@
       <c r="Q64" s="31" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="32" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$7*B65,"")</f>
@@ -18457,7 +18549,7 @@
       <c r="Q65" s="31" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="32" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$7*B66,"")</f>
@@ -18503,7 +18595,7 @@
       <c r="Q66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="32" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$7*B67,"")</f>
@@ -18549,7 +18641,7 @@
       <c r="Q67" s="31" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="32" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$7*B68,"")</f>
@@ -18595,7 +18687,7 @@
       <c r="Q68" s="31" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="32" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$7*B69,"")</f>
@@ -18641,7 +18733,7 @@
       <c r="Q69" s="31" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="32" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$7*B70,"")</f>
@@ -18687,7 +18779,7 @@
       <c r="Q70" s="31" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="32" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$7*B71,"")</f>
@@ -18733,7 +18825,7 @@
       <c r="Q71" s="31" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="32" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$7*B72,"")</f>
@@ -18779,7 +18871,7 @@
       <c r="Q72" s="31" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="32" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$7*B73,"")</f>
@@ -18825,7 +18917,7 @@
       <c r="Q73" s="31" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="32" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$7*B74,"")</f>
@@ -18871,7 +18963,7 @@
       <c r="Q74" s="31" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="32" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$7*B75,"")</f>
@@ -18917,7 +19009,7 @@
       <c r="Q75" s="31" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="32" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$7*B76,"")</f>
@@ -18963,7 +19055,7 @@
       <c r="Q76" s="31" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="32" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$7*B77,"")</f>
@@ -19009,7 +19101,7 @@
       <c r="Q77" s="31" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="32" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$7*B78,"")</f>
@@ -19055,7 +19147,7 @@
       <c r="Q78" s="31" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="32" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$7*B79,"")</f>
@@ -19101,7 +19193,7 @@
       <c r="Q79" s="31" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="32" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$7*B80,"")</f>
@@ -19147,7 +19239,7 @@
       <c r="Q80" s="31" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="32" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$7*B81,"")</f>
@@ -19193,7 +19285,7 @@
       <c r="Q81" s="31" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="32" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$7*B82,"")</f>
@@ -19239,7 +19331,7 @@
       <c r="Q82" s="31" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="32" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$7*B83,"")</f>
@@ -19285,7 +19377,7 @@
       <c r="Q83" s="31" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="32" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$7*B84,"")</f>
@@ -19331,7 +19423,7 @@
       <c r="Q84" s="31" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="32" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$7*B85,"")</f>
@@ -19377,7 +19469,7 @@
       <c r="Q85" s="31" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="32" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$7*B86,"")</f>
@@ -19423,7 +19515,7 @@
       <c r="Q86" s="31" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="32" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$7*B87,"")</f>
@@ -19469,7 +19561,7 @@
       <c r="Q87" s="31" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="32" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$7*B88,"")</f>
@@ -19515,7 +19607,7 @@
       <c r="Q88" s="31" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="32" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$7*B89,"")</f>
@@ -19561,7 +19653,7 @@
       <c r="Q89" s="31" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="32" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$7*B90,"")</f>
@@ -19607,7 +19699,7 @@
       <c r="Q90" s="31" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="32" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$7*B91,"")</f>
@@ -19653,7 +19745,7 @@
       <c r="Q91" s="31" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="32" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$7*B92,"")</f>
@@ -19699,7 +19791,7 @@
       <c r="Q92" s="31" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="32" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$7*B93,"")</f>
@@ -19745,7 +19837,7 @@
       <c r="Q93" s="31" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="32" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$7*B94,"")</f>
@@ -19791,7 +19883,7 @@
       <c r="Q94" s="31" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="32" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$7*B95,"")</f>
@@ -19837,7 +19929,7 @@
       <c r="Q95" s="31" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="32" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$7*B96,"")</f>
@@ -19883,7 +19975,7 @@
       <c r="Q96" s="31" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="32" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$7*B97,"")</f>
@@ -19929,7 +20021,7 @@
       <c r="Q97" s="31" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="32" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$7*B98,"")</f>
@@ -19975,7 +20067,7 @@
       <c r="Q98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="32" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$7*B99,"")</f>
@@ -20021,7 +20113,7 @@
       <c r="Q99" s="31" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="32" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$7*B100,"")</f>
@@ -20067,7 +20159,7 @@
       <c r="Q100" s="31" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="32" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$7*B101,"")</f>
@@ -20113,7 +20205,7 @@
       <c r="Q101" s="31" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="32" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$7*B102,"")</f>
@@ -20159,7 +20251,7 @@
       <c r="Q102" s="31" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="32" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$7*B103,"")</f>
@@ -20205,7 +20297,7 @@
       <c r="Q103" s="31" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="32" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$7*B104,"")</f>
@@ -20420,19 +20512,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$8*B5,"")</f>
         <v/>
       </c>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
+      <c r="D5" s="26" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>1.7458</v>
+      </c>
       <c r="F5" s="27">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="n"/>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -20449,8 +20553,12 @@
         <f>IFERROR(IF(F5&gt;=参数配置!$C$18,-(H5),IF(F5&gt;=参数配置!$C$17,-((H5-C5)*参数配置!$D$17),IF(F5&gt;=参数配置!$C$16,-((H5-C5)*参数配置!$D$16),IF(F5&gt;=参数配置!$C$15,-((H5-C5)*参数配置!$D$15),IF(F5&lt;=参数配置!$C$23,I5+参数配置!$C$8*参数配置!$D$23,IF(F5&lt;=参数配置!$C$22,I5+参数配置!$C$8*参数配置!$D$22,IF(F5&lt;=参数配置!$C$21,I5+参数配置!$C$8*参数配置!$D$21,I5))))))),"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="26" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>2284.8</v>
+      </c>
+      <c r="M5" s="26" t="n">
+        <v>1200</v>
+      </c>
       <c r="N5" s="30">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -20466,7 +20574,7 @@
       <c r="Q5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="32" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$8*B6,"")</f>
@@ -20512,7 +20620,7 @@
       <c r="Q6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="32" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$8*B7,"")</f>
@@ -20558,7 +20666,7 @@
       <c r="Q7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="32" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$8*B8,"")</f>
@@ -20604,7 +20712,7 @@
       <c r="Q8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="32" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$8*B9,"")</f>
@@ -20650,7 +20758,7 @@
       <c r="Q9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="32" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$8*B10,"")</f>
@@ -20696,7 +20804,7 @@
       <c r="Q10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="32" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$8*B11,"")</f>
@@ -20742,7 +20850,7 @@
       <c r="Q11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="32" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$8*B12,"")</f>
@@ -20788,7 +20896,7 @@
       <c r="Q12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="32" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$8*B13,"")</f>
@@ -20834,7 +20942,7 @@
       <c r="Q13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="32" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$8*B14,"")</f>
@@ -20880,7 +20988,7 @@
       <c r="Q14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="32" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$8*B15,"")</f>
@@ -20926,7 +21034,7 @@
       <c r="Q15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="32" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$8*B16,"")</f>
@@ -20972,7 +21080,7 @@
       <c r="Q16" s="31" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="32" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$8*B17,"")</f>
@@ -21018,7 +21126,7 @@
       <c r="Q17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="32" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$8*B18,"")</f>
@@ -21064,7 +21172,7 @@
       <c r="Q18" s="31" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="32" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$8*B19,"")</f>
@@ -21110,7 +21218,7 @@
       <c r="Q19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="32" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$8*B20,"")</f>
@@ -21156,7 +21264,7 @@
       <c r="Q20" s="31" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="32" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$8*B21,"")</f>
@@ -21202,7 +21310,7 @@
       <c r="Q21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="32" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$8*B22,"")</f>
@@ -21248,7 +21356,7 @@
       <c r="Q22" s="31" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="32" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$8*B23,"")</f>
@@ -21294,7 +21402,7 @@
       <c r="Q23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="32" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$8*B24,"")</f>
@@ -21340,7 +21448,7 @@
       <c r="Q24" s="31" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="32" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$8*B25,"")</f>
@@ -21386,7 +21494,7 @@
       <c r="Q25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="32" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$8*B26,"")</f>
@@ -21432,7 +21540,7 @@
       <c r="Q26" s="31" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="32" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$8*B27,"")</f>
@@ -21478,7 +21586,7 @@
       <c r="Q27" s="31" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="32" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$8*B28,"")</f>
@@ -21524,7 +21632,7 @@
       <c r="Q28" s="31" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="32" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$8*B29,"")</f>
@@ -21570,7 +21678,7 @@
       <c r="Q29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="32" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$8*B30,"")</f>
@@ -21616,7 +21724,7 @@
       <c r="Q30" s="31" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="32" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$8*B31,"")</f>
@@ -21662,7 +21770,7 @@
       <c r="Q31" s="31" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="32" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$8*B32,"")</f>
@@ -21708,7 +21816,7 @@
       <c r="Q32" s="31" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="32" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$8*B33,"")</f>
@@ -21754,7 +21862,7 @@
       <c r="Q33" s="31" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="32" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$8*B34,"")</f>
@@ -21800,7 +21908,7 @@
       <c r="Q34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="32" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$8*B35,"")</f>
@@ -21846,7 +21954,7 @@
       <c r="Q35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="32" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$8*B36,"")</f>
@@ -21892,7 +22000,7 @@
       <c r="Q36" s="31" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="32" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$8*B37,"")</f>
@@ -21938,7 +22046,7 @@
       <c r="Q37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="32" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$8*B38,"")</f>
@@ -21984,7 +22092,7 @@
       <c r="Q38" s="31" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="32" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$8*B39,"")</f>
@@ -22030,7 +22138,7 @@
       <c r="Q39" s="31" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="32" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$8*B40,"")</f>
@@ -22076,7 +22184,7 @@
       <c r="Q40" s="31" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="32" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$8*B41,"")</f>
@@ -22122,7 +22230,7 @@
       <c r="Q41" s="31" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="32" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$8*B42,"")</f>
@@ -22168,7 +22276,7 @@
       <c r="Q42" s="31" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="32" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$8*B43,"")</f>
@@ -22214,7 +22322,7 @@
       <c r="Q43" s="31" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="32" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$8*B44,"")</f>
@@ -22260,7 +22368,7 @@
       <c r="Q44" s="31" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="32" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$8*B45,"")</f>
@@ -22306,7 +22414,7 @@
       <c r="Q45" s="31" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="32" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$8*B46,"")</f>
@@ -22352,7 +22460,7 @@
       <c r="Q46" s="31" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="32" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$8*B47,"")</f>
@@ -22398,7 +22506,7 @@
       <c r="Q47" s="31" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="32" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$8*B48,"")</f>
@@ -22444,7 +22552,7 @@
       <c r="Q48" s="31" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="32" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$8*B49,"")</f>
@@ -22490,7 +22598,7 @@
       <c r="Q49" s="31" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="32" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$8*B50,"")</f>
@@ -22536,7 +22644,7 @@
       <c r="Q50" s="31" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="32" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$8*B51,"")</f>
@@ -22582,7 +22690,7 @@
       <c r="Q51" s="31" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="32" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$8*B52,"")</f>
@@ -22628,7 +22736,7 @@
       <c r="Q52" s="31" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="32" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$8*B53,"")</f>
@@ -22674,7 +22782,7 @@
       <c r="Q53" s="31" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="32" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$8*B54,"")</f>
@@ -22720,7 +22828,7 @@
       <c r="Q54" s="31" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="32" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$8*B55,"")</f>
@@ -22766,7 +22874,7 @@
       <c r="Q55" s="31" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="32" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$8*B56,"")</f>
@@ -22812,7 +22920,7 @@
       <c r="Q56" s="31" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="32" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$8*B57,"")</f>
@@ -22858,7 +22966,7 @@
       <c r="Q57" s="31" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="32" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$8*B58,"")</f>
@@ -22904,7 +23012,7 @@
       <c r="Q58" s="31" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="32" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$8*B59,"")</f>
@@ -22950,7 +23058,7 @@
       <c r="Q59" s="31" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="32" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$8*B60,"")</f>
@@ -22996,7 +23104,7 @@
       <c r="Q60" s="31" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="32" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$8*B61,"")</f>
@@ -23042,7 +23150,7 @@
       <c r="Q61" s="31" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="32" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$8*B62,"")</f>
@@ -23088,7 +23196,7 @@
       <c r="Q62" s="31" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="32" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$8*B63,"")</f>
@@ -23134,7 +23242,7 @@
       <c r="Q63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="32" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$8*B64,"")</f>
@@ -23180,7 +23288,7 @@
       <c r="Q64" s="31" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="32" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$8*B65,"")</f>
@@ -23226,7 +23334,7 @@
       <c r="Q65" s="31" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="32" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$8*B66,"")</f>
@@ -23272,7 +23380,7 @@
       <c r="Q66" s="31" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="32" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$8*B67,"")</f>
@@ -23318,7 +23426,7 @@
       <c r="Q67" s="31" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="32" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$8*B68,"")</f>
@@ -23364,7 +23472,7 @@
       <c r="Q68" s="31" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="32" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$8*B69,"")</f>
@@ -23410,7 +23518,7 @@
       <c r="Q69" s="31" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="32" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$8*B70,"")</f>
@@ -23456,7 +23564,7 @@
       <c r="Q70" s="31" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="32" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$8*B71,"")</f>
@@ -23502,7 +23610,7 @@
       <c r="Q71" s="31" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="32" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$8*B72,"")</f>
@@ -23548,7 +23656,7 @@
       <c r="Q72" s="31" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="32" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$8*B73,"")</f>
@@ -23594,7 +23702,7 @@
       <c r="Q73" s="31" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="32" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$8*B74,"")</f>
@@ -23640,7 +23748,7 @@
       <c r="Q74" s="31" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="32" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$8*B75,"")</f>
@@ -23686,7 +23794,7 @@
       <c r="Q75" s="31" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="32" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$8*B76,"")</f>
@@ -23732,7 +23840,7 @@
       <c r="Q76" s="31" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="32" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$8*B77,"")</f>
@@ -23778,7 +23886,7 @@
       <c r="Q77" s="31" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="32" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$8*B78,"")</f>
@@ -23824,7 +23932,7 @@
       <c r="Q78" s="31" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="32" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$8*B79,"")</f>
@@ -23870,7 +23978,7 @@
       <c r="Q79" s="31" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="32" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$8*B80,"")</f>
@@ -23916,7 +24024,7 @@
       <c r="Q80" s="31" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="32" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$8*B81,"")</f>
@@ -23962,7 +24070,7 @@
       <c r="Q81" s="31" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="32" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$8*B82,"")</f>
@@ -24008,7 +24116,7 @@
       <c r="Q82" s="31" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="32" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$8*B83,"")</f>
@@ -24054,7 +24162,7 @@
       <c r="Q83" s="31" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="32" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$8*B84,"")</f>
@@ -24100,7 +24208,7 @@
       <c r="Q84" s="31" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="32" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$8*B85,"")</f>
@@ -24146,7 +24254,7 @@
       <c r="Q85" s="31" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="32" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$8*B86,"")</f>
@@ -24192,7 +24300,7 @@
       <c r="Q86" s="31" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="32" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$8*B87,"")</f>
@@ -24238,7 +24346,7 @@
       <c r="Q87" s="31" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="32" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$8*B88,"")</f>
@@ -24284,7 +24392,7 @@
       <c r="Q88" s="31" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="32" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$8*B89,"")</f>
@@ -24330,7 +24438,7 @@
       <c r="Q89" s="31" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="32" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$8*B90,"")</f>
@@ -24376,7 +24484,7 @@
       <c r="Q90" s="31" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="32" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$8*B91,"")</f>
@@ -24422,7 +24530,7 @@
       <c r="Q91" s="31" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="32" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$8*B92,"")</f>
@@ -24468,7 +24576,7 @@
       <c r="Q92" s="31" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="32" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$8*B93,"")</f>
@@ -24514,7 +24622,7 @@
       <c r="Q93" s="31" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="32" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$8*B94,"")</f>
@@ -24560,7 +24668,7 @@
       <c r="Q94" s="31" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="32" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$8*B95,"")</f>
@@ -24606,7 +24714,7 @@
       <c r="Q95" s="31" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="32" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$8*B96,"")</f>
@@ -24652,7 +24760,7 @@
       <c r="Q96" s="31" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="32" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$8*B97,"")</f>
@@ -24698,7 +24806,7 @@
       <c r="Q97" s="31" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="32" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$8*B98,"")</f>
@@ -24744,7 +24852,7 @@
       <c r="Q98" s="31" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="32" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$8*B99,"")</f>
@@ -24790,7 +24898,7 @@
       <c r="Q99" s="31" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="32" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$8*B100,"")</f>
@@ -24836,7 +24944,7 @@
       <c r="Q100" s="31" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="32" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$8*B101,"")</f>
@@ -24882,7 +24990,7 @@
       <c r="Q101" s="31" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="32" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$8*B102,"")</f>
@@ -24928,7 +25036,7 @@
       <c r="Q102" s="31" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="32" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$8*B103,"")</f>
@@ -24974,7 +25082,7 @@
       <c r="Q103" s="31" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="32" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$8*B104,"")</f>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -5872,7 +5872,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>120日均线</t>
+          <t>250日均线</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>120日均线</t>
+          <t>250日均线</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>120日均线</t>
+          <t>250日均线</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>120日均线</t>
+          <t>250日均线</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>MAX(0,参数配置!$C$16-IFERROR(LOOKUP(2,1/(每期汇总!L5:L1000&lt;&gt;""),每期汇总!L5:L1000),0))</f>
+        <f>MAX(0,参数配置!$C$15-IFERROR(LOOKUP(2,1/(每期汇总!L5:L1000&lt;&gt;""),每期汇总!L5:L1000),0))</f>
         <v/>
       </c>
       <c r="C16" s="12" t="n"/>
@@ -1051,7 +1051,7 @@
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(IF(L5&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L5&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(IF(L6&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L6&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(IF(L7&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L7&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(IF(L8&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L8&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v/>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(IF(L9&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L9&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
         <v/>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(IF(L10&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L10&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         <v/>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(IF(L11&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L11&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(IF(L12&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L12&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(IF(L13&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L13&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(IF(L14&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L14&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(IF(L15&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L15&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(IF(L16&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L16&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(IF(L17&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L17&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
         <v/>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(IF(L18&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L18&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
         <v/>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(IF(L19&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L19&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v/>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(IF(L20&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L20&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(IF(L21&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L21&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
         <v/>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(IF(L22&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L22&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v/>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(IF(L23&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L23&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v/>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(IF(L24&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L24&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
         <v/>
       </c>
       <c r="M25" s="5">
-        <f>IFERROR(IF(L25&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L25&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
         <v/>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(IF(L26&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L26&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
         <v/>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(IF(L27&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L27&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
         <v/>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(IF(L28&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L28&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v/>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(IF(L29&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L29&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
         <v/>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(IF(L30&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L30&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
         <v/>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(IF(L31&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L31&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
         <v/>
       </c>
       <c r="M32" s="5">
-        <f>IFERROR(IF(L32&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L32&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         <v/>
       </c>
       <c r="M33" s="5">
-        <f>IFERROR(IF(L33&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L33&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
         <v/>
       </c>
       <c r="M34" s="5">
-        <f>IFERROR(IF(L34&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L34&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v/>
       </c>
       <c r="M35" s="5">
-        <f>IFERROR(IF(L35&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L35&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="M36" s="5">
-        <f>IFERROR(IF(L36&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L36&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
         <v/>
       </c>
       <c r="M37" s="5">
-        <f>IFERROR(IF(L37&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L37&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         <v/>
       </c>
       <c r="M38" s="5">
-        <f>IFERROR(IF(L38&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L38&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
         <v/>
       </c>
       <c r="M39" s="5">
-        <f>IFERROR(IF(L39&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L39&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
         <v/>
       </c>
       <c r="M40" s="5">
-        <f>IFERROR(IF(L40&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L40&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
         <v/>
       </c>
       <c r="M41" s="5">
-        <f>IFERROR(IF(L41&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L41&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
         <v/>
       </c>
       <c r="M42" s="5">
-        <f>IFERROR(IF(L42&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L42&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
         <v/>
       </c>
       <c r="M43" s="5">
-        <f>IFERROR(IF(L43&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L43&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         <v/>
       </c>
       <c r="M44" s="5">
-        <f>IFERROR(IF(L44&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L44&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="M45" s="5">
-        <f>IFERROR(IF(L45&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L45&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
         <v/>
       </c>
       <c r="M46" s="5">
-        <f>IFERROR(IF(L46&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L46&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
         <v/>
       </c>
       <c r="M47" s="5">
-        <f>IFERROR(IF(L47&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L47&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
         <v/>
       </c>
       <c r="M48" s="5">
-        <f>IFERROR(IF(L48&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L48&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="M49" s="5">
-        <f>IFERROR(IF(L49&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L49&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
         <v/>
       </c>
       <c r="M50" s="5">
-        <f>IFERROR(IF(L50&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L50&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v/>
       </c>
       <c r="M51" s="5">
-        <f>IFERROR(IF(L51&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L51&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
         <v/>
       </c>
       <c r="M52" s="5">
-        <f>IFERROR(IF(L52&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L52&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
         <v/>
       </c>
       <c r="M53" s="5">
-        <f>IFERROR(IF(L53&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L53&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
         <v/>
       </c>
       <c r="M54" s="5">
-        <f>IFERROR(IF(L54&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L54&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="M55" s="5">
-        <f>IFERROR(IF(L55&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L55&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
         <v/>
       </c>
       <c r="M56" s="5">
-        <f>IFERROR(IF(L56&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L56&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
         <v/>
       </c>
       <c r="M57" s="5">
-        <f>IFERROR(IF(L57&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L57&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
         <v/>
       </c>
       <c r="M58" s="5">
-        <f>IFERROR(IF(L58&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L58&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
         <v/>
       </c>
       <c r="M59" s="5">
-        <f>IFERROR(IF(L59&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L59&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         <v/>
       </c>
       <c r="M60" s="5">
-        <f>IFERROR(IF(L60&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L60&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
         <v/>
       </c>
       <c r="M61" s="5">
-        <f>IFERROR(IF(L61&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L61&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
         <v/>
       </c>
       <c r="M62" s="5">
-        <f>IFERROR(IF(L62&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L62&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
         <v/>
       </c>
       <c r="M63" s="5">
-        <f>IFERROR(IF(L63&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L63&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v/>
       </c>
       <c r="M64" s="5">
-        <f>IFERROR(IF(L64&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L64&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
         <v/>
       </c>
       <c r="M65" s="5">
-        <f>IFERROR(IF(L65&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L65&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
         <v/>
       </c>
       <c r="M66" s="5">
-        <f>IFERROR(IF(L66&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L66&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
         <v/>
       </c>
       <c r="M67" s="5">
-        <f>IFERROR(IF(L67&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L67&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
         <v/>
       </c>
       <c r="M68" s="5">
-        <f>IFERROR(IF(L68&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L68&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
         <v/>
       </c>
       <c r="M69" s="5">
-        <f>IFERROR(IF(L69&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L69&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
         <v/>
       </c>
       <c r="M70" s="5">
-        <f>IFERROR(IF(L70&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L70&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="M71" s="5">
-        <f>IFERROR(IF(L71&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L71&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
         <v/>
       </c>
       <c r="M72" s="5">
-        <f>IFERROR(IF(L72&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L72&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
         <v/>
       </c>
       <c r="M73" s="5">
-        <f>IFERROR(IF(L73&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L73&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
         <v/>
       </c>
       <c r="M74" s="5">
-        <f>IFERROR(IF(L74&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L74&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v/>
       </c>
       <c r="M75" s="5">
-        <f>IFERROR(IF(L75&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L75&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
         <v/>
       </c>
       <c r="M76" s="5">
-        <f>IFERROR(IF(L76&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L76&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v/>
       </c>
       <c r="M77" s="5">
-        <f>IFERROR(IF(L77&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L77&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="M78" s="5">
-        <f>IFERROR(IF(L78&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L78&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
         <v/>
       </c>
       <c r="M79" s="5">
-        <f>IFERROR(IF(L79&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L79&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
         <v/>
       </c>
       <c r="M80" s="5">
-        <f>IFERROR(IF(L80&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L80&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
         <v/>
       </c>
       <c r="M81" s="5">
-        <f>IFERROR(IF(L81&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L81&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
         <v/>
       </c>
       <c r="M82" s="5">
-        <f>IFERROR(IF(L82&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L82&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
         <v/>
       </c>
       <c r="M83" s="5">
-        <f>IFERROR(IF(L83&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L83&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
         <v/>
       </c>
       <c r="M84" s="5">
-        <f>IFERROR(IF(L84&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L84&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
         <v/>
       </c>
       <c r="M85" s="5">
-        <f>IFERROR(IF(L85&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L85&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
         <v/>
       </c>
       <c r="M86" s="5">
-        <f>IFERROR(IF(L86&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L86&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
         <v/>
       </c>
       <c r="M87" s="5">
-        <f>IFERROR(IF(L87&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L87&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
         <v/>
       </c>
       <c r="M88" s="5">
-        <f>IFERROR(IF(L88&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L88&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="M89" s="5">
-        <f>IFERROR(IF(L89&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L89&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v/>
       </c>
       <c r="M90" s="5">
-        <f>IFERROR(IF(L90&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L90&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         <v/>
       </c>
       <c r="M91" s="5">
-        <f>IFERROR(IF(L91&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L91&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
         <v/>
       </c>
       <c r="M92" s="5">
-        <f>IFERROR(IF(L92&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L92&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
         <v/>
       </c>
       <c r="M93" s="5">
-        <f>IFERROR(IF(L93&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L93&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
         <v/>
       </c>
       <c r="M94" s="5">
-        <f>IFERROR(IF(L94&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L94&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
         <v/>
       </c>
       <c r="M95" s="5">
-        <f>IFERROR(IF(L95&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L95&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
         <v/>
       </c>
       <c r="M96" s="5">
-        <f>IFERROR(IF(L96&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L96&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
         <v/>
       </c>
       <c r="M97" s="5">
-        <f>IFERROR(IF(L97&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L97&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
         <v/>
       </c>
       <c r="M98" s="5">
-        <f>IFERROR(IF(L98&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L98&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
         <v/>
       </c>
       <c r="M99" s="5">
-        <f>IFERROR(IF(L99&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L99&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="M100" s="5">
-        <f>IFERROR(IF(L100&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L100&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         <v/>
       </c>
       <c r="M101" s="5">
-        <f>IFERROR(IF(L101&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L101&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v/>
       </c>
       <c r="M102" s="5">
-        <f>IFERROR(IF(L102&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L102&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
         <v/>
       </c>
       <c r="M103" s="5">
-        <f>IFERROR(IF(L103&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L103&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
         <v/>
       </c>
       <c r="M104" s="5">
-        <f>IFERROR(IF(L104&gt;=参数配置!$C$16,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L104&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5689,69 +5689,53 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>减半清仓偏离度阈值</t>
+          <t>全仓清仓偏离度阈值</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="20" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>偏离度超 +35%，卖至目标市值 50%，不进冷却</t>
+          <t>偏离度超 +55%，全部清仓并进入冷却期；冷却期目标冻结，解除后从第 1 期重新积累</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>全仓清仓偏离度阈值</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="20" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>偏离度超 +55%，全部清仓并进入冷却期</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>三、增量阶段</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>触发门槛（累计净投入）</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="17" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>达到后切换为增量阶段，买卖均走储备金池</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>触发门槛（累计净投入）</t>
+          <t>每期增量注入金额</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="17" t="n">
-        <v>150000</v>
+        <v>2000</v>
       </c>
       <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>达到后切换为增量阶段，买卖均走储备金池</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>每期增量注入金额</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>每期向储备金池注入的新增资金</t>
         </is>
@@ -5760,9 +5744,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D17:E17"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5955,11 +5939,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,-H5,IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),-(H5-C5*0.5),C5-H5)),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),"减半清仓",IF(H5&gt;C5,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -6001,11 +5985,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,-H6,IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),-(H6-C6*0.5),C6-H6)),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),"减半清仓",IF(H6&gt;C6,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -6047,11 +6031,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,-H7,IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),-(H7-C7*0.5),C7-H7)),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),"减半清仓",IF(H7&gt;C7,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -6093,11 +6077,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,-H8,IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),-(H8-C8*0.5),C8-H8)),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),"减半清仓",IF(H8&gt;C8,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -6139,11 +6123,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,-H9,IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),-(H9-C9*0.5),C9-H9)),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),"减半清仓",IF(H9&gt;C9,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -6185,11 +6169,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,-H10,IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),-(H10-C10*0.5),C10-H10)),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),"减半清仓",IF(H10&gt;C10,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -6231,11 +6215,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,-H11,IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),-(H11-C11*0.5),C11-H11)),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),"减半清仓",IF(H11&gt;C11,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -6277,11 +6261,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,-H12,IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),-(H12-C12*0.5),C12-H12)),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),"减半清仓",IF(H12&gt;C12,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -6323,11 +6307,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,-H13,IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),-(H13-C13*0.5),C13-H13)),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),"减半清仓",IF(H13&gt;C13,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -6369,11 +6353,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,-H14,IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),-(H14-C14*0.5),C14-H14)),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),"减半清仓",IF(H14&gt;C14,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -6415,11 +6399,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,-H15,IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),-(H15-C15*0.5),C15-H15)),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),"减半清仓",IF(H15&gt;C15,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -6461,11 +6445,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,-H16,IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),-(H16-C16*0.5),C16-H16)),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),"减半清仓",IF(H16&gt;C16,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -6507,11 +6491,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,-H17,IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),-(H17-C17*0.5),C17-H17)),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),"减半清仓",IF(H17&gt;C17,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -6553,11 +6537,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,-H18,IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),-(H18-C18*0.5),C18-H18)),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),"减半清仓",IF(H18&gt;C18,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -6599,11 +6583,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,-H19,IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),-(H19-C19*0.5),C19-H19)),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),"减半清仓",IF(H19&gt;C19,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -6645,11 +6629,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,-H20,IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),-(H20-C20*0.5),C20-H20)),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),"减半清仓",IF(H20&gt;C20,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -6691,11 +6675,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,-H21,IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),-(H21-C21*0.5),C21-H21)),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),"减半清仓",IF(H21&gt;C21,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -6737,11 +6721,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,-H22,IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),-(H22-C22*0.5),C22-H22)),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),"减半清仓",IF(H22&gt;C22,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -6783,11 +6767,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,-H23,IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),-(H23-C23*0.5),C23-H23)),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),"减半清仓",IF(H23&gt;C23,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -6829,11 +6813,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,-H24,IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),-(H24-C24*0.5),C24-H24)),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),"减半清仓",IF(H24&gt;C24,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -6875,11 +6859,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,-H25,IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),-(H25-C25*0.5),C25-H25)),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),"减半清仓",IF(H25&gt;C25,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -6921,11 +6905,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,-H26,IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),-(H26-C26*0.5),C26-H26)),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),"减半清仓",IF(H26&gt;C26,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -6967,11 +6951,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,-H27,IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),-(H27-C27*0.5),C27-H27)),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),"减半清仓",IF(H27&gt;C27,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -7013,11 +6997,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,-H28,IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),-(H28-C28*0.5),C28-H28)),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),"减半清仓",IF(H28&gt;C28,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -7059,11 +7043,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,-H29,IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),-(H29-C29*0.5),C29-H29)),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),"减半清仓",IF(H29&gt;C29,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -7105,11 +7089,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,-H30,IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),-(H30-C30*0.5),C30-H30)),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),"减半清仓",IF(H30&gt;C30,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -7151,11 +7135,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,-H31,IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),-(H31-C31*0.5),C31-H31)),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),"减半清仓",IF(H31&gt;C31,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -7197,11 +7181,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,-H32,IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),-(H32-C32*0.5),C32-H32)),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),"减半清仓",IF(H32&gt;C32,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -7243,11 +7227,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,-H33,IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),-(H33-C33*0.5),C33-H33)),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),"减半清仓",IF(H33&gt;C33,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -7289,11 +7273,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,-H34,IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),-(H34-C34*0.5),C34-H34)),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),"减半清仓",IF(H34&gt;C34,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -7335,11 +7319,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,-H35,IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),-(H35-C35*0.5),C35-H35)),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),"减半清仓",IF(H35&gt;C35,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -7381,11 +7365,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,-H36,IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),-(H36-C36*0.5),C36-H36)),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),"减半清仓",IF(H36&gt;C36,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -7427,11 +7411,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,-H37,IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),-(H37-C37*0.5),C37-H37)),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),"减半清仓",IF(H37&gt;C37,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -7473,11 +7457,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,-H38,IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),-(H38-C38*0.5),C38-H38)),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),"减半清仓",IF(H38&gt;C38,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -7519,11 +7503,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,-H39,IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),-(H39-C39*0.5),C39-H39)),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),"减半清仓",IF(H39&gt;C39,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -7565,11 +7549,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,-H40,IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),-(H40-C40*0.5),C40-H40)),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),"减半清仓",IF(H40&gt;C40,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -7611,11 +7595,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,-H41,IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),-(H41-C41*0.5),C41-H41)),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),"减半清仓",IF(H41&gt;C41,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -7657,11 +7641,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,-H42,IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),-(H42-C42*0.5),C42-H42)),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),"减半清仓",IF(H42&gt;C42,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -7703,11 +7687,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,-H43,IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),-(H43-C43*0.5),C43-H43)),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),"减半清仓",IF(H43&gt;C43,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -7749,11 +7733,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,-H44,IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),-(H44-C44*0.5),C44-H44)),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),"减半清仓",IF(H44&gt;C44,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -7795,11 +7779,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,-H45,IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),-(H45-C45*0.5),C45-H45)),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),"减半清仓",IF(H45&gt;C45,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -7841,11 +7825,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,-H46,IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),-(H46-C46*0.5),C46-H46)),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),"减半清仓",IF(H46&gt;C46,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -7887,11 +7871,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,-H47,IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),-(H47-C47*0.5),C47-H47)),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),"减半清仓",IF(H47&gt;C47,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -7933,11 +7917,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,-H48,IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),-(H48-C48*0.5),C48-H48)),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),"减半清仓",IF(H48&gt;C48,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -7979,11 +7963,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,-H49,IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),-(H49-C49*0.5),C49-H49)),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),"减半清仓",IF(H49&gt;C49,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -8025,11 +8009,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,-H50,IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),-(H50-C50*0.5),C50-H50)),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),"减半清仓",IF(H50&gt;C50,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -8071,11 +8055,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,-H51,IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),-(H51-C51*0.5),C51-H51)),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),"减半清仓",IF(H51&gt;C51,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -8117,11 +8101,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,-H52,IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),-(H52-C52*0.5),C52-H52)),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),"减半清仓",IF(H52&gt;C52,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -8163,11 +8147,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,-H53,IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),-(H53-C53*0.5),C53-H53)),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),"减半清仓",IF(H53&gt;C53,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -8209,11 +8193,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,-H54,IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),-(H54-C54*0.5),C54-H54)),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),"减半清仓",IF(H54&gt;C54,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -8255,11 +8239,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,-H55,IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),-(H55-C55*0.5),C55-H55)),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),"减半清仓",IF(H55&gt;C55,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -8301,11 +8285,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,-H56,IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),-(H56-C56*0.5),C56-H56)),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),"减半清仓",IF(H56&gt;C56,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -8347,11 +8331,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,-H57,IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),-(H57-C57*0.5),C57-H57)),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),"减半清仓",IF(H57&gt;C57,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -8393,11 +8377,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,-H58,IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),-(H58-C58*0.5),C58-H58)),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),"减半清仓",IF(H58&gt;C58,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -8439,11 +8423,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,-H59,IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),-(H59-C59*0.5),C59-H59)),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),"减半清仓",IF(H59&gt;C59,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -8485,11 +8469,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,-H60,IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),-(H60-C60*0.5),C60-H60)),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),"减半清仓",IF(H60&gt;C60,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -8531,11 +8515,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,-H61,IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),-(H61-C61*0.5),C61-H61)),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),"减半清仓",IF(H61&gt;C61,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -8577,11 +8561,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,-H62,IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),-(H62-C62*0.5),C62-H62)),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),"减半清仓",IF(H62&gt;C62,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -8623,11 +8607,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,-H63,IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),-(H63-C63*0.5),C63-H63)),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),"减半清仓",IF(H63&gt;C63,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -8669,11 +8653,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,-H64,IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),-(H64-C64*0.5),C64-H64)),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),"减半清仓",IF(H64&gt;C64,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -8715,11 +8699,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,-H65,IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),-(H65-C65*0.5),C65-H65)),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),"减半清仓",IF(H65&gt;C65,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -8761,11 +8745,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,-H66,IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),-(H66-C66*0.5),C66-H66)),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),"减半清仓",IF(H66&gt;C66,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -8807,11 +8791,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,-H67,IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),-(H67-C67*0.5),C67-H67)),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),"减半清仓",IF(H67&gt;C67,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -8853,11 +8837,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,-H68,IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),-(H68-C68*0.5),C68-H68)),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),"减半清仓",IF(H68&gt;C68,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -8899,11 +8883,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,-H69,IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),-(H69-C69*0.5),C69-H69)),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),"减半清仓",IF(H69&gt;C69,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -8945,11 +8929,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,-H70,IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),-(H70-C70*0.5),C70-H70)),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),"减半清仓",IF(H70&gt;C70,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -8991,11 +8975,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,-H71,IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),-(H71-C71*0.5),C71-H71)),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),"减半清仓",IF(H71&gt;C71,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -9037,11 +9021,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,-H72,IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),-(H72-C72*0.5),C72-H72)),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),"减半清仓",IF(H72&gt;C72,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -9083,11 +9067,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,-H73,IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),-(H73-C73*0.5),C73-H73)),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),"减半清仓",IF(H73&gt;C73,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -9129,11 +9113,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,-H74,IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),-(H74-C74*0.5),C74-H74)),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),"减半清仓",IF(H74&gt;C74,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -9175,11 +9159,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,-H75,IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),-(H75-C75*0.5),C75-H75)),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),"减半清仓",IF(H75&gt;C75,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -9221,11 +9205,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,-H76,IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),-(H76-C76*0.5),C76-H76)),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),"减半清仓",IF(H76&gt;C76,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -9267,11 +9251,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,-H77,IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),-(H77-C77*0.5),C77-H77)),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),"减半清仓",IF(H77&gt;C77,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -9313,11 +9297,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,-H78,IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),-(H78-C78*0.5),C78-H78)),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),"减半清仓",IF(H78&gt;C78,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -9359,11 +9343,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,-H79,IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),-(H79-C79*0.5),C79-H79)),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),"减半清仓",IF(H79&gt;C79,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -9405,11 +9389,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,-H80,IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),-(H80-C80*0.5),C80-H80)),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),"减半清仓",IF(H80&gt;C80,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -9451,11 +9435,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,-H81,IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),-(H81-C81*0.5),C81-H81)),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),"减半清仓",IF(H81&gt;C81,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -9497,11 +9481,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,-H82,IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),-(H82-C82*0.5),C82-H82)),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),"减半清仓",IF(H82&gt;C82,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -9543,11 +9527,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,-H83,IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),-(H83-C83*0.5),C83-H83)),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),"减半清仓",IF(H83&gt;C83,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -9589,11 +9573,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,-H84,IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),-(H84-C84*0.5),C84-H84)),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),"减半清仓",IF(H84&gt;C84,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -9635,11 +9619,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,-H85,IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),-(H85-C85*0.5),C85-H85)),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),"减半清仓",IF(H85&gt;C85,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -9681,11 +9665,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,-H86,IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),-(H86-C86*0.5),C86-H86)),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),"减半清仓",IF(H86&gt;C86,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -9727,11 +9711,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,-H87,IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),-(H87-C87*0.5),C87-H87)),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),"减半清仓",IF(H87&gt;C87,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -9773,11 +9757,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,-H88,IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),-(H88-C88*0.5),C88-H88)),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),"减半清仓",IF(H88&gt;C88,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -9819,11 +9803,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,-H89,IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),-(H89-C89*0.5),C89-H89)),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),"减半清仓",IF(H89&gt;C89,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -9865,11 +9849,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,-H90,IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),-(H90-C90*0.5),C90-H90)),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),"减半清仓",IF(H90&gt;C90,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -9911,11 +9895,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,-H91,IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),-(H91-C91*0.5),C91-H91)),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),"减半清仓",IF(H91&gt;C91,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -9957,11 +9941,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,-H92,IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),-(H92-C92*0.5),C92-H92)),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),"减半清仓",IF(H92&gt;C92,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -10003,11 +9987,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,-H93,IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),-(H93-C93*0.5),C93-H93)),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),"减半清仓",IF(H93&gt;C93,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -10049,11 +10033,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,-H94,IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),-(H94-C94*0.5),C94-H94)),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),"减半清仓",IF(H94&gt;C94,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -10095,11 +10079,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,-H95,IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),-(H95-C95*0.5),C95-H95)),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),"减半清仓",IF(H95&gt;C95,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -10141,11 +10125,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,-H96,IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),-(H96-C96*0.5),C96-H96)),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),"减半清仓",IF(H96&gt;C96,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -10187,11 +10171,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,-H97,IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),-(H97-C97*0.5),C97-H97)),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),"减半清仓",IF(H97&gt;C97,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -10233,11 +10217,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,-H98,IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),-(H98-C98*0.5),C98-H98)),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),"减半清仓",IF(H98&gt;C98,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -10279,11 +10263,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,-H99,IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),-(H99-C99*0.5),C99-H99)),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),"减半清仓",IF(H99&gt;C99,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -10325,11 +10309,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,-H100,IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),-(H100-C100*0.5),C100-H100)),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),"减半清仓",IF(H100&gt;C100,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -10371,11 +10355,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,-H101,IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),-(H101-C101*0.5),C101-H101)),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),"减半清仓",IF(H101&gt;C101,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -10417,11 +10401,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,-H102,IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),-(H102-C102*0.5),C102-H102)),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),"减半清仓",IF(H102&gt;C102,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -10463,11 +10447,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,-H103,IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),-(H103-C103*0.5),C103-H103)),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),"减半清仓",IF(H103&gt;C103,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -10509,11 +10493,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,-H104,IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),-(H104-C104*0.5),C104-H104)),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),"减半清仓",IF(H104&gt;C104,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">
@@ -10732,11 +10716,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,-H5,IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),-(H5-C5*0.5),C5-H5)),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),"减半清仓",IF(H5&gt;C5,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -10778,11 +10762,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,-H6,IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),-(H6-C6*0.5),C6-H6)),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),"减半清仓",IF(H6&gt;C6,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -10824,11 +10808,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,-H7,IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),-(H7-C7*0.5),C7-H7)),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),"减半清仓",IF(H7&gt;C7,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -10870,11 +10854,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,-H8,IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),-(H8-C8*0.5),C8-H8)),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),"减半清仓",IF(H8&gt;C8,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -10916,11 +10900,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,-H9,IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),-(H9-C9*0.5),C9-H9)),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),"减半清仓",IF(H9&gt;C9,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -10962,11 +10946,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,-H10,IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),-(H10-C10*0.5),C10-H10)),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),"减半清仓",IF(H10&gt;C10,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -11008,11 +10992,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,-H11,IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),-(H11-C11*0.5),C11-H11)),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),"减半清仓",IF(H11&gt;C11,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -11054,11 +11038,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,-H12,IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),-(H12-C12*0.5),C12-H12)),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),"减半清仓",IF(H12&gt;C12,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -11100,11 +11084,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,-H13,IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),-(H13-C13*0.5),C13-H13)),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),"减半清仓",IF(H13&gt;C13,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -11146,11 +11130,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,-H14,IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),-(H14-C14*0.5),C14-H14)),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),"减半清仓",IF(H14&gt;C14,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -11192,11 +11176,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,-H15,IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),-(H15-C15*0.5),C15-H15)),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),"减半清仓",IF(H15&gt;C15,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -11238,11 +11222,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,-H16,IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),-(H16-C16*0.5),C16-H16)),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),"减半清仓",IF(H16&gt;C16,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -11284,11 +11268,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,-H17,IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),-(H17-C17*0.5),C17-H17)),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),"减半清仓",IF(H17&gt;C17,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -11330,11 +11314,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,-H18,IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),-(H18-C18*0.5),C18-H18)),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),"减半清仓",IF(H18&gt;C18,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -11376,11 +11360,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,-H19,IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),-(H19-C19*0.5),C19-H19)),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),"减半清仓",IF(H19&gt;C19,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -11422,11 +11406,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,-H20,IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),-(H20-C20*0.5),C20-H20)),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),"减半清仓",IF(H20&gt;C20,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -11468,11 +11452,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,-H21,IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),-(H21-C21*0.5),C21-H21)),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),"减半清仓",IF(H21&gt;C21,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -11514,11 +11498,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,-H22,IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),-(H22-C22*0.5),C22-H22)),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),"减半清仓",IF(H22&gt;C22,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -11560,11 +11544,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,-H23,IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),-(H23-C23*0.5),C23-H23)),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),"减半清仓",IF(H23&gt;C23,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -11606,11 +11590,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,-H24,IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),-(H24-C24*0.5),C24-H24)),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),"减半清仓",IF(H24&gt;C24,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -11652,11 +11636,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,-H25,IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),-(H25-C25*0.5),C25-H25)),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),"减半清仓",IF(H25&gt;C25,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -11698,11 +11682,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,-H26,IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),-(H26-C26*0.5),C26-H26)),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),"减半清仓",IF(H26&gt;C26,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -11744,11 +11728,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,-H27,IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),-(H27-C27*0.5),C27-H27)),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),"减半清仓",IF(H27&gt;C27,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -11790,11 +11774,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,-H28,IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),-(H28-C28*0.5),C28-H28)),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),"减半清仓",IF(H28&gt;C28,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -11836,11 +11820,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,-H29,IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),-(H29-C29*0.5),C29-H29)),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),"减半清仓",IF(H29&gt;C29,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -11882,11 +11866,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,-H30,IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),-(H30-C30*0.5),C30-H30)),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),"减半清仓",IF(H30&gt;C30,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -11928,11 +11912,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,-H31,IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),-(H31-C31*0.5),C31-H31)),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),"减半清仓",IF(H31&gt;C31,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -11974,11 +11958,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,-H32,IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),-(H32-C32*0.5),C32-H32)),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),"减半清仓",IF(H32&gt;C32,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -12020,11 +12004,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,-H33,IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),-(H33-C33*0.5),C33-H33)),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),"减半清仓",IF(H33&gt;C33,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -12066,11 +12050,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,-H34,IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),-(H34-C34*0.5),C34-H34)),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),"减半清仓",IF(H34&gt;C34,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -12112,11 +12096,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,-H35,IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),-(H35-C35*0.5),C35-H35)),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),"减半清仓",IF(H35&gt;C35,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -12158,11 +12142,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,-H36,IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),-(H36-C36*0.5),C36-H36)),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),"减半清仓",IF(H36&gt;C36,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -12204,11 +12188,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,-H37,IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),-(H37-C37*0.5),C37-H37)),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),"减半清仓",IF(H37&gt;C37,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -12250,11 +12234,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,-H38,IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),-(H38-C38*0.5),C38-H38)),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),"减半清仓",IF(H38&gt;C38,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -12296,11 +12280,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,-H39,IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),-(H39-C39*0.5),C39-H39)),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),"减半清仓",IF(H39&gt;C39,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -12342,11 +12326,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,-H40,IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),-(H40-C40*0.5),C40-H40)),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),"减半清仓",IF(H40&gt;C40,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -12388,11 +12372,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,-H41,IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),-(H41-C41*0.5),C41-H41)),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),"减半清仓",IF(H41&gt;C41,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -12434,11 +12418,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,-H42,IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),-(H42-C42*0.5),C42-H42)),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),"减半清仓",IF(H42&gt;C42,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -12480,11 +12464,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,-H43,IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),-(H43-C43*0.5),C43-H43)),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),"减半清仓",IF(H43&gt;C43,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -12526,11 +12510,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,-H44,IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),-(H44-C44*0.5),C44-H44)),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),"减半清仓",IF(H44&gt;C44,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -12572,11 +12556,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,-H45,IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),-(H45-C45*0.5),C45-H45)),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),"减半清仓",IF(H45&gt;C45,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -12618,11 +12602,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,-H46,IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),-(H46-C46*0.5),C46-H46)),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),"减半清仓",IF(H46&gt;C46,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -12664,11 +12648,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,-H47,IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),-(H47-C47*0.5),C47-H47)),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),"减半清仓",IF(H47&gt;C47,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -12710,11 +12694,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,-H48,IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),-(H48-C48*0.5),C48-H48)),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),"减半清仓",IF(H48&gt;C48,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -12756,11 +12740,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,-H49,IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),-(H49-C49*0.5),C49-H49)),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),"减半清仓",IF(H49&gt;C49,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -12802,11 +12786,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,-H50,IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),-(H50-C50*0.5),C50-H50)),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),"减半清仓",IF(H50&gt;C50,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -12848,11 +12832,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,-H51,IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),-(H51-C51*0.5),C51-H51)),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),"减半清仓",IF(H51&gt;C51,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -12894,11 +12878,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,-H52,IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),-(H52-C52*0.5),C52-H52)),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),"减半清仓",IF(H52&gt;C52,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -12940,11 +12924,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,-H53,IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),-(H53-C53*0.5),C53-H53)),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),"减半清仓",IF(H53&gt;C53,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -12986,11 +12970,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,-H54,IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),-(H54-C54*0.5),C54-H54)),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),"减半清仓",IF(H54&gt;C54,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -13032,11 +13016,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,-H55,IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),-(H55-C55*0.5),C55-H55)),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),"减半清仓",IF(H55&gt;C55,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -13078,11 +13062,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,-H56,IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),-(H56-C56*0.5),C56-H56)),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),"减半清仓",IF(H56&gt;C56,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -13124,11 +13108,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,-H57,IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),-(H57-C57*0.5),C57-H57)),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),"减半清仓",IF(H57&gt;C57,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -13170,11 +13154,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,-H58,IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),-(H58-C58*0.5),C58-H58)),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),"减半清仓",IF(H58&gt;C58,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -13216,11 +13200,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,-H59,IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),-(H59-C59*0.5),C59-H59)),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),"减半清仓",IF(H59&gt;C59,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -13262,11 +13246,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,-H60,IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),-(H60-C60*0.5),C60-H60)),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),"减半清仓",IF(H60&gt;C60,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -13308,11 +13292,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,-H61,IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),-(H61-C61*0.5),C61-H61)),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),"减半清仓",IF(H61&gt;C61,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -13354,11 +13338,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,-H62,IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),-(H62-C62*0.5),C62-H62)),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),"减半清仓",IF(H62&gt;C62,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -13400,11 +13384,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,-H63,IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),-(H63-C63*0.5),C63-H63)),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),"减半清仓",IF(H63&gt;C63,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -13446,11 +13430,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,-H64,IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),-(H64-C64*0.5),C64-H64)),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),"减半清仓",IF(H64&gt;C64,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -13492,11 +13476,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,-H65,IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),-(H65-C65*0.5),C65-H65)),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),"减半清仓",IF(H65&gt;C65,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -13538,11 +13522,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,-H66,IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),-(H66-C66*0.5),C66-H66)),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),"减半清仓",IF(H66&gt;C66,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -13584,11 +13568,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,-H67,IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),-(H67-C67*0.5),C67-H67)),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),"减半清仓",IF(H67&gt;C67,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -13630,11 +13614,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,-H68,IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),-(H68-C68*0.5),C68-H68)),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),"减半清仓",IF(H68&gt;C68,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -13676,11 +13660,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,-H69,IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),-(H69-C69*0.5),C69-H69)),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),"减半清仓",IF(H69&gt;C69,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -13722,11 +13706,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,-H70,IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),-(H70-C70*0.5),C70-H70)),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),"减半清仓",IF(H70&gt;C70,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -13768,11 +13752,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,-H71,IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),-(H71-C71*0.5),C71-H71)),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),"减半清仓",IF(H71&gt;C71,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -13814,11 +13798,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,-H72,IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),-(H72-C72*0.5),C72-H72)),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),"减半清仓",IF(H72&gt;C72,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -13860,11 +13844,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,-H73,IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),-(H73-C73*0.5),C73-H73)),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),"减半清仓",IF(H73&gt;C73,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -13906,11 +13890,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,-H74,IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),-(H74-C74*0.5),C74-H74)),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),"减半清仓",IF(H74&gt;C74,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -13952,11 +13936,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,-H75,IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),-(H75-C75*0.5),C75-H75)),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),"减半清仓",IF(H75&gt;C75,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -13998,11 +13982,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,-H76,IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),-(H76-C76*0.5),C76-H76)),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),"减半清仓",IF(H76&gt;C76,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -14044,11 +14028,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,-H77,IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),-(H77-C77*0.5),C77-H77)),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),"减半清仓",IF(H77&gt;C77,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -14090,11 +14074,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,-H78,IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),-(H78-C78*0.5),C78-H78)),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),"减半清仓",IF(H78&gt;C78,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -14136,11 +14120,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,-H79,IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),-(H79-C79*0.5),C79-H79)),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),"减半清仓",IF(H79&gt;C79,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -14182,11 +14166,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,-H80,IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),-(H80-C80*0.5),C80-H80)),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),"减半清仓",IF(H80&gt;C80,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -14228,11 +14212,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,-H81,IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),-(H81-C81*0.5),C81-H81)),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),"减半清仓",IF(H81&gt;C81,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -14274,11 +14258,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,-H82,IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),-(H82-C82*0.5),C82-H82)),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),"减半清仓",IF(H82&gt;C82,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -14320,11 +14304,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,-H83,IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),-(H83-C83*0.5),C83-H83)),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),"减半清仓",IF(H83&gt;C83,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -14366,11 +14350,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,-H84,IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),-(H84-C84*0.5),C84-H84)),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),"减半清仓",IF(H84&gt;C84,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -14412,11 +14396,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,-H85,IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),-(H85-C85*0.5),C85-H85)),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),"减半清仓",IF(H85&gt;C85,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -14458,11 +14442,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,-H86,IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),-(H86-C86*0.5),C86-H86)),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),"减半清仓",IF(H86&gt;C86,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -14504,11 +14488,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,-H87,IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),-(H87-C87*0.5),C87-H87)),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),"减半清仓",IF(H87&gt;C87,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -14550,11 +14534,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,-H88,IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),-(H88-C88*0.5),C88-H88)),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),"减半清仓",IF(H88&gt;C88,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -14596,11 +14580,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,-H89,IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),-(H89-C89*0.5),C89-H89)),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),"减半清仓",IF(H89&gt;C89,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -14642,11 +14626,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,-H90,IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),-(H90-C90*0.5),C90-H90)),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),"减半清仓",IF(H90&gt;C90,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -14688,11 +14672,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,-H91,IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),-(H91-C91*0.5),C91-H91)),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),"减半清仓",IF(H91&gt;C91,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -14734,11 +14718,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,-H92,IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),-(H92-C92*0.5),C92-H92)),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),"减半清仓",IF(H92&gt;C92,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -14780,11 +14764,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,-H93,IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),-(H93-C93*0.5),C93-H93)),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),"减半清仓",IF(H93&gt;C93,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -14826,11 +14810,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,-H94,IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),-(H94-C94*0.5),C94-H94)),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),"减半清仓",IF(H94&gt;C94,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -14872,11 +14856,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,-H95,IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),-(H95-C95*0.5),C95-H95)),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),"减半清仓",IF(H95&gt;C95,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -14918,11 +14902,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,-H96,IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),-(H96-C96*0.5),C96-H96)),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),"减半清仓",IF(H96&gt;C96,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -14964,11 +14948,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,-H97,IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),-(H97-C97*0.5),C97-H97)),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),"减半清仓",IF(H97&gt;C97,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -15010,11 +14994,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,-H98,IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),-(H98-C98*0.5),C98-H98)),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),"减半清仓",IF(H98&gt;C98,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -15056,11 +15040,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,-H99,IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),-(H99-C99*0.5),C99-H99)),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),"减半清仓",IF(H99&gt;C99,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -15102,11 +15086,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,-H100,IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),-(H100-C100*0.5),C100-H100)),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),"减半清仓",IF(H100&gt;C100,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -15148,11 +15132,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,-H101,IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),-(H101-C101*0.5),C101-H101)),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),"减半清仓",IF(H101&gt;C101,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -15194,11 +15178,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,-H102,IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),-(H102-C102*0.5),C102-H102)),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),"减半清仓",IF(H102&gt;C102,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -15240,11 +15224,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,-H103,IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),-(H103-C103*0.5),C103-H103)),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),"减半清仓",IF(H103&gt;C103,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -15286,11 +15270,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,-H104,IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),-(H104-C104*0.5),C104-H104)),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),"减半清仓",IF(H104&gt;C104,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">
@@ -15509,11 +15493,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,-H5,IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),-(H5-C5*0.5),C5-H5)),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),"减半清仓",IF(H5&gt;C5,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -15555,11 +15539,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,-H6,IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),-(H6-C6*0.5),C6-H6)),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),"减半清仓",IF(H6&gt;C6,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -15601,11 +15585,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,-H7,IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),-(H7-C7*0.5),C7-H7)),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),"减半清仓",IF(H7&gt;C7,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -15647,11 +15631,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,-H8,IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),-(H8-C8*0.5),C8-H8)),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),"减半清仓",IF(H8&gt;C8,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -15693,11 +15677,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,-H9,IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),-(H9-C9*0.5),C9-H9)),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),"减半清仓",IF(H9&gt;C9,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -15739,11 +15723,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,-H10,IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),-(H10-C10*0.5),C10-H10)),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),"减半清仓",IF(H10&gt;C10,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -15785,11 +15769,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,-H11,IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),-(H11-C11*0.5),C11-H11)),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),"减半清仓",IF(H11&gt;C11,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -15831,11 +15815,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,-H12,IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),-(H12-C12*0.5),C12-H12)),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),"减半清仓",IF(H12&gt;C12,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -15877,11 +15861,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,-H13,IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),-(H13-C13*0.5),C13-H13)),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),"减半清仓",IF(H13&gt;C13,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -15923,11 +15907,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,-H14,IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),-(H14-C14*0.5),C14-H14)),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),"减半清仓",IF(H14&gt;C14,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -15969,11 +15953,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,-H15,IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),-(H15-C15*0.5),C15-H15)),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),"减半清仓",IF(H15&gt;C15,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -16015,11 +15999,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,-H16,IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),-(H16-C16*0.5),C16-H16)),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),"减半清仓",IF(H16&gt;C16,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -16061,11 +16045,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,-H17,IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),-(H17-C17*0.5),C17-H17)),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),"减半清仓",IF(H17&gt;C17,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -16107,11 +16091,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,-H18,IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),-(H18-C18*0.5),C18-H18)),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),"减半清仓",IF(H18&gt;C18,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -16153,11 +16137,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,-H19,IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),-(H19-C19*0.5),C19-H19)),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),"减半清仓",IF(H19&gt;C19,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -16199,11 +16183,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,-H20,IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),-(H20-C20*0.5),C20-H20)),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),"减半清仓",IF(H20&gt;C20,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -16245,11 +16229,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,-H21,IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),-(H21-C21*0.5),C21-H21)),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),"减半清仓",IF(H21&gt;C21,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -16291,11 +16275,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,-H22,IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),-(H22-C22*0.5),C22-H22)),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),"减半清仓",IF(H22&gt;C22,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -16337,11 +16321,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,-H23,IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),-(H23-C23*0.5),C23-H23)),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),"减半清仓",IF(H23&gt;C23,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -16383,11 +16367,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,-H24,IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),-(H24-C24*0.5),C24-H24)),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),"减半清仓",IF(H24&gt;C24,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -16429,11 +16413,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,-H25,IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),-(H25-C25*0.5),C25-H25)),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),"减半清仓",IF(H25&gt;C25,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -16475,11 +16459,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,-H26,IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),-(H26-C26*0.5),C26-H26)),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),"减半清仓",IF(H26&gt;C26,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -16521,11 +16505,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,-H27,IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),-(H27-C27*0.5),C27-H27)),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),"减半清仓",IF(H27&gt;C27,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -16567,11 +16551,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,-H28,IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),-(H28-C28*0.5),C28-H28)),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),"减半清仓",IF(H28&gt;C28,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -16613,11 +16597,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,-H29,IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),-(H29-C29*0.5),C29-H29)),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),"减半清仓",IF(H29&gt;C29,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -16659,11 +16643,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,-H30,IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),-(H30-C30*0.5),C30-H30)),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),"减半清仓",IF(H30&gt;C30,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -16705,11 +16689,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,-H31,IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),-(H31-C31*0.5),C31-H31)),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),"减半清仓",IF(H31&gt;C31,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -16751,11 +16735,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,-H32,IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),-(H32-C32*0.5),C32-H32)),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),"减半清仓",IF(H32&gt;C32,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -16797,11 +16781,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,-H33,IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),-(H33-C33*0.5),C33-H33)),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),"减半清仓",IF(H33&gt;C33,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -16843,11 +16827,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,-H34,IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),-(H34-C34*0.5),C34-H34)),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),"减半清仓",IF(H34&gt;C34,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -16889,11 +16873,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,-H35,IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),-(H35-C35*0.5),C35-H35)),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),"减半清仓",IF(H35&gt;C35,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -16935,11 +16919,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,-H36,IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),-(H36-C36*0.5),C36-H36)),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),"减半清仓",IF(H36&gt;C36,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -16981,11 +16965,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,-H37,IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),-(H37-C37*0.5),C37-H37)),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),"减半清仓",IF(H37&gt;C37,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -17027,11 +17011,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,-H38,IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),-(H38-C38*0.5),C38-H38)),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),"减半清仓",IF(H38&gt;C38,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -17073,11 +17057,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,-H39,IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),-(H39-C39*0.5),C39-H39)),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),"减半清仓",IF(H39&gt;C39,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -17119,11 +17103,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,-H40,IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),-(H40-C40*0.5),C40-H40)),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),"减半清仓",IF(H40&gt;C40,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -17165,11 +17149,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,-H41,IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),-(H41-C41*0.5),C41-H41)),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),"减半清仓",IF(H41&gt;C41,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -17211,11 +17195,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,-H42,IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),-(H42-C42*0.5),C42-H42)),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),"减半清仓",IF(H42&gt;C42,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -17257,11 +17241,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,-H43,IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),-(H43-C43*0.5),C43-H43)),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),"减半清仓",IF(H43&gt;C43,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -17303,11 +17287,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,-H44,IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),-(H44-C44*0.5),C44-H44)),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),"减半清仓",IF(H44&gt;C44,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -17349,11 +17333,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,-H45,IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),-(H45-C45*0.5),C45-H45)),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),"减半清仓",IF(H45&gt;C45,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -17395,11 +17379,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,-H46,IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),-(H46-C46*0.5),C46-H46)),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),"减半清仓",IF(H46&gt;C46,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -17441,11 +17425,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,-H47,IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),-(H47-C47*0.5),C47-H47)),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),"减半清仓",IF(H47&gt;C47,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -17487,11 +17471,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,-H48,IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),-(H48-C48*0.5),C48-H48)),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),"减半清仓",IF(H48&gt;C48,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -17533,11 +17517,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,-H49,IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),-(H49-C49*0.5),C49-H49)),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),"减半清仓",IF(H49&gt;C49,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -17579,11 +17563,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,-H50,IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),-(H50-C50*0.5),C50-H50)),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),"减半清仓",IF(H50&gt;C50,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -17625,11 +17609,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,-H51,IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),-(H51-C51*0.5),C51-H51)),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),"减半清仓",IF(H51&gt;C51,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -17671,11 +17655,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,-H52,IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),-(H52-C52*0.5),C52-H52)),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),"减半清仓",IF(H52&gt;C52,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -17717,11 +17701,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,-H53,IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),-(H53-C53*0.5),C53-H53)),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),"减半清仓",IF(H53&gt;C53,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -17763,11 +17747,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,-H54,IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),-(H54-C54*0.5),C54-H54)),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),"减半清仓",IF(H54&gt;C54,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -17809,11 +17793,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,-H55,IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),-(H55-C55*0.5),C55-H55)),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),"减半清仓",IF(H55&gt;C55,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -17855,11 +17839,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,-H56,IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),-(H56-C56*0.5),C56-H56)),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),"减半清仓",IF(H56&gt;C56,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -17901,11 +17885,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,-H57,IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),-(H57-C57*0.5),C57-H57)),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),"减半清仓",IF(H57&gt;C57,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -17947,11 +17931,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,-H58,IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),-(H58-C58*0.5),C58-H58)),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),"减半清仓",IF(H58&gt;C58,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -17993,11 +17977,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,-H59,IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),-(H59-C59*0.5),C59-H59)),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),"减半清仓",IF(H59&gt;C59,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -18039,11 +18023,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,-H60,IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),-(H60-C60*0.5),C60-H60)),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),"减半清仓",IF(H60&gt;C60,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -18085,11 +18069,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,-H61,IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),-(H61-C61*0.5),C61-H61)),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),"减半清仓",IF(H61&gt;C61,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -18131,11 +18115,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,-H62,IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),-(H62-C62*0.5),C62-H62)),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),"减半清仓",IF(H62&gt;C62,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -18177,11 +18161,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,-H63,IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),-(H63-C63*0.5),C63-H63)),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),"减半清仓",IF(H63&gt;C63,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -18223,11 +18207,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,-H64,IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),-(H64-C64*0.5),C64-H64)),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),"减半清仓",IF(H64&gt;C64,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -18269,11 +18253,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,-H65,IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),-(H65-C65*0.5),C65-H65)),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),"减半清仓",IF(H65&gt;C65,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -18315,11 +18299,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,-H66,IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),-(H66-C66*0.5),C66-H66)),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),"减半清仓",IF(H66&gt;C66,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -18361,11 +18345,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,-H67,IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),-(H67-C67*0.5),C67-H67)),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),"减半清仓",IF(H67&gt;C67,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -18407,11 +18391,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,-H68,IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),-(H68-C68*0.5),C68-H68)),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),"减半清仓",IF(H68&gt;C68,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -18453,11 +18437,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,-H69,IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),-(H69-C69*0.5),C69-H69)),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),"减半清仓",IF(H69&gt;C69,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -18499,11 +18483,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,-H70,IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),-(H70-C70*0.5),C70-H70)),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),"减半清仓",IF(H70&gt;C70,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -18545,11 +18529,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,-H71,IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),-(H71-C71*0.5),C71-H71)),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),"减半清仓",IF(H71&gt;C71,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -18591,11 +18575,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,-H72,IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),-(H72-C72*0.5),C72-H72)),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),"减半清仓",IF(H72&gt;C72,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -18637,11 +18621,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,-H73,IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),-(H73-C73*0.5),C73-H73)),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),"减半清仓",IF(H73&gt;C73,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -18683,11 +18667,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,-H74,IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),-(H74-C74*0.5),C74-H74)),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),"减半清仓",IF(H74&gt;C74,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -18729,11 +18713,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,-H75,IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),-(H75-C75*0.5),C75-H75)),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),"减半清仓",IF(H75&gt;C75,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -18775,11 +18759,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,-H76,IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),-(H76-C76*0.5),C76-H76)),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),"减半清仓",IF(H76&gt;C76,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -18821,11 +18805,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,-H77,IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),-(H77-C77*0.5),C77-H77)),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),"减半清仓",IF(H77&gt;C77,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -18867,11 +18851,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,-H78,IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),-(H78-C78*0.5),C78-H78)),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),"减半清仓",IF(H78&gt;C78,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -18913,11 +18897,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,-H79,IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),-(H79-C79*0.5),C79-H79)),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),"减半清仓",IF(H79&gt;C79,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -18959,11 +18943,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,-H80,IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),-(H80-C80*0.5),C80-H80)),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),"减半清仓",IF(H80&gt;C80,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -19005,11 +18989,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,-H81,IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),-(H81-C81*0.5),C81-H81)),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),"减半清仓",IF(H81&gt;C81,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -19051,11 +19035,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,-H82,IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),-(H82-C82*0.5),C82-H82)),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),"减半清仓",IF(H82&gt;C82,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -19097,11 +19081,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,-H83,IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),-(H83-C83*0.5),C83-H83)),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),"减半清仓",IF(H83&gt;C83,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -19143,11 +19127,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,-H84,IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),-(H84-C84*0.5),C84-H84)),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),"减半清仓",IF(H84&gt;C84,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -19189,11 +19173,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,-H85,IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),-(H85-C85*0.5),C85-H85)),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),"减半清仓",IF(H85&gt;C85,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -19235,11 +19219,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,-H86,IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),-(H86-C86*0.5),C86-H86)),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),"减半清仓",IF(H86&gt;C86,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -19281,11 +19265,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,-H87,IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),-(H87-C87*0.5),C87-H87)),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),"减半清仓",IF(H87&gt;C87,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -19327,11 +19311,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,-H88,IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),-(H88-C88*0.5),C88-H88)),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),"减半清仓",IF(H88&gt;C88,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -19373,11 +19357,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,-H89,IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),-(H89-C89*0.5),C89-H89)),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),"减半清仓",IF(H89&gt;C89,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -19419,11 +19403,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,-H90,IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),-(H90-C90*0.5),C90-H90)),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),"减半清仓",IF(H90&gt;C90,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -19465,11 +19449,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,-H91,IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),-(H91-C91*0.5),C91-H91)),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),"减半清仓",IF(H91&gt;C91,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -19511,11 +19495,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,-H92,IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),-(H92-C92*0.5),C92-H92)),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),"减半清仓",IF(H92&gt;C92,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -19557,11 +19541,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,-H93,IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),-(H93-C93*0.5),C93-H93)),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),"减半清仓",IF(H93&gt;C93,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -19603,11 +19587,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,-H94,IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),-(H94-C94*0.5),C94-H94)),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),"减半清仓",IF(H94&gt;C94,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -19649,11 +19633,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,-H95,IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),-(H95-C95*0.5),C95-H95)),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),"减半清仓",IF(H95&gt;C95,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -19695,11 +19679,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,-H96,IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),-(H96-C96*0.5),C96-H96)),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),"减半清仓",IF(H96&gt;C96,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -19741,11 +19725,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,-H97,IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),-(H97-C97*0.5),C97-H97)),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),"减半清仓",IF(H97&gt;C97,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -19787,11 +19771,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,-H98,IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),-(H98-C98*0.5),C98-H98)),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),"减半清仓",IF(H98&gt;C98,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -19833,11 +19817,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,-H99,IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),-(H99-C99*0.5),C99-H99)),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),"减半清仓",IF(H99&gt;C99,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -19879,11 +19863,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,-H100,IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),-(H100-C100*0.5),C100-H100)),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),"减半清仓",IF(H100&gt;C100,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -19925,11 +19909,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,-H101,IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),-(H101-C101*0.5),C101-H101)),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),"减半清仓",IF(H101&gt;C101,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -19971,11 +19955,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,-H102,IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),-(H102-C102*0.5),C102-H102)),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),"减半清仓",IF(H102&gt;C102,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -20017,11 +20001,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,-H103,IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),-(H103-C103*0.5),C103-H103)),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),"减半清仓",IF(H103&gt;C103,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -20063,11 +20047,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,-H104,IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),-(H104-C104*0.5),C104-H104)),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),"减半清仓",IF(H104&gt;C104,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">
@@ -20286,11 +20270,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,-H5,IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),-(H5-C5*0.5),C5-H5)),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F5&gt;=参数配置!$C$12,H5&gt;C5*0.5),"减半清仓",IF(H5&gt;C5,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -20332,11 +20316,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,-H6,IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),-(H6-C6*0.5),C6-H6)),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F6&gt;=参数配置!$C$12,H6&gt;C6*0.5),"减半清仓",IF(H6&gt;C6,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -20378,11 +20362,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,-H7,IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),-(H7-C7*0.5),C7-H7)),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F7&gt;=参数配置!$C$12,H7&gt;C7*0.5),"减半清仓",IF(H7&gt;C7,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -20424,11 +20408,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,-H8,IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),-(H8-C8*0.5),C8-H8)),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F8&gt;=参数配置!$C$12,H8&gt;C8*0.5),"减半清仓",IF(H8&gt;C8,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -20470,11 +20454,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,-H9,IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),-(H9-C9*0.5),C9-H9)),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F9&gt;=参数配置!$C$12,H9&gt;C9*0.5),"减半清仓",IF(H9&gt;C9,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -20516,11 +20500,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,-H10,IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),-(H10-C10*0.5),C10-H10)),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F10&gt;=参数配置!$C$12,H10&gt;C10*0.5),"减半清仓",IF(H10&gt;C10,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -20562,11 +20546,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,-H11,IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),-(H11-C11*0.5),C11-H11)),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F11&gt;=参数配置!$C$12,H11&gt;C11*0.5),"减半清仓",IF(H11&gt;C11,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -20608,11 +20592,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,-H12,IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),-(H12-C12*0.5),C12-H12)),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F12&gt;=参数配置!$C$12,H12&gt;C12*0.5),"减半清仓",IF(H12&gt;C12,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -20654,11 +20638,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,-H13,IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),-(H13-C13*0.5),C13-H13)),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F13&gt;=参数配置!$C$12,H13&gt;C13*0.5),"减半清仓",IF(H13&gt;C13,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -20700,11 +20684,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,-H14,IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),-(H14-C14*0.5),C14-H14)),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F14&gt;=参数配置!$C$12,H14&gt;C14*0.5),"减半清仓",IF(H14&gt;C14,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -20746,11 +20730,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,-H15,IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),-(H15-C15*0.5),C15-H15)),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F15&gt;=参数配置!$C$12,H15&gt;C15*0.5),"减半清仓",IF(H15&gt;C15,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -20792,11 +20776,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,-H16,IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),-(H16-C16*0.5),C16-H16)),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F16&gt;=参数配置!$C$12,H16&gt;C16*0.5),"减半清仓",IF(H16&gt;C16,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -20838,11 +20822,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,-H17,IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),-(H17-C17*0.5),C17-H17)),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F17&gt;=参数配置!$C$12,H17&gt;C17*0.5),"减半清仓",IF(H17&gt;C17,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -20884,11 +20868,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,-H18,IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),-(H18-C18*0.5),C18-H18)),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F18&gt;=参数配置!$C$12,H18&gt;C18*0.5),"减半清仓",IF(H18&gt;C18,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -20930,11 +20914,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,-H19,IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),-(H19-C19*0.5),C19-H19)),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F19&gt;=参数配置!$C$12,H19&gt;C19*0.5),"减半清仓",IF(H19&gt;C19,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -20976,11 +20960,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,-H20,IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),-(H20-C20*0.5),C20-H20)),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F20&gt;=参数配置!$C$12,H20&gt;C20*0.5),"减半清仓",IF(H20&gt;C20,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -21022,11 +21006,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,-H21,IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),-(H21-C21*0.5),C21-H21)),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F21&gt;=参数配置!$C$12,H21&gt;C21*0.5),"减半清仓",IF(H21&gt;C21,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -21068,11 +21052,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,-H22,IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),-(H22-C22*0.5),C22-H22)),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F22&gt;=参数配置!$C$12,H22&gt;C22*0.5),"减半清仓",IF(H22&gt;C22,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -21114,11 +21098,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,-H23,IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),-(H23-C23*0.5),C23-H23)),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F23&gt;=参数配置!$C$12,H23&gt;C23*0.5),"减半清仓",IF(H23&gt;C23,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -21160,11 +21144,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,-H24,IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),-(H24-C24*0.5),C24-H24)),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F24&gt;=参数配置!$C$12,H24&gt;C24*0.5),"减半清仓",IF(H24&gt;C24,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -21206,11 +21190,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,-H25,IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),-(H25-C25*0.5),C25-H25)),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F25&gt;=参数配置!$C$12,H25&gt;C25*0.5),"减半清仓",IF(H25&gt;C25,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -21252,11 +21236,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,-H26,IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),-(H26-C26*0.5),C26-H26)),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F26&gt;=参数配置!$C$12,H26&gt;C26*0.5),"减半清仓",IF(H26&gt;C26,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -21298,11 +21282,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,-H27,IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),-(H27-C27*0.5),C27-H27)),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F27&gt;=参数配置!$C$12,H27&gt;C27*0.5),"减半清仓",IF(H27&gt;C27,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -21344,11 +21328,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,-H28,IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),-(H28-C28*0.5),C28-H28)),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F28&gt;=参数配置!$C$12,H28&gt;C28*0.5),"减半清仓",IF(H28&gt;C28,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -21390,11 +21374,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,-H29,IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),-(H29-C29*0.5),C29-H29)),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F29&gt;=参数配置!$C$12,H29&gt;C29*0.5),"减半清仓",IF(H29&gt;C29,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -21436,11 +21420,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,-H30,IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),-(H30-C30*0.5),C30-H30)),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F30&gt;=参数配置!$C$12,H30&gt;C30*0.5),"减半清仓",IF(H30&gt;C30,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -21482,11 +21466,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,-H31,IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),-(H31-C31*0.5),C31-H31)),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F31&gt;=参数配置!$C$12,H31&gt;C31*0.5),"减半清仓",IF(H31&gt;C31,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -21528,11 +21512,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,-H32,IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),-(H32-C32*0.5),C32-H32)),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F32&gt;=参数配置!$C$12,H32&gt;C32*0.5),"减半清仓",IF(H32&gt;C32,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -21574,11 +21558,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,-H33,IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),-(H33-C33*0.5),C33-H33)),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F33&gt;=参数配置!$C$12,H33&gt;C33*0.5),"减半清仓",IF(H33&gt;C33,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -21620,11 +21604,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,-H34,IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),-(H34-C34*0.5),C34-H34)),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F34&gt;=参数配置!$C$12,H34&gt;C34*0.5),"减半清仓",IF(H34&gt;C34,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -21666,11 +21650,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,-H35,IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),-(H35-C35*0.5),C35-H35)),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F35&gt;=参数配置!$C$12,H35&gt;C35*0.5),"减半清仓",IF(H35&gt;C35,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -21712,11 +21696,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,-H36,IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),-(H36-C36*0.5),C36-H36)),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F36&gt;=参数配置!$C$12,H36&gt;C36*0.5),"减半清仓",IF(H36&gt;C36,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -21758,11 +21742,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,-H37,IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),-(H37-C37*0.5),C37-H37)),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F37&gt;=参数配置!$C$12,H37&gt;C37*0.5),"减半清仓",IF(H37&gt;C37,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -21804,11 +21788,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,-H38,IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),-(H38-C38*0.5),C38-H38)),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F38&gt;=参数配置!$C$12,H38&gt;C38*0.5),"减半清仓",IF(H38&gt;C38,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -21850,11 +21834,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,-H39,IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),-(H39-C39*0.5),C39-H39)),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F39&gt;=参数配置!$C$12,H39&gt;C39*0.5),"减半清仓",IF(H39&gt;C39,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -21896,11 +21880,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,-H40,IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),-(H40-C40*0.5),C40-H40)),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F40&gt;=参数配置!$C$12,H40&gt;C40*0.5),"减半清仓",IF(H40&gt;C40,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -21942,11 +21926,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,-H41,IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),-(H41-C41*0.5),C41-H41)),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F41&gt;=参数配置!$C$12,H41&gt;C41*0.5),"减半清仓",IF(H41&gt;C41,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -21988,11 +21972,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,-H42,IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),-(H42-C42*0.5),C42-H42)),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F42&gt;=参数配置!$C$12,H42&gt;C42*0.5),"减半清仓",IF(H42&gt;C42,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -22034,11 +22018,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,-H43,IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),-(H43-C43*0.5),C43-H43)),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F43&gt;=参数配置!$C$12,H43&gt;C43*0.5),"减半清仓",IF(H43&gt;C43,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -22080,11 +22064,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,-H44,IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),-(H44-C44*0.5),C44-H44)),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F44&gt;=参数配置!$C$12,H44&gt;C44*0.5),"减半清仓",IF(H44&gt;C44,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -22126,11 +22110,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,-H45,IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),-(H45-C45*0.5),C45-H45)),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F45&gt;=参数配置!$C$12,H45&gt;C45*0.5),"减半清仓",IF(H45&gt;C45,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -22172,11 +22156,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,-H46,IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),-(H46-C46*0.5),C46-H46)),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F46&gt;=参数配置!$C$12,H46&gt;C46*0.5),"减半清仓",IF(H46&gt;C46,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -22218,11 +22202,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,-H47,IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),-(H47-C47*0.5),C47-H47)),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F47&gt;=参数配置!$C$12,H47&gt;C47*0.5),"减半清仓",IF(H47&gt;C47,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -22264,11 +22248,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,-H48,IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),-(H48-C48*0.5),C48-H48)),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F48&gt;=参数配置!$C$12,H48&gt;C48*0.5),"减半清仓",IF(H48&gt;C48,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -22310,11 +22294,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,-H49,IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),-(H49-C49*0.5),C49-H49)),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F49&gt;=参数配置!$C$12,H49&gt;C49*0.5),"减半清仓",IF(H49&gt;C49,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -22356,11 +22340,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,-H50,IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),-(H50-C50*0.5),C50-H50)),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F50&gt;=参数配置!$C$12,H50&gt;C50*0.5),"减半清仓",IF(H50&gt;C50,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -22402,11 +22386,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,-H51,IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),-(H51-C51*0.5),C51-H51)),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F51&gt;=参数配置!$C$12,H51&gt;C51*0.5),"减半清仓",IF(H51&gt;C51,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -22448,11 +22432,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,-H52,IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),-(H52-C52*0.5),C52-H52)),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F52&gt;=参数配置!$C$12,H52&gt;C52*0.5),"减半清仓",IF(H52&gt;C52,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -22494,11 +22478,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,-H53,IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),-(H53-C53*0.5),C53-H53)),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F53&gt;=参数配置!$C$12,H53&gt;C53*0.5),"减半清仓",IF(H53&gt;C53,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -22540,11 +22524,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,-H54,IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),-(H54-C54*0.5),C54-H54)),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F54&gt;=参数配置!$C$12,H54&gt;C54*0.5),"减半清仓",IF(H54&gt;C54,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -22586,11 +22570,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,-H55,IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),-(H55-C55*0.5),C55-H55)),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F55&gt;=参数配置!$C$12,H55&gt;C55*0.5),"减半清仓",IF(H55&gt;C55,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -22632,11 +22616,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,-H56,IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),-(H56-C56*0.5),C56-H56)),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F56&gt;=参数配置!$C$12,H56&gt;C56*0.5),"减半清仓",IF(H56&gt;C56,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -22678,11 +22662,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,-H57,IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),-(H57-C57*0.5),C57-H57)),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F57&gt;=参数配置!$C$12,H57&gt;C57*0.5),"减半清仓",IF(H57&gt;C57,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -22724,11 +22708,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,-H58,IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),-(H58-C58*0.5),C58-H58)),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F58&gt;=参数配置!$C$12,H58&gt;C58*0.5),"减半清仓",IF(H58&gt;C58,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -22770,11 +22754,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,-H59,IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),-(H59-C59*0.5),C59-H59)),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F59&gt;=参数配置!$C$12,H59&gt;C59*0.5),"减半清仓",IF(H59&gt;C59,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -22816,11 +22800,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,-H60,IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),-(H60-C60*0.5),C60-H60)),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F60&gt;=参数配置!$C$12,H60&gt;C60*0.5),"减半清仓",IF(H60&gt;C60,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -22862,11 +22846,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,-H61,IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),-(H61-C61*0.5),C61-H61)),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F61&gt;=参数配置!$C$12,H61&gt;C61*0.5),"减半清仓",IF(H61&gt;C61,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -22908,11 +22892,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,-H62,IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),-(H62-C62*0.5),C62-H62)),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F62&gt;=参数配置!$C$12,H62&gt;C62*0.5),"减半清仓",IF(H62&gt;C62,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -22954,11 +22938,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,-H63,IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),-(H63-C63*0.5),C63-H63)),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F63&gt;=参数配置!$C$12,H63&gt;C63*0.5),"减半清仓",IF(H63&gt;C63,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -23000,11 +22984,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,-H64,IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),-(H64-C64*0.5),C64-H64)),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F64&gt;=参数配置!$C$12,H64&gt;C64*0.5),"减半清仓",IF(H64&gt;C64,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -23046,11 +23030,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,-H65,IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),-(H65-C65*0.5),C65-H65)),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F65&gt;=参数配置!$C$12,H65&gt;C65*0.5),"减半清仓",IF(H65&gt;C65,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -23092,11 +23076,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,-H66,IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),-(H66-C66*0.5),C66-H66)),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F66&gt;=参数配置!$C$12,H66&gt;C66*0.5),"减半清仓",IF(H66&gt;C66,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -23138,11 +23122,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,-H67,IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),-(H67-C67*0.5),C67-H67)),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F67&gt;=参数配置!$C$12,H67&gt;C67*0.5),"减半清仓",IF(H67&gt;C67,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -23184,11 +23168,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,-H68,IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),-(H68-C68*0.5),C68-H68)),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F68&gt;=参数配置!$C$12,H68&gt;C68*0.5),"减半清仓",IF(H68&gt;C68,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -23230,11 +23214,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,-H69,IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),-(H69-C69*0.5),C69-H69)),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F69&gt;=参数配置!$C$12,H69&gt;C69*0.5),"减半清仓",IF(H69&gt;C69,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -23276,11 +23260,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,-H70,IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),-(H70-C70*0.5),C70-H70)),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F70&gt;=参数配置!$C$12,H70&gt;C70*0.5),"减半清仓",IF(H70&gt;C70,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -23322,11 +23306,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,-H71,IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),-(H71-C71*0.5),C71-H71)),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F71&gt;=参数配置!$C$12,H71&gt;C71*0.5),"减半清仓",IF(H71&gt;C71,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -23368,11 +23352,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,-H72,IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),-(H72-C72*0.5),C72-H72)),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F72&gt;=参数配置!$C$12,H72&gt;C72*0.5),"减半清仓",IF(H72&gt;C72,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -23414,11 +23398,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,-H73,IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),-(H73-C73*0.5),C73-H73)),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F73&gt;=参数配置!$C$12,H73&gt;C73*0.5),"减半清仓",IF(H73&gt;C73,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -23460,11 +23444,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,-H74,IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),-(H74-C74*0.5),C74-H74)),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F74&gt;=参数配置!$C$12,H74&gt;C74*0.5),"减半清仓",IF(H74&gt;C74,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -23506,11 +23490,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,-H75,IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),-(H75-C75*0.5),C75-H75)),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F75&gt;=参数配置!$C$12,H75&gt;C75*0.5),"减半清仓",IF(H75&gt;C75,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -23552,11 +23536,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,-H76,IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),-(H76-C76*0.5),C76-H76)),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F76&gt;=参数配置!$C$12,H76&gt;C76*0.5),"减半清仓",IF(H76&gt;C76,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -23598,11 +23582,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,-H77,IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),-(H77-C77*0.5),C77-H77)),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F77&gt;=参数配置!$C$12,H77&gt;C77*0.5),"减半清仓",IF(H77&gt;C77,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -23644,11 +23628,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,-H78,IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),-(H78-C78*0.5),C78-H78)),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F78&gt;=参数配置!$C$12,H78&gt;C78*0.5),"减半清仓",IF(H78&gt;C78,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -23690,11 +23674,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,-H79,IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),-(H79-C79*0.5),C79-H79)),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F79&gt;=参数配置!$C$12,H79&gt;C79*0.5),"减半清仓",IF(H79&gt;C79,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -23736,11 +23720,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,-H80,IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),-(H80-C80*0.5),C80-H80)),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F80&gt;=参数配置!$C$12,H80&gt;C80*0.5),"减半清仓",IF(H80&gt;C80,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -23782,11 +23766,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,-H81,IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),-(H81-C81*0.5),C81-H81)),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F81&gt;=参数配置!$C$12,H81&gt;C81*0.5),"减半清仓",IF(H81&gt;C81,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -23828,11 +23812,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,-H82,IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),-(H82-C82*0.5),C82-H82)),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F82&gt;=参数配置!$C$12,H82&gt;C82*0.5),"减半清仓",IF(H82&gt;C82,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -23874,11 +23858,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,-H83,IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),-(H83-C83*0.5),C83-H83)),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F83&gt;=参数配置!$C$12,H83&gt;C83*0.5),"减半清仓",IF(H83&gt;C83,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -23920,11 +23904,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,-H84,IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),-(H84-C84*0.5),C84-H84)),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F84&gt;=参数配置!$C$12,H84&gt;C84*0.5),"减半清仓",IF(H84&gt;C84,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -23966,11 +23950,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,-H85,IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),-(H85-C85*0.5),C85-H85)),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F85&gt;=参数配置!$C$12,H85&gt;C85*0.5),"减半清仓",IF(H85&gt;C85,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -24012,11 +23996,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,-H86,IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),-(H86-C86*0.5),C86-H86)),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F86&gt;=参数配置!$C$12,H86&gt;C86*0.5),"减半清仓",IF(H86&gt;C86,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -24058,11 +24042,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,-H87,IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),-(H87-C87*0.5),C87-H87)),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F87&gt;=参数配置!$C$12,H87&gt;C87*0.5),"减半清仓",IF(H87&gt;C87,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -24104,11 +24088,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,-H88,IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),-(H88-C88*0.5),C88-H88)),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F88&gt;=参数配置!$C$12,H88&gt;C88*0.5),"减半清仓",IF(H88&gt;C88,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -24150,11 +24134,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,-H89,IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),-(H89-C89*0.5),C89-H89)),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F89&gt;=参数配置!$C$12,H89&gt;C89*0.5),"减半清仓",IF(H89&gt;C89,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -24196,11 +24180,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,-H90,IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),-(H90-C90*0.5),C90-H90)),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F90&gt;=参数配置!$C$12,H90&gt;C90*0.5),"减半清仓",IF(H90&gt;C90,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -24242,11 +24226,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,-H91,IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),-(H91-C91*0.5),C91-H91)),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F91&gt;=参数配置!$C$12,H91&gt;C91*0.5),"减半清仓",IF(H91&gt;C91,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -24288,11 +24272,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,-H92,IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),-(H92-C92*0.5),C92-H92)),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F92&gt;=参数配置!$C$12,H92&gt;C92*0.5),"减半清仓",IF(H92&gt;C92,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -24334,11 +24318,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,-H93,IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),-(H93-C93*0.5),C93-H93)),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F93&gt;=参数配置!$C$12,H93&gt;C93*0.5),"减半清仓",IF(H93&gt;C93,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -24380,11 +24364,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,-H94,IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),-(H94-C94*0.5),C94-H94)),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F94&gt;=参数配置!$C$12,H94&gt;C94*0.5),"减半清仓",IF(H94&gt;C94,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -24426,11 +24410,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,-H95,IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),-(H95-C95*0.5),C95-H95)),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F95&gt;=参数配置!$C$12,H95&gt;C95*0.5),"减半清仓",IF(H95&gt;C95,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -24472,11 +24456,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,-H96,IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),-(H96-C96*0.5),C96-H96)),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F96&gt;=参数配置!$C$12,H96&gt;C96*0.5),"减半清仓",IF(H96&gt;C96,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -24518,11 +24502,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,-H97,IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),-(H97-C97*0.5),C97-H97)),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F97&gt;=参数配置!$C$12,H97&gt;C97*0.5),"减半清仓",IF(H97&gt;C97,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -24564,11 +24548,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,-H98,IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),-(H98-C98*0.5),C98-H98)),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F98&gt;=参数配置!$C$12,H98&gt;C98*0.5),"减半清仓",IF(H98&gt;C98,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -24610,11 +24594,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,-H99,IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),-(H99-C99*0.5),C99-H99)),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F99&gt;=参数配置!$C$12,H99&gt;C99*0.5),"减半清仓",IF(H99&gt;C99,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -24656,11 +24640,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,-H100,IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),-(H100-C100*0.5),C100-H100)),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F100&gt;=参数配置!$C$12,H100&gt;C100*0.5),"减半清仓",IF(H100&gt;C100,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -24702,11 +24686,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,-H101,IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),-(H101-C101*0.5),C101-H101)),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F101&gt;=参数配置!$C$12,H101&gt;C101*0.5),"减半清仓",IF(H101&gt;C101,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -24748,11 +24732,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,-H102,IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),-(H102-C102*0.5),C102-H102)),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F102&gt;=参数配置!$C$12,H102&gt;C102*0.5),"减半清仓",IF(H102&gt;C102,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -24794,11 +24778,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,-H103,IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),-(H103-C103*0.5),C103-H103)),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F103&gt;=参数配置!$C$12,H103&gt;C103*0.5),"减半清仓",IF(H103&gt;C103,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -24840,11 +24824,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,-H104,IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),-(H104-C104*0.5),C104-H104)),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,"全仓清仓",IF(AND(F104&gt;=参数配置!$C$12,H104&gt;C104*0.5),"减半清仓",IF(H104&gt;C104,"卖出超额","正常定投"))),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -23,9 +23,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="+0%"/>
-    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="+0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="+0.00%;-0.00%;0.00%"/>
   </numFmts>
@@ -113,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -127,11 +127,32 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -176,19 +197,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +248,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1011,8 +1045,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="16" t="n"/>
+      <c r="A5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A5,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1033,7 +1073,9 @@
         <f>IFERROR(IF(M5="增量阶段",H5,SUMPRODUCT(MAX(C5,0),1)+SUMPRODUCT(MAX(D5,0),1)+SUMPRODUCT(MAX(E5,0),1)+SUMPRODUCT(MAX(F5,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H5" s="17" t="n"/>
+      <c r="H5" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I5" s="7">
         <f>IFERROR(MAX(-C5,0)+MAX(-D5,0)+MAX(-E5,0)+MAX(-F5,0),"")</f>
         <v/>
@@ -1057,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n"/>
-      <c r="B6" s="16" t="n"/>
+      <c r="B6" s="33" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A6,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1102,7 +1144,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n"/>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="33" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A7,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1147,7 +1189,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n"/>
-      <c r="B8" s="16" t="n"/>
+      <c r="B8" s="33" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A8,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1192,7 +1234,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n"/>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="33" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A9,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1237,7 +1279,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n"/>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="33" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A10,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1282,7 +1324,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n"/>
-      <c r="B11" s="16" t="n"/>
+      <c r="B11" s="33" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A11,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1327,7 +1369,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n"/>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="33" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A12,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1372,7 +1414,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="33" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A13,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1417,7 +1459,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n"/>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="33" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A14,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1462,7 +1504,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n"/>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="33" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A15,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1507,7 +1549,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n"/>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="33" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A16,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1552,7 +1594,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n"/>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="33" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A17,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1597,7 +1639,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n"/>
-      <c r="B18" s="16" t="n"/>
+      <c r="B18" s="33" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A18,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1642,7 +1684,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n"/>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="33" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A19,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1687,7 +1729,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n"/>
-      <c r="B20" s="16" t="n"/>
+      <c r="B20" s="33" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A20,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1732,7 +1774,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n"/>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="33" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A21,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1777,7 +1819,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n"/>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="33" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A22,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1822,7 +1864,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n"/>
-      <c r="B23" s="16" t="n"/>
+      <c r="B23" s="33" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A23,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1867,7 +1909,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n"/>
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="33" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A24,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1912,7 +1954,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n"/>
-      <c r="B25" s="16" t="n"/>
+      <c r="B25" s="33" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A25,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1957,7 +1999,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
-      <c r="B26" s="16" t="n"/>
+      <c r="B26" s="33" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A26,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2002,7 +2044,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n"/>
-      <c r="B27" s="16" t="n"/>
+      <c r="B27" s="33" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A27,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2047,7 +2089,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n"/>
-      <c r="B28" s="16" t="n"/>
+      <c r="B28" s="33" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A28,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2092,7 +2134,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="33" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A29,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2137,7 +2179,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
-      <c r="B30" s="16" t="n"/>
+      <c r="B30" s="33" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A30,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2182,7 +2224,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n"/>
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="33" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A31,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2227,7 +2269,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n"/>
-      <c r="B32" s="16" t="n"/>
+      <c r="B32" s="33" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A32,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2272,7 +2314,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n"/>
-      <c r="B33" s="16" t="n"/>
+      <c r="B33" s="33" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A33,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2317,7 +2359,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n"/>
-      <c r="B34" s="16" t="n"/>
+      <c r="B34" s="33" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A34,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2362,7 +2404,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n"/>
-      <c r="B35" s="16" t="n"/>
+      <c r="B35" s="33" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A35,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2407,7 +2449,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n"/>
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="33" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A36,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2452,7 +2494,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n"/>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="33" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A37,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2497,7 +2539,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n"/>
-      <c r="B38" s="16" t="n"/>
+      <c r="B38" s="33" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A38,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2542,7 +2584,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n"/>
-      <c r="B39" s="16" t="n"/>
+      <c r="B39" s="33" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A39,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2587,7 +2629,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n"/>
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="33" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A40,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2632,7 +2674,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n"/>
-      <c r="B41" s="16" t="n"/>
+      <c r="B41" s="33" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A41,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2677,7 +2719,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n"/>
-      <c r="B42" s="16" t="n"/>
+      <c r="B42" s="33" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A42,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2722,7 +2764,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n"/>
-      <c r="B43" s="16" t="n"/>
+      <c r="B43" s="33" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A43,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2767,7 +2809,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n"/>
-      <c r="B44" s="16" t="n"/>
+      <c r="B44" s="33" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A44,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2812,7 +2854,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n"/>
-      <c r="B45" s="16" t="n"/>
+      <c r="B45" s="33" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A45,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2857,7 +2899,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n"/>
-      <c r="B46" s="16" t="n"/>
+      <c r="B46" s="33" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A46,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2902,7 +2944,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n"/>
-      <c r="B47" s="16" t="n"/>
+      <c r="B47" s="33" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A47,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2947,7 +2989,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n"/>
-      <c r="B48" s="16" t="n"/>
+      <c r="B48" s="33" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A48,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -2992,7 +3034,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n"/>
-      <c r="B49" s="16" t="n"/>
+      <c r="B49" s="33" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A49,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3037,7 +3079,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n"/>
-      <c r="B50" s="16" t="n"/>
+      <c r="B50" s="33" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A50,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3082,7 +3124,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n"/>
-      <c r="B51" s="16" t="n"/>
+      <c r="B51" s="33" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A51,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3127,7 +3169,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n"/>
-      <c r="B52" s="16" t="n"/>
+      <c r="B52" s="33" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A52,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3172,7 +3214,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n"/>
-      <c r="B53" s="16" t="n"/>
+      <c r="B53" s="33" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A53,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3217,7 +3259,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n"/>
-      <c r="B54" s="16" t="n"/>
+      <c r="B54" s="33" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A54,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3262,7 +3304,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n"/>
-      <c r="B55" s="16" t="n"/>
+      <c r="B55" s="33" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A55,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3307,7 +3349,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n"/>
-      <c r="B56" s="16" t="n"/>
+      <c r="B56" s="33" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A56,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3352,7 +3394,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n"/>
-      <c r="B57" s="16" t="n"/>
+      <c r="B57" s="33" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A57,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3397,7 +3439,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n"/>
-      <c r="B58" s="16" t="n"/>
+      <c r="B58" s="33" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A58,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3442,7 +3484,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n"/>
-      <c r="B59" s="16" t="n"/>
+      <c r="B59" s="33" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A59,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3487,7 +3529,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n"/>
-      <c r="B60" s="16" t="n"/>
+      <c r="B60" s="33" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A60,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3532,7 +3574,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n"/>
-      <c r="B61" s="16" t="n"/>
+      <c r="B61" s="33" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A61,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3577,7 +3619,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n"/>
-      <c r="B62" s="16" t="n"/>
+      <c r="B62" s="33" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A62,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3622,7 +3664,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n"/>
-      <c r="B63" s="16" t="n"/>
+      <c r="B63" s="33" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A63,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3667,7 +3709,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n"/>
-      <c r="B64" s="16" t="n"/>
+      <c r="B64" s="33" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A64,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3712,7 +3754,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n"/>
-      <c r="B65" s="16" t="n"/>
+      <c r="B65" s="33" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A65,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3757,7 +3799,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n"/>
-      <c r="B66" s="16" t="n"/>
+      <c r="B66" s="33" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A66,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3802,7 +3844,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n"/>
-      <c r="B67" s="16" t="n"/>
+      <c r="B67" s="33" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A67,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3847,7 +3889,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n"/>
-      <c r="B68" s="16" t="n"/>
+      <c r="B68" s="33" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A68,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3892,7 +3934,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n"/>
-      <c r="B69" s="16" t="n"/>
+      <c r="B69" s="33" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A69,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3937,7 +3979,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n"/>
-      <c r="B70" s="16" t="n"/>
+      <c r="B70" s="33" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A70,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -3982,7 +4024,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n"/>
-      <c r="B71" s="16" t="n"/>
+      <c r="B71" s="33" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A71,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4027,7 +4069,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n"/>
-      <c r="B72" s="16" t="n"/>
+      <c r="B72" s="33" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A72,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4072,7 +4114,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n"/>
-      <c r="B73" s="16" t="n"/>
+      <c r="B73" s="33" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A73,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4117,7 +4159,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n"/>
-      <c r="B74" s="16" t="n"/>
+      <c r="B74" s="33" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A74,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4162,7 +4204,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n"/>
-      <c r="B75" s="16" t="n"/>
+      <c r="B75" s="33" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A75,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4207,7 +4249,7 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n"/>
-      <c r="B76" s="16" t="n"/>
+      <c r="B76" s="33" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A76,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4252,7 +4294,7 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n"/>
-      <c r="B77" s="16" t="n"/>
+      <c r="B77" s="33" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A77,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4297,7 +4339,7 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n"/>
-      <c r="B78" s="16" t="n"/>
+      <c r="B78" s="33" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A78,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4342,7 +4384,7 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n"/>
-      <c r="B79" s="16" t="n"/>
+      <c r="B79" s="33" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A79,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4387,7 +4429,7 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n"/>
-      <c r="B80" s="16" t="n"/>
+      <c r="B80" s="33" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A80,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4432,7 +4474,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n"/>
-      <c r="B81" s="16" t="n"/>
+      <c r="B81" s="33" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A81,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4477,7 +4519,7 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n"/>
-      <c r="B82" s="16" t="n"/>
+      <c r="B82" s="33" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A82,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4522,7 +4564,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n"/>
-      <c r="B83" s="16" t="n"/>
+      <c r="B83" s="33" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A83,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4567,7 +4609,7 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n"/>
-      <c r="B84" s="16" t="n"/>
+      <c r="B84" s="33" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A84,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4612,7 +4654,7 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n"/>
-      <c r="B85" s="16" t="n"/>
+      <c r="B85" s="33" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A85,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4657,7 +4699,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n"/>
-      <c r="B86" s="16" t="n"/>
+      <c r="B86" s="33" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A86,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4702,7 +4744,7 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n"/>
-      <c r="B87" s="16" t="n"/>
+      <c r="B87" s="33" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A87,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4747,7 +4789,7 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n"/>
-      <c r="B88" s="16" t="n"/>
+      <c r="B88" s="33" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A88,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4792,7 +4834,7 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n"/>
-      <c r="B89" s="16" t="n"/>
+      <c r="B89" s="33" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A89,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4837,7 +4879,7 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n"/>
-      <c r="B90" s="16" t="n"/>
+      <c r="B90" s="33" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A90,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4882,7 +4924,7 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n"/>
-      <c r="B91" s="16" t="n"/>
+      <c r="B91" s="33" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A91,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4927,7 +4969,7 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n"/>
-      <c r="B92" s="16" t="n"/>
+      <c r="B92" s="33" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A92,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -4972,7 +5014,7 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n"/>
-      <c r="B93" s="16" t="n"/>
+      <c r="B93" s="33" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A93,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5017,7 +5059,7 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n"/>
-      <c r="B94" s="16" t="n"/>
+      <c r="B94" s="33" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A94,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5062,7 +5104,7 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n"/>
-      <c r="B95" s="16" t="n"/>
+      <c r="B95" s="33" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A95,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5107,7 +5149,7 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n"/>
-      <c r="B96" s="16" t="n"/>
+      <c r="B96" s="33" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A96,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5152,7 +5194,7 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n"/>
-      <c r="B97" s="16" t="n"/>
+      <c r="B97" s="33" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A97,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5197,7 +5239,7 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n"/>
-      <c r="B98" s="16" t="n"/>
+      <c r="B98" s="33" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A98,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5242,7 +5284,7 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n"/>
-      <c r="B99" s="16" t="n"/>
+      <c r="B99" s="33" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A99,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5287,7 +5329,7 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n"/>
-      <c r="B100" s="16" t="n"/>
+      <c r="B100" s="33" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A100,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5332,7 +5374,7 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n"/>
-      <c r="B101" s="16" t="n"/>
+      <c r="B101" s="33" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A101,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5377,7 +5419,7 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n"/>
-      <c r="B102" s="16" t="n"/>
+      <c r="B102" s="33" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A102,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5422,7 +5464,7 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n"/>
-      <c r="B103" s="16" t="n"/>
+      <c r="B103" s="33" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A103,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5467,7 +5509,7 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n"/>
-      <c r="B104" s="16" t="n"/>
+      <c r="B104" s="33" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A104,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -5590,7 +5632,7 @@
       <c r="C5" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="34" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5608,7 +5650,7 @@
       <c r="C6" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="34" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5626,7 +5668,7 @@
       <c r="C7" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="34" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5644,7 +5686,7 @@
       <c r="C8" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="34" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -5659,7 +5701,7 @@
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="35">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
@@ -5693,7 +5735,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="36" t="n">
         <v>0.55</v>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -5724,6 +5766,7 @@
           <t>达到后切换为增量阶段，买卖均走储备金池</t>
         </is>
       </c>
+      <c r="E15" s="37" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -5740,6 +5783,7 @@
           <t>每期向储备金池注入的新增资金</t>
         </is>
       </c>
+      <c r="E16" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5921,19 +5965,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$5*(B5-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="D5" s="27" t="n">
+        <v>4.774</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>4.3435</v>
+      </c>
       <c r="F5" s="28">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="27" t="n"/>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -5950,8 +6006,12 @@
         <f>IFERROR(I5,"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="27" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>1432.2</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N5" s="31">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -5967,7 +6027,7 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$5*(B6-$S$3),"")</f>
@@ -6013,7 +6073,7 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="33" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$5*(B7-$S$3),"")</f>
@@ -6059,7 +6119,7 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="33" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$5*(B8-$S$3),"")</f>
@@ -6105,7 +6165,7 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="33" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$5*(B9-$S$3),"")</f>
@@ -6151,7 +6211,7 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="33" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$5*(B10-$S$3),"")</f>
@@ -6197,7 +6257,7 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="33" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$5*(B11-$S$3),"")</f>
@@ -6243,7 +6303,7 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="33" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$5*(B12-$S$3),"")</f>
@@ -6289,7 +6349,7 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="33" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$5*(B13-$S$3),"")</f>
@@ -6335,7 +6395,7 @@
       <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="33" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$5*(B14-$S$3),"")</f>
@@ -6381,7 +6441,7 @@
       <c r="Q14" s="32" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="33" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$5*(B15-$S$3),"")</f>
@@ -6427,7 +6487,7 @@
       <c r="Q15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="33" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$5*(B16-$S$3),"")</f>
@@ -6473,7 +6533,7 @@
       <c r="Q16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="33" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$5*(B17-$S$3),"")</f>
@@ -6519,7 +6579,7 @@
       <c r="Q17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="33" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$5*(B18-$S$3),"")</f>
@@ -6565,7 +6625,7 @@
       <c r="Q18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="33" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$5*(B19-$S$3),"")</f>
@@ -6611,7 +6671,7 @@
       <c r="Q19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="33" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$5*(B20-$S$3),"")</f>
@@ -6657,7 +6717,7 @@
       <c r="Q20" s="32" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="33" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$5*(B21-$S$3),"")</f>
@@ -6703,7 +6763,7 @@
       <c r="Q21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="33" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$5*(B22-$S$3),"")</f>
@@ -6749,7 +6809,7 @@
       <c r="Q22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="33" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$5*(B23-$S$3),"")</f>
@@ -6795,7 +6855,7 @@
       <c r="Q23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="33" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$5*(B24-$S$3),"")</f>
@@ -6841,7 +6901,7 @@
       <c r="Q24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="33" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$5*(B25-$S$3),"")</f>
@@ -6887,7 +6947,7 @@
       <c r="Q25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="33" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$5*(B26-$S$3),"")</f>
@@ -6933,7 +6993,7 @@
       <c r="Q26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="33" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$5*(B27-$S$3),"")</f>
@@ -6979,7 +7039,7 @@
       <c r="Q27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="33" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$5*(B28-$S$3),"")</f>
@@ -7025,7 +7085,7 @@
       <c r="Q28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="33" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$5*(B29-$S$3),"")</f>
@@ -7071,7 +7131,7 @@
       <c r="Q29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="33" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$5*(B30-$S$3),"")</f>
@@ -7117,7 +7177,7 @@
       <c r="Q30" s="32" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="33" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$5*(B31-$S$3),"")</f>
@@ -7163,7 +7223,7 @@
       <c r="Q31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="33" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$5*(B32-$S$3),"")</f>
@@ -7209,7 +7269,7 @@
       <c r="Q32" s="32" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="33" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$5*(B33-$S$3),"")</f>
@@ -7255,7 +7315,7 @@
       <c r="Q33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="33" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$5*(B34-$S$3),"")</f>
@@ -7301,7 +7361,7 @@
       <c r="Q34" s="32" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="33" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$5*(B35-$S$3),"")</f>
@@ -7347,7 +7407,7 @@
       <c r="Q35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="33" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$5*(B36-$S$3),"")</f>
@@ -7393,7 +7453,7 @@
       <c r="Q36" s="32" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="33" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$5*(B37-$S$3),"")</f>
@@ -7439,7 +7499,7 @@
       <c r="Q37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="33" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$5*(B38-$S$3),"")</f>
@@ -7485,7 +7545,7 @@
       <c r="Q38" s="32" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="33" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$5*(B39-$S$3),"")</f>
@@ -7531,7 +7591,7 @@
       <c r="Q39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="33" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$5*(B40-$S$3),"")</f>
@@ -7577,7 +7637,7 @@
       <c r="Q40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="33" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$5*(B41-$S$3),"")</f>
@@ -7623,7 +7683,7 @@
       <c r="Q41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="33" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$5*(B42-$S$3),"")</f>
@@ -7669,7 +7729,7 @@
       <c r="Q42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="33" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$5*(B43-$S$3),"")</f>
@@ -7715,7 +7775,7 @@
       <c r="Q43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="33" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$5*(B44-$S$3),"")</f>
@@ -7761,7 +7821,7 @@
       <c r="Q44" s="32" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="33" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$5*(B45-$S$3),"")</f>
@@ -7807,7 +7867,7 @@
       <c r="Q45" s="32" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="33" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$5*(B46-$S$3),"")</f>
@@ -7853,7 +7913,7 @@
       <c r="Q46" s="32" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="33" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$5*(B47-$S$3),"")</f>
@@ -7899,7 +7959,7 @@
       <c r="Q47" s="32" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="33" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$5*(B48-$S$3),"")</f>
@@ -7945,7 +8005,7 @@
       <c r="Q48" s="32" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="33" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$5*(B49-$S$3),"")</f>
@@ -7991,7 +8051,7 @@
       <c r="Q49" s="32" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="33" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$5*(B50-$S$3),"")</f>
@@ -8037,7 +8097,7 @@
       <c r="Q50" s="32" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="33" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$5*(B51-$S$3),"")</f>
@@ -8083,7 +8143,7 @@
       <c r="Q51" s="32" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="33" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$5*(B52-$S$3),"")</f>
@@ -8129,7 +8189,7 @@
       <c r="Q52" s="32" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="33" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$5*(B53-$S$3),"")</f>
@@ -8175,7 +8235,7 @@
       <c r="Q53" s="32" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="33" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$5*(B54-$S$3),"")</f>
@@ -8221,7 +8281,7 @@
       <c r="Q54" s="32" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="33" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$5*(B55-$S$3),"")</f>
@@ -8267,7 +8327,7 @@
       <c r="Q55" s="32" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="33" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$5*(B56-$S$3),"")</f>
@@ -8313,7 +8373,7 @@
       <c r="Q56" s="32" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="33" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$5*(B57-$S$3),"")</f>
@@ -8359,7 +8419,7 @@
       <c r="Q57" s="32" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="33" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$5*(B58-$S$3),"")</f>
@@ -8405,7 +8465,7 @@
       <c r="Q58" s="32" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="33" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$5*(B59-$S$3),"")</f>
@@ -8451,7 +8511,7 @@
       <c r="Q59" s="32" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="33" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$5*(B60-$S$3),"")</f>
@@ -8497,7 +8557,7 @@
       <c r="Q60" s="32" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="33" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$5*(B61-$S$3),"")</f>
@@ -8543,7 +8603,7 @@
       <c r="Q61" s="32" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="33" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$5*(B62-$S$3),"")</f>
@@ -8589,7 +8649,7 @@
       <c r="Q62" s="32" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="33" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$5*(B63-$S$3),"")</f>
@@ -8635,7 +8695,7 @@
       <c r="Q63" s="32" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="33" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$5*(B64-$S$3),"")</f>
@@ -8681,7 +8741,7 @@
       <c r="Q64" s="32" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="33" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$5*(B65-$S$3),"")</f>
@@ -8727,7 +8787,7 @@
       <c r="Q65" s="32" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="33" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$5*(B66-$S$3),"")</f>
@@ -8773,7 +8833,7 @@
       <c r="Q66" s="32" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="33" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$5*(B67-$S$3),"")</f>
@@ -8819,7 +8879,7 @@
       <c r="Q67" s="32" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="33" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$5*(B68-$S$3),"")</f>
@@ -8865,7 +8925,7 @@
       <c r="Q68" s="32" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="33" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$5*(B69-$S$3),"")</f>
@@ -8911,7 +8971,7 @@
       <c r="Q69" s="32" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="33" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$5*(B70-$S$3),"")</f>
@@ -8957,7 +9017,7 @@
       <c r="Q70" s="32" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="33" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$5*(B71-$S$3),"")</f>
@@ -9003,7 +9063,7 @@
       <c r="Q71" s="32" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="33" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$5*(B72-$S$3),"")</f>
@@ -9049,7 +9109,7 @@
       <c r="Q72" s="32" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="33" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$5*(B73-$S$3),"")</f>
@@ -9095,7 +9155,7 @@
       <c r="Q73" s="32" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="33" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$5*(B74-$S$3),"")</f>
@@ -9141,7 +9201,7 @@
       <c r="Q74" s="32" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="33" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$5*(B75-$S$3),"")</f>
@@ -9187,7 +9247,7 @@
       <c r="Q75" s="32" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="33" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$5*(B76-$S$3),"")</f>
@@ -9233,7 +9293,7 @@
       <c r="Q76" s="32" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="33" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$5*(B77-$S$3),"")</f>
@@ -9279,7 +9339,7 @@
       <c r="Q77" s="32" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="33" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$5*(B78-$S$3),"")</f>
@@ -9325,7 +9385,7 @@
       <c r="Q78" s="32" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="33" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$5*(B79-$S$3),"")</f>
@@ -9371,7 +9431,7 @@
       <c r="Q79" s="32" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="33" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$5*(B80-$S$3),"")</f>
@@ -9417,7 +9477,7 @@
       <c r="Q80" s="32" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="33" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$5*(B81-$S$3),"")</f>
@@ -9463,7 +9523,7 @@
       <c r="Q81" s="32" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="33" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$5*(B82-$S$3),"")</f>
@@ -9509,7 +9569,7 @@
       <c r="Q82" s="32" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="33" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$5*(B83-$S$3),"")</f>
@@ -9555,7 +9615,7 @@
       <c r="Q83" s="32" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="33" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$5*(B84-$S$3),"")</f>
@@ -9601,7 +9661,7 @@
       <c r="Q84" s="32" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="33" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$5*(B85-$S$3),"")</f>
@@ -9647,7 +9707,7 @@
       <c r="Q85" s="32" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="33" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$5*(B86-$S$3),"")</f>
@@ -9693,7 +9753,7 @@
       <c r="Q86" s="32" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="33" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$5*(B87-$S$3),"")</f>
@@ -9739,7 +9799,7 @@
       <c r="Q87" s="32" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="33" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$5*(B88-$S$3),"")</f>
@@ -9785,7 +9845,7 @@
       <c r="Q88" s="32" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="33" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$5*(B89-$S$3),"")</f>
@@ -9831,7 +9891,7 @@
       <c r="Q89" s="32" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="33" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$5*(B90-$S$3),"")</f>
@@ -9877,7 +9937,7 @@
       <c r="Q90" s="32" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="33" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$5*(B91-$S$3),"")</f>
@@ -9923,7 +9983,7 @@
       <c r="Q91" s="32" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="33" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$5*(B92-$S$3),"")</f>
@@ -9969,7 +10029,7 @@
       <c r="Q92" s="32" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="33" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$5*(B93-$S$3),"")</f>
@@ -10015,7 +10075,7 @@
       <c r="Q93" s="32" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="33" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$5*(B94-$S$3),"")</f>
@@ -10061,7 +10121,7 @@
       <c r="Q94" s="32" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="33" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$5*(B95-$S$3),"")</f>
@@ -10107,7 +10167,7 @@
       <c r="Q95" s="32" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="33" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$5*(B96-$S$3),"")</f>
@@ -10153,7 +10213,7 @@
       <c r="Q96" s="32" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="33" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$5*(B97-$S$3),"")</f>
@@ -10199,7 +10259,7 @@
       <c r="Q97" s="32" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="33" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$5*(B98-$S$3),"")</f>
@@ -10245,7 +10305,7 @@
       <c r="Q98" s="32" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="33" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$5*(B99-$S$3),"")</f>
@@ -10291,7 +10351,7 @@
       <c r="Q99" s="32" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="33" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$5*(B100-$S$3),"")</f>
@@ -10337,7 +10397,7 @@
       <c r="Q100" s="32" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="33" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$5*(B101-$S$3),"")</f>
@@ -10383,7 +10443,7 @@
       <c r="Q101" s="32" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="33" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$5*(B102-$S$3),"")</f>
@@ -10429,7 +10489,7 @@
       <c r="Q102" s="32" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="33" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$5*(B103-$S$3),"")</f>
@@ -10475,7 +10535,7 @@
       <c r="Q103" s="32" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="33" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$5*(B104-$S$3),"")</f>
@@ -10698,19 +10758,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$6*(B5-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="D5" s="27" t="n">
+        <v>8.302</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>7.0208</v>
+      </c>
       <c r="F5" s="28">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="27" t="n"/>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -10727,8 +10799,12 @@
         <f>IFERROR(I5,"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="27" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>830.2</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="N5" s="31">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -10744,7 +10820,7 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$6*(B6-$S$3),"")</f>
@@ -10790,7 +10866,7 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="33" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$6*(B7-$S$3),"")</f>
@@ -10836,7 +10912,7 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="33" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$6*(B8-$S$3),"")</f>
@@ -10882,7 +10958,7 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="33" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$6*(B9-$S$3),"")</f>
@@ -10928,7 +11004,7 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="33" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$6*(B10-$S$3),"")</f>
@@ -10974,7 +11050,7 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="33" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$6*(B11-$S$3),"")</f>
@@ -11020,7 +11096,7 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="33" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$6*(B12-$S$3),"")</f>
@@ -11066,7 +11142,7 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="33" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$6*(B13-$S$3),"")</f>
@@ -11112,7 +11188,7 @@
       <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="33" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$6*(B14-$S$3),"")</f>
@@ -11158,7 +11234,7 @@
       <c r="Q14" s="32" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="33" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$6*(B15-$S$3),"")</f>
@@ -11204,7 +11280,7 @@
       <c r="Q15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="33" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$6*(B16-$S$3),"")</f>
@@ -11250,7 +11326,7 @@
       <c r="Q16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="33" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$6*(B17-$S$3),"")</f>
@@ -11296,7 +11372,7 @@
       <c r="Q17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="33" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$6*(B18-$S$3),"")</f>
@@ -11342,7 +11418,7 @@
       <c r="Q18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="33" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$6*(B19-$S$3),"")</f>
@@ -11388,7 +11464,7 @@
       <c r="Q19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="33" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$6*(B20-$S$3),"")</f>
@@ -11434,7 +11510,7 @@
       <c r="Q20" s="32" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="33" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$6*(B21-$S$3),"")</f>
@@ -11480,7 +11556,7 @@
       <c r="Q21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="33" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$6*(B22-$S$3),"")</f>
@@ -11526,7 +11602,7 @@
       <c r="Q22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="33" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$6*(B23-$S$3),"")</f>
@@ -11572,7 +11648,7 @@
       <c r="Q23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="33" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$6*(B24-$S$3),"")</f>
@@ -11618,7 +11694,7 @@
       <c r="Q24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="33" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$6*(B25-$S$3),"")</f>
@@ -11664,7 +11740,7 @@
       <c r="Q25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="33" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$6*(B26-$S$3),"")</f>
@@ -11710,7 +11786,7 @@
       <c r="Q26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="33" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$6*(B27-$S$3),"")</f>
@@ -11756,7 +11832,7 @@
       <c r="Q27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="33" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$6*(B28-$S$3),"")</f>
@@ -11802,7 +11878,7 @@
       <c r="Q28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="33" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$6*(B29-$S$3),"")</f>
@@ -11848,7 +11924,7 @@
       <c r="Q29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="33" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$6*(B30-$S$3),"")</f>
@@ -11894,7 +11970,7 @@
       <c r="Q30" s="32" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="33" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$6*(B31-$S$3),"")</f>
@@ -11940,7 +12016,7 @@
       <c r="Q31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="33" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$6*(B32-$S$3),"")</f>
@@ -11986,7 +12062,7 @@
       <c r="Q32" s="32" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="33" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$6*(B33-$S$3),"")</f>
@@ -12032,7 +12108,7 @@
       <c r="Q33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="33" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$6*(B34-$S$3),"")</f>
@@ -12078,7 +12154,7 @@
       <c r="Q34" s="32" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="33" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$6*(B35-$S$3),"")</f>
@@ -12124,7 +12200,7 @@
       <c r="Q35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="33" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$6*(B36-$S$3),"")</f>
@@ -12170,7 +12246,7 @@
       <c r="Q36" s="32" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="33" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$6*(B37-$S$3),"")</f>
@@ -12216,7 +12292,7 @@
       <c r="Q37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="33" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$6*(B38-$S$3),"")</f>
@@ -12262,7 +12338,7 @@
       <c r="Q38" s="32" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="33" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$6*(B39-$S$3),"")</f>
@@ -12308,7 +12384,7 @@
       <c r="Q39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="33" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$6*(B40-$S$3),"")</f>
@@ -12354,7 +12430,7 @@
       <c r="Q40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="33" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$6*(B41-$S$3),"")</f>
@@ -12400,7 +12476,7 @@
       <c r="Q41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="33" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$6*(B42-$S$3),"")</f>
@@ -12446,7 +12522,7 @@
       <c r="Q42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="33" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$6*(B43-$S$3),"")</f>
@@ -12492,7 +12568,7 @@
       <c r="Q43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="33" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$6*(B44-$S$3),"")</f>
@@ -12538,7 +12614,7 @@
       <c r="Q44" s="32" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="33" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$6*(B45-$S$3),"")</f>
@@ -12584,7 +12660,7 @@
       <c r="Q45" s="32" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="33" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$6*(B46-$S$3),"")</f>
@@ -12630,7 +12706,7 @@
       <c r="Q46" s="32" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="33" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$6*(B47-$S$3),"")</f>
@@ -12676,7 +12752,7 @@
       <c r="Q47" s="32" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="33" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$6*(B48-$S$3),"")</f>
@@ -12722,7 +12798,7 @@
       <c r="Q48" s="32" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="33" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$6*(B49-$S$3),"")</f>
@@ -12768,7 +12844,7 @@
       <c r="Q49" s="32" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="33" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$6*(B50-$S$3),"")</f>
@@ -12814,7 +12890,7 @@
       <c r="Q50" s="32" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="33" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$6*(B51-$S$3),"")</f>
@@ -12860,7 +12936,7 @@
       <c r="Q51" s="32" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="33" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$6*(B52-$S$3),"")</f>
@@ -12906,7 +12982,7 @@
       <c r="Q52" s="32" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="33" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$6*(B53-$S$3),"")</f>
@@ -12952,7 +13028,7 @@
       <c r="Q53" s="32" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="33" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$6*(B54-$S$3),"")</f>
@@ -12998,7 +13074,7 @@
       <c r="Q54" s="32" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="33" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$6*(B55-$S$3),"")</f>
@@ -13044,7 +13120,7 @@
       <c r="Q55" s="32" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="33" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$6*(B56-$S$3),"")</f>
@@ -13090,7 +13166,7 @@
       <c r="Q56" s="32" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="33" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$6*(B57-$S$3),"")</f>
@@ -13136,7 +13212,7 @@
       <c r="Q57" s="32" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="33" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$6*(B58-$S$3),"")</f>
@@ -13182,7 +13258,7 @@
       <c r="Q58" s="32" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="33" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$6*(B59-$S$3),"")</f>
@@ -13228,7 +13304,7 @@
       <c r="Q59" s="32" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="33" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$6*(B60-$S$3),"")</f>
@@ -13274,7 +13350,7 @@
       <c r="Q60" s="32" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="33" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$6*(B61-$S$3),"")</f>
@@ -13320,7 +13396,7 @@
       <c r="Q61" s="32" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="33" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$6*(B62-$S$3),"")</f>
@@ -13366,7 +13442,7 @@
       <c r="Q62" s="32" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="33" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$6*(B63-$S$3),"")</f>
@@ -13412,7 +13488,7 @@
       <c r="Q63" s="32" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="33" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$6*(B64-$S$3),"")</f>
@@ -13458,7 +13534,7 @@
       <c r="Q64" s="32" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="33" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$6*(B65-$S$3),"")</f>
@@ -13504,7 +13580,7 @@
       <c r="Q65" s="32" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="33" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$6*(B66-$S$3),"")</f>
@@ -13550,7 +13626,7 @@
       <c r="Q66" s="32" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="33" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$6*(B67-$S$3),"")</f>
@@ -13596,7 +13672,7 @@
       <c r="Q67" s="32" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="33" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$6*(B68-$S$3),"")</f>
@@ -13642,7 +13718,7 @@
       <c r="Q68" s="32" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="33" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$6*(B69-$S$3),"")</f>
@@ -13688,7 +13764,7 @@
       <c r="Q69" s="32" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="33" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$6*(B70-$S$3),"")</f>
@@ -13734,7 +13810,7 @@
       <c r="Q70" s="32" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="33" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$6*(B71-$S$3),"")</f>
@@ -13780,7 +13856,7 @@
       <c r="Q71" s="32" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="33" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$6*(B72-$S$3),"")</f>
@@ -13826,7 +13902,7 @@
       <c r="Q72" s="32" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="33" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$6*(B73-$S$3),"")</f>
@@ -13872,7 +13948,7 @@
       <c r="Q73" s="32" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="33" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$6*(B74-$S$3),"")</f>
@@ -13918,7 +13994,7 @@
       <c r="Q74" s="32" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="33" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$6*(B75-$S$3),"")</f>
@@ -13964,7 +14040,7 @@
       <c r="Q75" s="32" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="33" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$6*(B76-$S$3),"")</f>
@@ -14010,7 +14086,7 @@
       <c r="Q76" s="32" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="33" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$6*(B77-$S$3),"")</f>
@@ -14056,7 +14132,7 @@
       <c r="Q77" s="32" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="33" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$6*(B78-$S$3),"")</f>
@@ -14102,7 +14178,7 @@
       <c r="Q78" s="32" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="33" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$6*(B79-$S$3),"")</f>
@@ -14148,7 +14224,7 @@
       <c r="Q79" s="32" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="33" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$6*(B80-$S$3),"")</f>
@@ -14194,7 +14270,7 @@
       <c r="Q80" s="32" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="33" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$6*(B81-$S$3),"")</f>
@@ -14240,7 +14316,7 @@
       <c r="Q81" s="32" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="33" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$6*(B82-$S$3),"")</f>
@@ -14286,7 +14362,7 @@
       <c r="Q82" s="32" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="33" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$6*(B83-$S$3),"")</f>
@@ -14332,7 +14408,7 @@
       <c r="Q83" s="32" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="33" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$6*(B84-$S$3),"")</f>
@@ -14378,7 +14454,7 @@
       <c r="Q84" s="32" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="33" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$6*(B85-$S$3),"")</f>
@@ -14424,7 +14500,7 @@
       <c r="Q85" s="32" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="33" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$6*(B86-$S$3),"")</f>
@@ -14470,7 +14546,7 @@
       <c r="Q86" s="32" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="33" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$6*(B87-$S$3),"")</f>
@@ -14516,7 +14592,7 @@
       <c r="Q87" s="32" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="33" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$6*(B88-$S$3),"")</f>
@@ -14562,7 +14638,7 @@
       <c r="Q88" s="32" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="33" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$6*(B89-$S$3),"")</f>
@@ -14608,7 +14684,7 @@
       <c r="Q89" s="32" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="33" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$6*(B90-$S$3),"")</f>
@@ -14654,7 +14730,7 @@
       <c r="Q90" s="32" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="33" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$6*(B91-$S$3),"")</f>
@@ -14700,7 +14776,7 @@
       <c r="Q91" s="32" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="33" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$6*(B92-$S$3),"")</f>
@@ -14746,7 +14822,7 @@
       <c r="Q92" s="32" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="33" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$6*(B93-$S$3),"")</f>
@@ -14792,7 +14868,7 @@
       <c r="Q93" s="32" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="33" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$6*(B94-$S$3),"")</f>
@@ -14838,7 +14914,7 @@
       <c r="Q94" s="32" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="33" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$6*(B95-$S$3),"")</f>
@@ -14884,7 +14960,7 @@
       <c r="Q95" s="32" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="33" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$6*(B96-$S$3),"")</f>
@@ -14930,7 +15006,7 @@
       <c r="Q96" s="32" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="33" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$6*(B97-$S$3),"")</f>
@@ -14976,7 +15052,7 @@
       <c r="Q97" s="32" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="33" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$6*(B98-$S$3),"")</f>
@@ -15022,7 +15098,7 @@
       <c r="Q98" s="32" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="33" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$6*(B99-$S$3),"")</f>
@@ -15068,7 +15144,7 @@
       <c r="Q99" s="32" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="33" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$6*(B100-$S$3),"")</f>
@@ -15114,7 +15190,7 @@
       <c r="Q100" s="32" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="33" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$6*(B101-$S$3),"")</f>
@@ -15160,7 +15236,7 @@
       <c r="Q101" s="32" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="33" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$6*(B102-$S$3),"")</f>
@@ -15206,7 +15282,7 @@
       <c r="Q102" s="32" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="33" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$6*(B103-$S$3),"")</f>
@@ -15252,7 +15328,7 @@
       <c r="Q103" s="32" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="33" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$6*(B104-$S$3),"")</f>
@@ -15475,19 +15551,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$7*(B5-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="D5" s="27" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>1.5383</v>
+      </c>
       <c r="F5" s="28">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="27" t="n"/>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -15504,8 +15592,12 @@
         <f>IFERROR(I5,"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="27" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N5" s="31">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -15521,7 +15613,7 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$7*(B6-$S$3),"")</f>
@@ -15567,7 +15659,7 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="33" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$7*(B7-$S$3),"")</f>
@@ -15613,7 +15705,7 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="33" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$7*(B8-$S$3),"")</f>
@@ -15659,7 +15751,7 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="33" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$7*(B9-$S$3),"")</f>
@@ -15705,7 +15797,7 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="33" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$7*(B10-$S$3),"")</f>
@@ -15751,7 +15843,7 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="33" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$7*(B11-$S$3),"")</f>
@@ -15797,7 +15889,7 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="33" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$7*(B12-$S$3),"")</f>
@@ -15843,7 +15935,7 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="33" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$7*(B13-$S$3),"")</f>
@@ -15889,7 +15981,7 @@
       <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="33" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$7*(B14-$S$3),"")</f>
@@ -15935,7 +16027,7 @@
       <c r="Q14" s="32" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="33" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$7*(B15-$S$3),"")</f>
@@ -15981,7 +16073,7 @@
       <c r="Q15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="33" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$7*(B16-$S$3),"")</f>
@@ -16027,7 +16119,7 @@
       <c r="Q16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="33" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$7*(B17-$S$3),"")</f>
@@ -16073,7 +16165,7 @@
       <c r="Q17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="33" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$7*(B18-$S$3),"")</f>
@@ -16119,7 +16211,7 @@
       <c r="Q18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="33" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$7*(B19-$S$3),"")</f>
@@ -16165,7 +16257,7 @@
       <c r="Q19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="33" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$7*(B20-$S$3),"")</f>
@@ -16211,7 +16303,7 @@
       <c r="Q20" s="32" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="33" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$7*(B21-$S$3),"")</f>
@@ -16257,7 +16349,7 @@
       <c r="Q21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="33" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$7*(B22-$S$3),"")</f>
@@ -16303,7 +16395,7 @@
       <c r="Q22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="33" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$7*(B23-$S$3),"")</f>
@@ -16349,7 +16441,7 @@
       <c r="Q23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="33" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$7*(B24-$S$3),"")</f>
@@ -16395,7 +16487,7 @@
       <c r="Q24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="33" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$7*(B25-$S$3),"")</f>
@@ -16441,7 +16533,7 @@
       <c r="Q25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="33" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$7*(B26-$S$3),"")</f>
@@ -16487,7 +16579,7 @@
       <c r="Q26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="33" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$7*(B27-$S$3),"")</f>
@@ -16533,7 +16625,7 @@
       <c r="Q27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="33" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$7*(B28-$S$3),"")</f>
@@ -16579,7 +16671,7 @@
       <c r="Q28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="33" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$7*(B29-$S$3),"")</f>
@@ -16625,7 +16717,7 @@
       <c r="Q29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="33" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$7*(B30-$S$3),"")</f>
@@ -16671,7 +16763,7 @@
       <c r="Q30" s="32" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="33" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$7*(B31-$S$3),"")</f>
@@ -16717,7 +16809,7 @@
       <c r="Q31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="33" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$7*(B32-$S$3),"")</f>
@@ -16763,7 +16855,7 @@
       <c r="Q32" s="32" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="33" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$7*(B33-$S$3),"")</f>
@@ -16809,7 +16901,7 @@
       <c r="Q33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="33" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$7*(B34-$S$3),"")</f>
@@ -16855,7 +16947,7 @@
       <c r="Q34" s="32" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="33" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$7*(B35-$S$3),"")</f>
@@ -16901,7 +16993,7 @@
       <c r="Q35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="33" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$7*(B36-$S$3),"")</f>
@@ -16947,7 +17039,7 @@
       <c r="Q36" s="32" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="33" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$7*(B37-$S$3),"")</f>
@@ -16993,7 +17085,7 @@
       <c r="Q37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="33" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$7*(B38-$S$3),"")</f>
@@ -17039,7 +17131,7 @@
       <c r="Q38" s="32" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="33" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$7*(B39-$S$3),"")</f>
@@ -17085,7 +17177,7 @@
       <c r="Q39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="33" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$7*(B40-$S$3),"")</f>
@@ -17131,7 +17223,7 @@
       <c r="Q40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="33" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$7*(B41-$S$3),"")</f>
@@ -17177,7 +17269,7 @@
       <c r="Q41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="33" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$7*(B42-$S$3),"")</f>
@@ -17223,7 +17315,7 @@
       <c r="Q42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="33" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$7*(B43-$S$3),"")</f>
@@ -17269,7 +17361,7 @@
       <c r="Q43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="33" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$7*(B44-$S$3),"")</f>
@@ -17315,7 +17407,7 @@
       <c r="Q44" s="32" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="33" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$7*(B45-$S$3),"")</f>
@@ -17361,7 +17453,7 @@
       <c r="Q45" s="32" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="33" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$7*(B46-$S$3),"")</f>
@@ -17407,7 +17499,7 @@
       <c r="Q46" s="32" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="33" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$7*(B47-$S$3),"")</f>
@@ -17453,7 +17545,7 @@
       <c r="Q47" s="32" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="33" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$7*(B48-$S$3),"")</f>
@@ -17499,7 +17591,7 @@
       <c r="Q48" s="32" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="33" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$7*(B49-$S$3),"")</f>
@@ -17545,7 +17637,7 @@
       <c r="Q49" s="32" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="33" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$7*(B50-$S$3),"")</f>
@@ -17591,7 +17683,7 @@
       <c r="Q50" s="32" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="33" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$7*(B51-$S$3),"")</f>
@@ -17637,7 +17729,7 @@
       <c r="Q51" s="32" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="33" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$7*(B52-$S$3),"")</f>
@@ -17683,7 +17775,7 @@
       <c r="Q52" s="32" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="33" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$7*(B53-$S$3),"")</f>
@@ -17729,7 +17821,7 @@
       <c r="Q53" s="32" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="33" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$7*(B54-$S$3),"")</f>
@@ -17775,7 +17867,7 @@
       <c r="Q54" s="32" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="33" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$7*(B55-$S$3),"")</f>
@@ -17821,7 +17913,7 @@
       <c r="Q55" s="32" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="33" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$7*(B56-$S$3),"")</f>
@@ -17867,7 +17959,7 @@
       <c r="Q56" s="32" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="33" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$7*(B57-$S$3),"")</f>
@@ -17913,7 +18005,7 @@
       <c r="Q57" s="32" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="33" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$7*(B58-$S$3),"")</f>
@@ -17959,7 +18051,7 @@
       <c r="Q58" s="32" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="33" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$7*(B59-$S$3),"")</f>
@@ -18005,7 +18097,7 @@
       <c r="Q59" s="32" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="33" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$7*(B60-$S$3),"")</f>
@@ -18051,7 +18143,7 @@
       <c r="Q60" s="32" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="33" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$7*(B61-$S$3),"")</f>
@@ -18097,7 +18189,7 @@
       <c r="Q61" s="32" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="33" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$7*(B62-$S$3),"")</f>
@@ -18143,7 +18235,7 @@
       <c r="Q62" s="32" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="33" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$7*(B63-$S$3),"")</f>
@@ -18189,7 +18281,7 @@
       <c r="Q63" s="32" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="33" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$7*(B64-$S$3),"")</f>
@@ -18235,7 +18327,7 @@
       <c r="Q64" s="32" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="33" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$7*(B65-$S$3),"")</f>
@@ -18281,7 +18373,7 @@
       <c r="Q65" s="32" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="33" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$7*(B66-$S$3),"")</f>
@@ -18327,7 +18419,7 @@
       <c r="Q66" s="32" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="33" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$7*(B67-$S$3),"")</f>
@@ -18373,7 +18465,7 @@
       <c r="Q67" s="32" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="33" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$7*(B68-$S$3),"")</f>
@@ -18419,7 +18511,7 @@
       <c r="Q68" s="32" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="33" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$7*(B69-$S$3),"")</f>
@@ -18465,7 +18557,7 @@
       <c r="Q69" s="32" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="33" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$7*(B70-$S$3),"")</f>
@@ -18511,7 +18603,7 @@
       <c r="Q70" s="32" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="33" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$7*(B71-$S$3),"")</f>
@@ -18557,7 +18649,7 @@
       <c r="Q71" s="32" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="33" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$7*(B72-$S$3),"")</f>
@@ -18603,7 +18695,7 @@
       <c r="Q72" s="32" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="33" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$7*(B73-$S$3),"")</f>
@@ -18649,7 +18741,7 @@
       <c r="Q73" s="32" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="33" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$7*(B74-$S$3),"")</f>
@@ -18695,7 +18787,7 @@
       <c r="Q74" s="32" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="33" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$7*(B75-$S$3),"")</f>
@@ -18741,7 +18833,7 @@
       <c r="Q75" s="32" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="33" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$7*(B76-$S$3),"")</f>
@@ -18787,7 +18879,7 @@
       <c r="Q76" s="32" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="33" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$7*(B77-$S$3),"")</f>
@@ -18833,7 +18925,7 @@
       <c r="Q77" s="32" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="33" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$7*(B78-$S$3),"")</f>
@@ -18879,7 +18971,7 @@
       <c r="Q78" s="32" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="33" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$7*(B79-$S$3),"")</f>
@@ -18925,7 +19017,7 @@
       <c r="Q79" s="32" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="33" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$7*(B80-$S$3),"")</f>
@@ -18971,7 +19063,7 @@
       <c r="Q80" s="32" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="33" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$7*(B81-$S$3),"")</f>
@@ -19017,7 +19109,7 @@
       <c r="Q81" s="32" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="33" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$7*(B82-$S$3),"")</f>
@@ -19063,7 +19155,7 @@
       <c r="Q82" s="32" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="33" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$7*(B83-$S$3),"")</f>
@@ -19109,7 +19201,7 @@
       <c r="Q83" s="32" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="33" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$7*(B84-$S$3),"")</f>
@@ -19155,7 +19247,7 @@
       <c r="Q84" s="32" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="33" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$7*(B85-$S$3),"")</f>
@@ -19201,7 +19293,7 @@
       <c r="Q85" s="32" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="33" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$7*(B86-$S$3),"")</f>
@@ -19247,7 +19339,7 @@
       <c r="Q86" s="32" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="33" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$7*(B87-$S$3),"")</f>
@@ -19293,7 +19385,7 @@
       <c r="Q87" s="32" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="33" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$7*(B88-$S$3),"")</f>
@@ -19339,7 +19431,7 @@
       <c r="Q88" s="32" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="33" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$7*(B89-$S$3),"")</f>
@@ -19385,7 +19477,7 @@
       <c r="Q89" s="32" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="33" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$7*(B90-$S$3),"")</f>
@@ -19431,7 +19523,7 @@
       <c r="Q90" s="32" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="33" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$7*(B91-$S$3),"")</f>
@@ -19477,7 +19569,7 @@
       <c r="Q91" s="32" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="33" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$7*(B92-$S$3),"")</f>
@@ -19523,7 +19615,7 @@
       <c r="Q92" s="32" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="33" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$7*(B93-$S$3),"")</f>
@@ -19569,7 +19661,7 @@
       <c r="Q93" s="32" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="33" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$7*(B94-$S$3),"")</f>
@@ -19615,7 +19707,7 @@
       <c r="Q94" s="32" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="33" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$7*(B95-$S$3),"")</f>
@@ -19661,7 +19753,7 @@
       <c r="Q95" s="32" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="33" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$7*(B96-$S$3),"")</f>
@@ -19707,7 +19799,7 @@
       <c r="Q96" s="32" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="33" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$7*(B97-$S$3),"")</f>
@@ -19753,7 +19845,7 @@
       <c r="Q97" s="32" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="33" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$7*(B98-$S$3),"")</f>
@@ -19799,7 +19891,7 @@
       <c r="Q98" s="32" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="33" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$7*(B99-$S$3),"")</f>
@@ -19845,7 +19937,7 @@
       <c r="Q99" s="32" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="33" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$7*(B100-$S$3),"")</f>
@@ -19891,7 +19983,7 @@
       <c r="Q100" s="32" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="33" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$7*(B101-$S$3),"")</f>
@@ -19937,7 +20029,7 @@
       <c r="Q101" s="32" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="33" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$7*(B102-$S$3),"")</f>
@@ -19983,7 +20075,7 @@
       <c r="Q102" s="32" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="33" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$7*(B103-$S$3),"")</f>
@@ -20029,7 +20121,7 @@
       <c r="Q103" s="32" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="33" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$7*(B104-$S$3),"")</f>
@@ -20252,19 +20344,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="7">
         <f>IFERROR(参数配置!$C$8*(B5-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="D5" s="27" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>1.7458</v>
+      </c>
       <c r="F5" s="28">
         <f>IFERROR((D5-E5)/E5,"")</f>
         <v/>
       </c>
-      <c r="G5" s="27" t="n"/>
+      <c r="G5" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="7">
         <f>IFERROR(G5*D5,"")</f>
         <v/>
@@ -20281,8 +20385,12 @@
         <f>IFERROR(I5,"")</f>
         <v/>
       </c>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="27" t="n"/>
+      <c r="L5" s="17" t="n">
+        <v>2284.8</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1200</v>
+      </c>
       <c r="N5" s="31">
         <f>IFERROR(G5+M5,"")</f>
         <v/>
@@ -20298,7 +20406,7 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n"/>
+      <c r="A6" s="33" t="n"/>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$8*(B6-$S$3),"")</f>
@@ -20344,7 +20452,7 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n"/>
+      <c r="A7" s="33" t="n"/>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$8*(B7-$S$3),"")</f>
@@ -20390,7 +20498,7 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="33" t="n"/>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$8*(B8-$S$3),"")</f>
@@ -20436,7 +20544,7 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="33" t="n"/>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$8*(B9-$S$3),"")</f>
@@ -20482,7 +20590,7 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="33" t="n"/>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$8*(B10-$S$3),"")</f>
@@ -20528,7 +20636,7 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="33" t="n"/>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$8*(B11-$S$3),"")</f>
@@ -20574,7 +20682,7 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="33" t="n"/>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$8*(B12-$S$3),"")</f>
@@ -20620,7 +20728,7 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="33" t="n"/>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$8*(B13-$S$3),"")</f>
@@ -20666,7 +20774,7 @@
       <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="33" t="n"/>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="7">
         <f>IFERROR(参数配置!$C$8*(B14-$S$3),"")</f>
@@ -20712,7 +20820,7 @@
       <c r="Q14" s="32" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="33" t="n"/>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="7">
         <f>IFERROR(参数配置!$C$8*(B15-$S$3),"")</f>
@@ -20758,7 +20866,7 @@
       <c r="Q15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="33" t="n"/>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="7">
         <f>IFERROR(参数配置!$C$8*(B16-$S$3),"")</f>
@@ -20804,7 +20912,7 @@
       <c r="Q16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="33" t="n"/>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="7">
         <f>IFERROR(参数配置!$C$8*(B17-$S$3),"")</f>
@@ -20850,7 +20958,7 @@
       <c r="Q17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="33" t="n"/>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="7">
         <f>IFERROR(参数配置!$C$8*(B18-$S$3),"")</f>
@@ -20896,7 +21004,7 @@
       <c r="Q18" s="32" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="33" t="n"/>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="7">
         <f>IFERROR(参数配置!$C$8*(B19-$S$3),"")</f>
@@ -20942,7 +21050,7 @@
       <c r="Q19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="33" t="n"/>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="7">
         <f>IFERROR(参数配置!$C$8*(B20-$S$3),"")</f>
@@ -20988,7 +21096,7 @@
       <c r="Q20" s="32" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="33" t="n"/>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="7">
         <f>IFERROR(参数配置!$C$8*(B21-$S$3),"")</f>
@@ -21034,7 +21142,7 @@
       <c r="Q21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="33" t="n"/>
       <c r="B22" s="15" t="n"/>
       <c r="C22" s="7">
         <f>IFERROR(参数配置!$C$8*(B22-$S$3),"")</f>
@@ -21080,7 +21188,7 @@
       <c r="Q22" s="32" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="33" t="n"/>
       <c r="B23" s="15" t="n"/>
       <c r="C23" s="7">
         <f>IFERROR(参数配置!$C$8*(B23-$S$3),"")</f>
@@ -21126,7 +21234,7 @@
       <c r="Q23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="33" t="n"/>
       <c r="B24" s="15" t="n"/>
       <c r="C24" s="7">
         <f>IFERROR(参数配置!$C$8*(B24-$S$3),"")</f>
@@ -21172,7 +21280,7 @@
       <c r="Q24" s="32" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="33" t="n"/>
       <c r="B25" s="15" t="n"/>
       <c r="C25" s="7">
         <f>IFERROR(参数配置!$C$8*(B25-$S$3),"")</f>
@@ -21218,7 +21326,7 @@
       <c r="Q25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="33" t="n"/>
       <c r="B26" s="15" t="n"/>
       <c r="C26" s="7">
         <f>IFERROR(参数配置!$C$8*(B26-$S$3),"")</f>
@@ -21264,7 +21372,7 @@
       <c r="Q26" s="32" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="33" t="n"/>
       <c r="B27" s="15" t="n"/>
       <c r="C27" s="7">
         <f>IFERROR(参数配置!$C$8*(B27-$S$3),"")</f>
@@ -21310,7 +21418,7 @@
       <c r="Q27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="33" t="n"/>
       <c r="B28" s="15" t="n"/>
       <c r="C28" s="7">
         <f>IFERROR(参数配置!$C$8*(B28-$S$3),"")</f>
@@ -21356,7 +21464,7 @@
       <c r="Q28" s="32" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="33" t="n"/>
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="7">
         <f>IFERROR(参数配置!$C$8*(B29-$S$3),"")</f>
@@ -21402,7 +21510,7 @@
       <c r="Q29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="33" t="n"/>
       <c r="B30" s="15" t="n"/>
       <c r="C30" s="7">
         <f>IFERROR(参数配置!$C$8*(B30-$S$3),"")</f>
@@ -21448,7 +21556,7 @@
       <c r="Q30" s="32" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="33" t="n"/>
       <c r="B31" s="15" t="n"/>
       <c r="C31" s="7">
         <f>IFERROR(参数配置!$C$8*(B31-$S$3),"")</f>
@@ -21494,7 +21602,7 @@
       <c r="Q31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="33" t="n"/>
       <c r="B32" s="15" t="n"/>
       <c r="C32" s="7">
         <f>IFERROR(参数配置!$C$8*(B32-$S$3),"")</f>
@@ -21540,7 +21648,7 @@
       <c r="Q32" s="32" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="33" t="n"/>
       <c r="B33" s="15" t="n"/>
       <c r="C33" s="7">
         <f>IFERROR(参数配置!$C$8*(B33-$S$3),"")</f>
@@ -21586,7 +21694,7 @@
       <c r="Q33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="33" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="C34" s="7">
         <f>IFERROR(参数配置!$C$8*(B34-$S$3),"")</f>
@@ -21632,7 +21740,7 @@
       <c r="Q34" s="32" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="33" t="n"/>
       <c r="B35" s="15" t="n"/>
       <c r="C35" s="7">
         <f>IFERROR(参数配置!$C$8*(B35-$S$3),"")</f>
@@ -21678,7 +21786,7 @@
       <c r="Q35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="33" t="n"/>
       <c r="B36" s="15" t="n"/>
       <c r="C36" s="7">
         <f>IFERROR(参数配置!$C$8*(B36-$S$3),"")</f>
@@ -21724,7 +21832,7 @@
       <c r="Q36" s="32" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="33" t="n"/>
       <c r="B37" s="15" t="n"/>
       <c r="C37" s="7">
         <f>IFERROR(参数配置!$C$8*(B37-$S$3),"")</f>
@@ -21770,7 +21878,7 @@
       <c r="Q37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="33" t="n"/>
       <c r="B38" s="15" t="n"/>
       <c r="C38" s="7">
         <f>IFERROR(参数配置!$C$8*(B38-$S$3),"")</f>
@@ -21816,7 +21924,7 @@
       <c r="Q38" s="32" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="33" t="n"/>
       <c r="B39" s="15" t="n"/>
       <c r="C39" s="7">
         <f>IFERROR(参数配置!$C$8*(B39-$S$3),"")</f>
@@ -21862,7 +21970,7 @@
       <c r="Q39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="33" t="n"/>
       <c r="B40" s="15" t="n"/>
       <c r="C40" s="7">
         <f>IFERROR(参数配置!$C$8*(B40-$S$3),"")</f>
@@ -21908,7 +22016,7 @@
       <c r="Q40" s="32" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="33" t="n"/>
       <c r="B41" s="15" t="n"/>
       <c r="C41" s="7">
         <f>IFERROR(参数配置!$C$8*(B41-$S$3),"")</f>
@@ -21954,7 +22062,7 @@
       <c r="Q41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="33" t="n"/>
       <c r="B42" s="15" t="n"/>
       <c r="C42" s="7">
         <f>IFERROR(参数配置!$C$8*(B42-$S$3),"")</f>
@@ -22000,7 +22108,7 @@
       <c r="Q42" s="32" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="33" t="n"/>
       <c r="B43" s="15" t="n"/>
       <c r="C43" s="7">
         <f>IFERROR(参数配置!$C$8*(B43-$S$3),"")</f>
@@ -22046,7 +22154,7 @@
       <c r="Q43" s="32" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="33" t="n"/>
       <c r="B44" s="15" t="n"/>
       <c r="C44" s="7">
         <f>IFERROR(参数配置!$C$8*(B44-$S$3),"")</f>
@@ -22092,7 +22200,7 @@
       <c r="Q44" s="32" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="n"/>
+      <c r="A45" s="33" t="n"/>
       <c r="B45" s="15" t="n"/>
       <c r="C45" s="7">
         <f>IFERROR(参数配置!$C$8*(B45-$S$3),"")</f>
@@ -22138,7 +22246,7 @@
       <c r="Q45" s="32" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="n"/>
+      <c r="A46" s="33" t="n"/>
       <c r="B46" s="15" t="n"/>
       <c r="C46" s="7">
         <f>IFERROR(参数配置!$C$8*(B46-$S$3),"")</f>
@@ -22184,7 +22292,7 @@
       <c r="Q46" s="32" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="n"/>
+      <c r="A47" s="33" t="n"/>
       <c r="B47" s="15" t="n"/>
       <c r="C47" s="7">
         <f>IFERROR(参数配置!$C$8*(B47-$S$3),"")</f>
@@ -22230,7 +22338,7 @@
       <c r="Q47" s="32" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="n"/>
+      <c r="A48" s="33" t="n"/>
       <c r="B48" s="15" t="n"/>
       <c r="C48" s="7">
         <f>IFERROR(参数配置!$C$8*(B48-$S$3),"")</f>
@@ -22276,7 +22384,7 @@
       <c r="Q48" s="32" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="n"/>
+      <c r="A49" s="33" t="n"/>
       <c r="B49" s="15" t="n"/>
       <c r="C49" s="7">
         <f>IFERROR(参数配置!$C$8*(B49-$S$3),"")</f>
@@ -22322,7 +22430,7 @@
       <c r="Q49" s="32" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="n"/>
+      <c r="A50" s="33" t="n"/>
       <c r="B50" s="15" t="n"/>
       <c r="C50" s="7">
         <f>IFERROR(参数配置!$C$8*(B50-$S$3),"")</f>
@@ -22368,7 +22476,7 @@
       <c r="Q50" s="32" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="n"/>
+      <c r="A51" s="33" t="n"/>
       <c r="B51" s="15" t="n"/>
       <c r="C51" s="7">
         <f>IFERROR(参数配置!$C$8*(B51-$S$3),"")</f>
@@ -22414,7 +22522,7 @@
       <c r="Q51" s="32" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="n"/>
+      <c r="A52" s="33" t="n"/>
       <c r="B52" s="15" t="n"/>
       <c r="C52" s="7">
         <f>IFERROR(参数配置!$C$8*(B52-$S$3),"")</f>
@@ -22460,7 +22568,7 @@
       <c r="Q52" s="32" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="n"/>
+      <c r="A53" s="33" t="n"/>
       <c r="B53" s="15" t="n"/>
       <c r="C53" s="7">
         <f>IFERROR(参数配置!$C$8*(B53-$S$3),"")</f>
@@ -22506,7 +22614,7 @@
       <c r="Q53" s="32" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="n"/>
+      <c r="A54" s="33" t="n"/>
       <c r="B54" s="15" t="n"/>
       <c r="C54" s="7">
         <f>IFERROR(参数配置!$C$8*(B54-$S$3),"")</f>
@@ -22552,7 +22660,7 @@
       <c r="Q54" s="32" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="n"/>
+      <c r="A55" s="33" t="n"/>
       <c r="B55" s="15" t="n"/>
       <c r="C55" s="7">
         <f>IFERROR(参数配置!$C$8*(B55-$S$3),"")</f>
@@ -22598,7 +22706,7 @@
       <c r="Q55" s="32" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="16" t="n"/>
+      <c r="A56" s="33" t="n"/>
       <c r="B56" s="15" t="n"/>
       <c r="C56" s="7">
         <f>IFERROR(参数配置!$C$8*(B56-$S$3),"")</f>
@@ -22644,7 +22752,7 @@
       <c r="Q56" s="32" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="16" t="n"/>
+      <c r="A57" s="33" t="n"/>
       <c r="B57" s="15" t="n"/>
       <c r="C57" s="7">
         <f>IFERROR(参数配置!$C$8*(B57-$S$3),"")</f>
@@ -22690,7 +22798,7 @@
       <c r="Q57" s="32" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="n"/>
+      <c r="A58" s="33" t="n"/>
       <c r="B58" s="15" t="n"/>
       <c r="C58" s="7">
         <f>IFERROR(参数配置!$C$8*(B58-$S$3),"")</f>
@@ -22736,7 +22844,7 @@
       <c r="Q58" s="32" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="n"/>
+      <c r="A59" s="33" t="n"/>
       <c r="B59" s="15" t="n"/>
       <c r="C59" s="7">
         <f>IFERROR(参数配置!$C$8*(B59-$S$3),"")</f>
@@ -22782,7 +22890,7 @@
       <c r="Q59" s="32" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="n"/>
+      <c r="A60" s="33" t="n"/>
       <c r="B60" s="15" t="n"/>
       <c r="C60" s="7">
         <f>IFERROR(参数配置!$C$8*(B60-$S$3),"")</f>
@@ -22828,7 +22936,7 @@
       <c r="Q60" s="32" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="n"/>
+      <c r="A61" s="33" t="n"/>
       <c r="B61" s="15" t="n"/>
       <c r="C61" s="7">
         <f>IFERROR(参数配置!$C$8*(B61-$S$3),"")</f>
@@ -22874,7 +22982,7 @@
       <c r="Q61" s="32" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="n"/>
+      <c r="A62" s="33" t="n"/>
       <c r="B62" s="15" t="n"/>
       <c r="C62" s="7">
         <f>IFERROR(参数配置!$C$8*(B62-$S$3),"")</f>
@@ -22920,7 +23028,7 @@
       <c r="Q62" s="32" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="n"/>
+      <c r="A63" s="33" t="n"/>
       <c r="B63" s="15" t="n"/>
       <c r="C63" s="7">
         <f>IFERROR(参数配置!$C$8*(B63-$S$3),"")</f>
@@ -22966,7 +23074,7 @@
       <c r="Q63" s="32" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n"/>
+      <c r="A64" s="33" t="n"/>
       <c r="B64" s="15" t="n"/>
       <c r="C64" s="7">
         <f>IFERROR(参数配置!$C$8*(B64-$S$3),"")</f>
@@ -23012,7 +23120,7 @@
       <c r="Q64" s="32" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="n"/>
+      <c r="A65" s="33" t="n"/>
       <c r="B65" s="15" t="n"/>
       <c r="C65" s="7">
         <f>IFERROR(参数配置!$C$8*(B65-$S$3),"")</f>
@@ -23058,7 +23166,7 @@
       <c r="Q65" s="32" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="n"/>
+      <c r="A66" s="33" t="n"/>
       <c r="B66" s="15" t="n"/>
       <c r="C66" s="7">
         <f>IFERROR(参数配置!$C$8*(B66-$S$3),"")</f>
@@ -23104,7 +23212,7 @@
       <c r="Q66" s="32" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="n"/>
+      <c r="A67" s="33" t="n"/>
       <c r="B67" s="15" t="n"/>
       <c r="C67" s="7">
         <f>IFERROR(参数配置!$C$8*(B67-$S$3),"")</f>
@@ -23150,7 +23258,7 @@
       <c r="Q67" s="32" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="n"/>
+      <c r="A68" s="33" t="n"/>
       <c r="B68" s="15" t="n"/>
       <c r="C68" s="7">
         <f>IFERROR(参数配置!$C$8*(B68-$S$3),"")</f>
@@ -23196,7 +23304,7 @@
       <c r="Q68" s="32" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="n"/>
+      <c r="A69" s="33" t="n"/>
       <c r="B69" s="15" t="n"/>
       <c r="C69" s="7">
         <f>IFERROR(参数配置!$C$8*(B69-$S$3),"")</f>
@@ -23242,7 +23350,7 @@
       <c r="Q69" s="32" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="n"/>
+      <c r="A70" s="33" t="n"/>
       <c r="B70" s="15" t="n"/>
       <c r="C70" s="7">
         <f>IFERROR(参数配置!$C$8*(B70-$S$3),"")</f>
@@ -23288,7 +23396,7 @@
       <c r="Q70" s="32" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="n"/>
+      <c r="A71" s="33" t="n"/>
       <c r="B71" s="15" t="n"/>
       <c r="C71" s="7">
         <f>IFERROR(参数配置!$C$8*(B71-$S$3),"")</f>
@@ -23334,7 +23442,7 @@
       <c r="Q71" s="32" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="n"/>
+      <c r="A72" s="33" t="n"/>
       <c r="B72" s="15" t="n"/>
       <c r="C72" s="7">
         <f>IFERROR(参数配置!$C$8*(B72-$S$3),"")</f>
@@ -23380,7 +23488,7 @@
       <c r="Q72" s="32" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="n"/>
+      <c r="A73" s="33" t="n"/>
       <c r="B73" s="15" t="n"/>
       <c r="C73" s="7">
         <f>IFERROR(参数配置!$C$8*(B73-$S$3),"")</f>
@@ -23426,7 +23534,7 @@
       <c r="Q73" s="32" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="n"/>
+      <c r="A74" s="33" t="n"/>
       <c r="B74" s="15" t="n"/>
       <c r="C74" s="7">
         <f>IFERROR(参数配置!$C$8*(B74-$S$3),"")</f>
@@ -23472,7 +23580,7 @@
       <c r="Q74" s="32" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n"/>
+      <c r="A75" s="33" t="n"/>
       <c r="B75" s="15" t="n"/>
       <c r="C75" s="7">
         <f>IFERROR(参数配置!$C$8*(B75-$S$3),"")</f>
@@ -23518,7 +23626,7 @@
       <c r="Q75" s="32" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="16" t="n"/>
+      <c r="A76" s="33" t="n"/>
       <c r="B76" s="15" t="n"/>
       <c r="C76" s="7">
         <f>IFERROR(参数配置!$C$8*(B76-$S$3),"")</f>
@@ -23564,7 +23672,7 @@
       <c r="Q76" s="32" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="16" t="n"/>
+      <c r="A77" s="33" t="n"/>
       <c r="B77" s="15" t="n"/>
       <c r="C77" s="7">
         <f>IFERROR(参数配置!$C$8*(B77-$S$3),"")</f>
@@ -23610,7 +23718,7 @@
       <c r="Q77" s="32" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n"/>
+      <c r="A78" s="33" t="n"/>
       <c r="B78" s="15" t="n"/>
       <c r="C78" s="7">
         <f>IFERROR(参数配置!$C$8*(B78-$S$3),"")</f>
@@ -23656,7 +23764,7 @@
       <c r="Q78" s="32" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n"/>
+      <c r="A79" s="33" t="n"/>
       <c r="B79" s="15" t="n"/>
       <c r="C79" s="7">
         <f>IFERROR(参数配置!$C$8*(B79-$S$3),"")</f>
@@ -23702,7 +23810,7 @@
       <c r="Q79" s="32" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n"/>
+      <c r="A80" s="33" t="n"/>
       <c r="B80" s="15" t="n"/>
       <c r="C80" s="7">
         <f>IFERROR(参数配置!$C$8*(B80-$S$3),"")</f>
@@ -23748,7 +23856,7 @@
       <c r="Q80" s="32" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n"/>
+      <c r="A81" s="33" t="n"/>
       <c r="B81" s="15" t="n"/>
       <c r="C81" s="7">
         <f>IFERROR(参数配置!$C$8*(B81-$S$3),"")</f>
@@ -23794,7 +23902,7 @@
       <c r="Q81" s="32" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n"/>
+      <c r="A82" s="33" t="n"/>
       <c r="B82" s="15" t="n"/>
       <c r="C82" s="7">
         <f>IFERROR(参数配置!$C$8*(B82-$S$3),"")</f>
@@ -23840,7 +23948,7 @@
       <c r="Q82" s="32" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n"/>
+      <c r="A83" s="33" t="n"/>
       <c r="B83" s="15" t="n"/>
       <c r="C83" s="7">
         <f>IFERROR(参数配置!$C$8*(B83-$S$3),"")</f>
@@ -23886,7 +23994,7 @@
       <c r="Q83" s="32" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="16" t="n"/>
+      <c r="A84" s="33" t="n"/>
       <c r="B84" s="15" t="n"/>
       <c r="C84" s="7">
         <f>IFERROR(参数配置!$C$8*(B84-$S$3),"")</f>
@@ -23932,7 +24040,7 @@
       <c r="Q84" s="32" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n"/>
+      <c r="A85" s="33" t="n"/>
       <c r="B85" s="15" t="n"/>
       <c r="C85" s="7">
         <f>IFERROR(参数配置!$C$8*(B85-$S$3),"")</f>
@@ -23978,7 +24086,7 @@
       <c r="Q85" s="32" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n"/>
+      <c r="A86" s="33" t="n"/>
       <c r="B86" s="15" t="n"/>
       <c r="C86" s="7">
         <f>IFERROR(参数配置!$C$8*(B86-$S$3),"")</f>
@@ -24024,7 +24132,7 @@
       <c r="Q86" s="32" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n"/>
+      <c r="A87" s="33" t="n"/>
       <c r="B87" s="15" t="n"/>
       <c r="C87" s="7">
         <f>IFERROR(参数配置!$C$8*(B87-$S$3),"")</f>
@@ -24070,7 +24178,7 @@
       <c r="Q87" s="32" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n"/>
+      <c r="A88" s="33" t="n"/>
       <c r="B88" s="15" t="n"/>
       <c r="C88" s="7">
         <f>IFERROR(参数配置!$C$8*(B88-$S$3),"")</f>
@@ -24116,7 +24224,7 @@
       <c r="Q88" s="32" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n"/>
+      <c r="A89" s="33" t="n"/>
       <c r="B89" s="15" t="n"/>
       <c r="C89" s="7">
         <f>IFERROR(参数配置!$C$8*(B89-$S$3),"")</f>
@@ -24162,7 +24270,7 @@
       <c r="Q89" s="32" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="n"/>
+      <c r="A90" s="33" t="n"/>
       <c r="B90" s="15" t="n"/>
       <c r="C90" s="7">
         <f>IFERROR(参数配置!$C$8*(B90-$S$3),"")</f>
@@ -24208,7 +24316,7 @@
       <c r="Q90" s="32" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="n"/>
+      <c r="A91" s="33" t="n"/>
       <c r="B91" s="15" t="n"/>
       <c r="C91" s="7">
         <f>IFERROR(参数配置!$C$8*(B91-$S$3),"")</f>
@@ -24254,7 +24362,7 @@
       <c r="Q91" s="32" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="n"/>
+      <c r="A92" s="33" t="n"/>
       <c r="B92" s="15" t="n"/>
       <c r="C92" s="7">
         <f>IFERROR(参数配置!$C$8*(B92-$S$3),"")</f>
@@ -24300,7 +24408,7 @@
       <c r="Q92" s="32" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="n"/>
+      <c r="A93" s="33" t="n"/>
       <c r="B93" s="15" t="n"/>
       <c r="C93" s="7">
         <f>IFERROR(参数配置!$C$8*(B93-$S$3),"")</f>
@@ -24346,7 +24454,7 @@
       <c r="Q93" s="32" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="16" t="n"/>
+      <c r="A94" s="33" t="n"/>
       <c r="B94" s="15" t="n"/>
       <c r="C94" s="7">
         <f>IFERROR(参数配置!$C$8*(B94-$S$3),"")</f>
@@ -24392,7 +24500,7 @@
       <c r="Q94" s="32" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="16" t="n"/>
+      <c r="A95" s="33" t="n"/>
       <c r="B95" s="15" t="n"/>
       <c r="C95" s="7">
         <f>IFERROR(参数配置!$C$8*(B95-$S$3),"")</f>
@@ -24438,7 +24546,7 @@
       <c r="Q95" s="32" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="n"/>
+      <c r="A96" s="33" t="n"/>
       <c r="B96" s="15" t="n"/>
       <c r="C96" s="7">
         <f>IFERROR(参数配置!$C$8*(B96-$S$3),"")</f>
@@ -24484,7 +24592,7 @@
       <c r="Q96" s="32" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="16" t="n"/>
+      <c r="A97" s="33" t="n"/>
       <c r="B97" s="15" t="n"/>
       <c r="C97" s="7">
         <f>IFERROR(参数配置!$C$8*(B97-$S$3),"")</f>
@@ -24530,7 +24638,7 @@
       <c r="Q97" s="32" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="16" t="n"/>
+      <c r="A98" s="33" t="n"/>
       <c r="B98" s="15" t="n"/>
       <c r="C98" s="7">
         <f>IFERROR(参数配置!$C$8*(B98-$S$3),"")</f>
@@ -24576,7 +24684,7 @@
       <c r="Q98" s="32" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="16" t="n"/>
+      <c r="A99" s="33" t="n"/>
       <c r="B99" s="15" t="n"/>
       <c r="C99" s="7">
         <f>IFERROR(参数配置!$C$8*(B99-$S$3),"")</f>
@@ -24622,7 +24730,7 @@
       <c r="Q99" s="32" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="16" t="n"/>
+      <c r="A100" s="33" t="n"/>
       <c r="B100" s="15" t="n"/>
       <c r="C100" s="7">
         <f>IFERROR(参数配置!$C$8*(B100-$S$3),"")</f>
@@ -24668,7 +24776,7 @@
       <c r="Q100" s="32" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="16" t="n"/>
+      <c r="A101" s="33" t="n"/>
       <c r="B101" s="15" t="n"/>
       <c r="C101" s="7">
         <f>IFERROR(参数配置!$C$8*(B101-$S$3),"")</f>
@@ -24714,7 +24822,7 @@
       <c r="Q101" s="32" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="n"/>
+      <c r="A102" s="33" t="n"/>
       <c r="B102" s="15" t="n"/>
       <c r="C102" s="7">
         <f>IFERROR(参数配置!$C$8*(B102-$S$3),"")</f>
@@ -24760,7 +24868,7 @@
       <c r="Q102" s="32" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="16" t="n"/>
+      <c r="A103" s="33" t="n"/>
       <c r="B103" s="15" t="n"/>
       <c r="C103" s="7">
         <f>IFERROR(参数配置!$C$8*(B103-$S$3),"")</f>
@@ -24806,7 +24914,7 @@
       <c r="Q103" s="32" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="16" t="n"/>
+      <c r="A104" s="33" t="n"/>
       <c r="B104" s="15" t="n"/>
       <c r="C104" s="7">
         <f>IFERROR(参数配置!$C$8*(B104-$S$3),"")</f>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>MAX(0,参数配置!$C$15-IFERROR(LOOKUP(2,1/(每期汇总!L5:L1000&lt;&gt;""),每期汇总!L5:L1000),0))</f>
+        <f>MAX(0,参数配置!$C$18-IFERROR(LOOKUP(2,1/(每期汇总!L5:L1000&lt;&gt;""),每期汇总!L5:L1000),0))</f>
         <v/>
       </c>
       <c r="C16" s="12" t="n"/>
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="M5" s="5">
-        <f>IFERROR(IF(L5&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L5&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         <v/>
       </c>
       <c r="M6" s="5">
-        <f>IFERROR(IF(L6&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L6&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         <v/>
       </c>
       <c r="M7" s="5">
-        <f>IFERROR(IF(L7&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L7&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
         <v/>
       </c>
       <c r="M8" s="5">
-        <f>IFERROR(IF(L8&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L8&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
         <v/>
       </c>
       <c r="M9" s="5">
-        <f>IFERROR(IF(L9&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L9&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         <v/>
       </c>
       <c r="M10" s="5">
-        <f>IFERROR(IF(L10&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L10&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="M11" s="5">
-        <f>IFERROR(IF(L11&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L11&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
         <v/>
       </c>
       <c r="M12" s="5">
-        <f>IFERROR(IF(L12&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L12&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <v/>
       </c>
       <c r="M13" s="5">
-        <f>IFERROR(IF(L13&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L13&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
         <v/>
       </c>
       <c r="M14" s="5">
-        <f>IFERROR(IF(L14&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L14&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="M15" s="5">
-        <f>IFERROR(IF(L15&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L15&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
         <v/>
       </c>
       <c r="M16" s="5">
-        <f>IFERROR(IF(L16&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L16&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
         <v/>
       </c>
       <c r="M17" s="5">
-        <f>IFERROR(IF(L17&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L17&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
         <v/>
       </c>
       <c r="M18" s="5">
-        <f>IFERROR(IF(L18&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L18&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
         <v/>
       </c>
       <c r="M19" s="5">
-        <f>IFERROR(IF(L19&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L19&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
         <v/>
       </c>
       <c r="M20" s="5">
-        <f>IFERROR(IF(L20&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L20&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
         <v/>
       </c>
       <c r="M21" s="5">
-        <f>IFERROR(IF(L21&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L21&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="M22" s="5">
-        <f>IFERROR(IF(L22&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L22&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v/>
       </c>
       <c r="M23" s="5">
-        <f>IFERROR(IF(L23&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L23&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         <v/>
       </c>
       <c r="M24" s="5">
-        <f>IFERROR(IF(L24&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L24&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
         <v/>
       </c>
       <c r="M25" s="5">
-        <f>IFERROR(IF(L25&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L25&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         <v/>
       </c>
       <c r="M26" s="5">
-        <f>IFERROR(IF(L26&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L26&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
         <v/>
       </c>
       <c r="M27" s="5">
-        <f>IFERROR(IF(L27&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L27&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="M28" s="5">
-        <f>IFERROR(IF(L28&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L28&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         <v/>
       </c>
       <c r="M29" s="5">
-        <f>IFERROR(IF(L29&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L29&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
         <v/>
       </c>
       <c r="M30" s="5">
-        <f>IFERROR(IF(L30&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L30&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
         <v/>
       </c>
       <c r="M31" s="5">
-        <f>IFERROR(IF(L31&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L31&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
         <v/>
       </c>
       <c r="M32" s="5">
-        <f>IFERROR(IF(L32&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L32&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
         <v/>
       </c>
       <c r="M33" s="5">
-        <f>IFERROR(IF(L33&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L33&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
         <v/>
       </c>
       <c r="M34" s="5">
-        <f>IFERROR(IF(L34&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L34&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="M35" s="5">
-        <f>IFERROR(IF(L35&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L35&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
         <v/>
       </c>
       <c r="M36" s="5">
-        <f>IFERROR(IF(L36&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L36&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v/>
       </c>
       <c r="M37" s="5">
-        <f>IFERROR(IF(L37&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L37&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
         <v/>
       </c>
       <c r="M38" s="5">
-        <f>IFERROR(IF(L38&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L38&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="M39" s="5">
-        <f>IFERROR(IF(L39&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L39&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         <v/>
       </c>
       <c r="M40" s="5">
-        <f>IFERROR(IF(L40&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L40&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
         <v/>
       </c>
       <c r="M41" s="5">
-        <f>IFERROR(IF(L41&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L41&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
         <v/>
       </c>
       <c r="M42" s="5">
-        <f>IFERROR(IF(L42&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L42&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="M43" s="5">
-        <f>IFERROR(IF(L43&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L43&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
         <v/>
       </c>
       <c r="M44" s="5">
-        <f>IFERROR(IF(L44&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L44&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
         <v/>
       </c>
       <c r="M45" s="5">
-        <f>IFERROR(IF(L45&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L45&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
         <v/>
       </c>
       <c r="M46" s="5">
-        <f>IFERROR(IF(L46&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L46&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
         <v/>
       </c>
       <c r="M47" s="5">
-        <f>IFERROR(IF(L47&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L47&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
         <v/>
       </c>
       <c r="M48" s="5">
-        <f>IFERROR(IF(L48&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L48&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="M49" s="5">
-        <f>IFERROR(IF(L49&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L49&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v/>
       </c>
       <c r="M50" s="5">
-        <f>IFERROR(IF(L50&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L50&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
         <v/>
       </c>
       <c r="M51" s="5">
-        <f>IFERROR(IF(L51&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L51&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
         <v/>
       </c>
       <c r="M52" s="5">
-        <f>IFERROR(IF(L52&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L52&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
         <v/>
       </c>
       <c r="M53" s="5">
-        <f>IFERROR(IF(L53&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L53&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
         <v/>
       </c>
       <c r="M54" s="5">
-        <f>IFERROR(IF(L54&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L54&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
         <v/>
       </c>
       <c r="M55" s="5">
-        <f>IFERROR(IF(L55&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L55&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="M56" s="5">
-        <f>IFERROR(IF(L56&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L56&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
         <v/>
       </c>
       <c r="M57" s="5">
-        <f>IFERROR(IF(L57&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L57&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         <v/>
       </c>
       <c r="M58" s="5">
-        <f>IFERROR(IF(L58&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L58&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
         <v/>
       </c>
       <c r="M59" s="5">
-        <f>IFERROR(IF(L59&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L59&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
         <v/>
       </c>
       <c r="M60" s="5">
-        <f>IFERROR(IF(L60&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L60&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
         <v/>
       </c>
       <c r="M61" s="5">
-        <f>IFERROR(IF(L61&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L61&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
         <v/>
       </c>
       <c r="M62" s="5">
-        <f>IFERROR(IF(L62&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L62&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3703,7 +3703,7 @@
         <v/>
       </c>
       <c r="M63" s="5">
-        <f>IFERROR(IF(L63&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L63&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         <v/>
       </c>
       <c r="M64" s="5">
-        <f>IFERROR(IF(L64&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L64&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
         <v/>
       </c>
       <c r="M65" s="5">
-        <f>IFERROR(IF(L65&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L65&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v/>
       </c>
       <c r="M66" s="5">
-        <f>IFERROR(IF(L66&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L66&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
         <v/>
       </c>
       <c r="M67" s="5">
-        <f>IFERROR(IF(L67&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L67&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
         <v/>
       </c>
       <c r="M68" s="5">
-        <f>IFERROR(IF(L68&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L68&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
         <v/>
       </c>
       <c r="M69" s="5">
-        <f>IFERROR(IF(L69&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L69&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
         <v/>
       </c>
       <c r="M70" s="5">
-        <f>IFERROR(IF(L70&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L70&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
         <v/>
       </c>
       <c r="M71" s="5">
-        <f>IFERROR(IF(L71&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L71&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
         <v/>
       </c>
       <c r="M72" s="5">
-        <f>IFERROR(IF(L72&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L72&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="M73" s="5">
-        <f>IFERROR(IF(L73&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L73&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="M74" s="5">
-        <f>IFERROR(IF(L74&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L74&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
         <v/>
       </c>
       <c r="M75" s="5">
-        <f>IFERROR(IF(L75&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L75&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         <v/>
       </c>
       <c r="M76" s="5">
-        <f>IFERROR(IF(L76&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L76&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
         <v/>
       </c>
       <c r="M77" s="5">
-        <f>IFERROR(IF(L77&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L77&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
         <v/>
       </c>
       <c r="M78" s="5">
-        <f>IFERROR(IF(L78&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L78&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         <v/>
       </c>
       <c r="M79" s="5">
-        <f>IFERROR(IF(L79&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L79&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
         <v/>
       </c>
       <c r="M80" s="5">
-        <f>IFERROR(IF(L80&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L80&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
         <v/>
       </c>
       <c r="M81" s="5">
-        <f>IFERROR(IF(L81&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L81&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4558,7 +4558,7 @@
         <v/>
       </c>
       <c r="M82" s="5">
-        <f>IFERROR(IF(L82&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L82&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
         <v/>
       </c>
       <c r="M83" s="5">
-        <f>IFERROR(IF(L83&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L83&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
         <v/>
       </c>
       <c r="M84" s="5">
-        <f>IFERROR(IF(L84&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L84&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
         <v/>
       </c>
       <c r="M85" s="5">
-        <f>IFERROR(IF(L85&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L85&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
         <v/>
       </c>
       <c r="M86" s="5">
-        <f>IFERROR(IF(L86&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L86&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
         <v/>
       </c>
       <c r="M87" s="5">
-        <f>IFERROR(IF(L87&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L87&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
         <v/>
       </c>
       <c r="M88" s="5">
-        <f>IFERROR(IF(L88&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L88&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         <v/>
       </c>
       <c r="M89" s="5">
-        <f>IFERROR(IF(L89&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L89&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
         <v/>
       </c>
       <c r="M90" s="5">
-        <f>IFERROR(IF(L90&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L90&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
         <v/>
       </c>
       <c r="M91" s="5">
-        <f>IFERROR(IF(L91&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L91&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
         <v/>
       </c>
       <c r="M92" s="5">
-        <f>IFERROR(IF(L92&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L92&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
         <v/>
       </c>
       <c r="M93" s="5">
-        <f>IFERROR(IF(L93&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L93&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
         <v/>
       </c>
       <c r="M94" s="5">
-        <f>IFERROR(IF(L94&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L94&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
         <v/>
       </c>
       <c r="M95" s="5">
-        <f>IFERROR(IF(L95&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L95&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
         <v/>
       </c>
       <c r="M96" s="5">
-        <f>IFERROR(IF(L96&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L96&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
         <v/>
       </c>
       <c r="M97" s="5">
-        <f>IFERROR(IF(L97&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L97&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
         <v/>
       </c>
       <c r="M98" s="5">
-        <f>IFERROR(IF(L98&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L98&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
         <v/>
       </c>
       <c r="M99" s="5">
-        <f>IFERROR(IF(L99&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L99&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
         <v/>
       </c>
       <c r="M100" s="5">
-        <f>IFERROR(IF(L100&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L100&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         <v/>
       </c>
       <c r="M101" s="5">
-        <f>IFERROR(IF(L101&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L101&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
         <v/>
       </c>
       <c r="M102" s="5">
-        <f>IFERROR(IF(L102&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L102&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
         <v/>
       </c>
       <c r="M103" s="5">
-        <f>IFERROR(IF(L103&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L103&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
         <v/>
       </c>
       <c r="M104" s="5">
-        <f>IFERROR(IF(L104&gt;=参数配置!$C$15,"增量阶段","存量阶段"),"")</f>
+        <f>IFERROR(IF(L104&gt;=参数配置!$C$18,"增量阶段","存量阶段"),"")</f>
         <v/>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>参数</t>
+          <t>标的</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>阈值</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -5734,63 +5734,103 @@
           <t>全仓清仓偏离度阈值</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>沪深300 ETF</t>
+        </is>
+      </c>
       <c r="C12" s="36" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>偏离度超 +55%，全部清仓并进入冷却期；冷却期目标冻结，解除后从第 1 期重新积累</t>
+          <t>偏离度超 +50%，全部清仓并进入冷却期</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>中证500 ETF</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
+    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>恒生指数 ETF</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>纳指100 ETF</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D15" s="21" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>三、增量阶段</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>触发门槛（累计净投入）</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="17" t="n">
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="17" t="n">
         <v>150000</v>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>达到后切换为增量阶段，买卖均走储备金池</t>
         </is>
       </c>
-      <c r="E15" s="37" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="E18" s="37" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>每期增量注入金额</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="17" t="n">
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>每期向储备金池注入的新增资金</t>
         </is>
       </c>
-      <c r="E16" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10788,11 +10828,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$13,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -10838,11 +10878,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$13,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -10884,11 +10924,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$13,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -10930,11 +10970,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$13,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -10976,11 +11016,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$13,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -11022,11 +11062,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$13,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -11068,11 +11108,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$13,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -11114,11 +11154,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$13,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -11160,11 +11200,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$13,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -11206,11 +11246,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$13,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -11252,11 +11292,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$13,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -11298,11 +11338,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$13,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -11344,11 +11384,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$13,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -11390,11 +11430,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$13,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -11436,11 +11476,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$13,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -11482,11 +11522,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$13,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -11528,11 +11568,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$13,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -11574,11 +11614,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$13,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -11620,11 +11660,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$13,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -11666,11 +11706,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$13,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -11712,11 +11752,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$13,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -11758,11 +11798,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$13,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -11804,11 +11844,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$13,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -11850,11 +11890,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$13,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -11896,11 +11936,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$13,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -11942,11 +11982,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$13,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -11988,11 +12028,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$13,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -12034,11 +12074,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$13,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -12080,11 +12120,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$13,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -12126,11 +12166,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$13,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -12172,11 +12212,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$13,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -12218,11 +12258,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$13,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -12264,11 +12304,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$13,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -12310,11 +12350,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$13,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -12356,11 +12396,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$13,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -12402,11 +12442,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$13,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -12448,11 +12488,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$13,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -12494,11 +12534,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$13,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -12540,11 +12580,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$13,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -12586,11 +12626,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$13,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -12632,11 +12672,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$13,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -12678,11 +12718,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$13,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -12724,11 +12764,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$13,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -12770,11 +12810,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$13,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -12816,11 +12856,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$13,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -12862,11 +12902,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$13,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -12908,11 +12948,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$13,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -12954,11 +12994,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$13,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -13000,11 +13040,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$13,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -13046,11 +13086,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$13,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -13092,11 +13132,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$13,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -13138,11 +13178,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$13,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -13184,11 +13224,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$13,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -13230,11 +13270,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$13,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -13276,11 +13316,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$13,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -13322,11 +13362,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$13,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -13368,11 +13408,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$13,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -13414,11 +13454,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$13,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -13460,11 +13500,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$13,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -13506,11 +13546,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$13,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -13552,11 +13592,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$13,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -13598,11 +13638,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$13,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -13644,11 +13684,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$13,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -13690,11 +13730,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$13,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -13736,11 +13776,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$13,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -13782,11 +13822,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$13,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -13828,11 +13868,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$13,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -13874,11 +13914,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$13,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -13920,11 +13960,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$13,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -13966,11 +14006,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$13,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -14012,11 +14052,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$13,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -14058,11 +14098,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$13,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -14104,11 +14144,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$13,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -14150,11 +14190,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$13,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -14196,11 +14236,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$13,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -14242,11 +14282,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$13,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -14288,11 +14328,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$13,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -14334,11 +14374,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$13,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -14380,11 +14420,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$13,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -14426,11 +14466,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$13,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -14472,11 +14512,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$13,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -14518,11 +14558,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$13,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -14564,11 +14604,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$13,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -14610,11 +14650,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$13,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -14656,11 +14696,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$13,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -14702,11 +14742,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$13,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -14748,11 +14788,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$13,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -14794,11 +14834,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$13,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -14840,11 +14880,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$13,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -14886,11 +14926,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$13,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -14932,11 +14972,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$13,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -14978,11 +15018,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$13,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -15024,11 +15064,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$13,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -15070,11 +15110,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$13,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -15116,11 +15156,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$13,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -15162,11 +15202,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$13,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -15208,11 +15248,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$13,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -15254,11 +15294,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$13,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -15300,11 +15340,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$13,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -15346,11 +15386,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$13,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">
@@ -15581,11 +15621,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$14,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$14,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -15631,11 +15671,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$14,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$14,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -15677,11 +15717,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$14,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$14,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -15723,11 +15763,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$14,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$14,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -15769,11 +15809,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$14,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$14,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -15815,11 +15855,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$14,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$14,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -15861,11 +15901,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$14,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$14,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -15907,11 +15947,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$14,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$14,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -15953,11 +15993,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$14,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$14,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -15999,11 +16039,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$14,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$14,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -16045,11 +16085,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$14,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$14,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -16091,11 +16131,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$14,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$14,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -16137,11 +16177,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$14,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$14,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -16183,11 +16223,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$14,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$14,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -16229,11 +16269,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$14,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$14,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -16275,11 +16315,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$14,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$14,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -16321,11 +16361,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$14,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$14,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -16367,11 +16407,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$14,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$14,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -16413,11 +16453,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$14,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$14,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -16459,11 +16499,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$14,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$14,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -16505,11 +16545,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$14,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$14,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -16551,11 +16591,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$14,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$14,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -16597,11 +16637,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$14,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$14,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -16643,11 +16683,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$14,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$14,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -16689,11 +16729,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$14,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$14,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -16735,11 +16775,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$14,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$14,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -16781,11 +16821,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$14,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$14,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -16827,11 +16867,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$14,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$14,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -16873,11 +16913,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$14,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$14,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -16919,11 +16959,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$14,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$14,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -16965,11 +17005,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$14,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$14,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -17011,11 +17051,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$14,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$14,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -17057,11 +17097,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$14,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$14,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -17103,11 +17143,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$14,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$14,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -17149,11 +17189,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$14,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$14,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -17195,11 +17235,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$14,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$14,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -17241,11 +17281,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$14,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$14,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -17287,11 +17327,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$14,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$14,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -17333,11 +17373,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$14,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$14,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -17379,11 +17419,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$14,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$14,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -17425,11 +17465,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$14,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$14,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -17471,11 +17511,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$14,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$14,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -17517,11 +17557,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$14,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$14,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -17563,11 +17603,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$14,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$14,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -17609,11 +17649,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$14,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$14,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -17655,11 +17695,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$14,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$14,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -17701,11 +17741,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$14,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$14,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -17747,11 +17787,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$14,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$14,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -17793,11 +17833,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$14,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$14,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -17839,11 +17879,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$14,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$14,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -17885,11 +17925,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$14,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$14,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -17931,11 +17971,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$14,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$14,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -17977,11 +18017,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$14,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$14,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -18023,11 +18063,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$14,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$14,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -18069,11 +18109,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$14,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$14,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -18115,11 +18155,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$14,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$14,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -18161,11 +18201,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$14,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$14,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -18207,11 +18247,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$14,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$14,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -18253,11 +18293,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$14,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$14,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -18299,11 +18339,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$14,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$14,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -18345,11 +18385,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$14,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$14,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -18391,11 +18431,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$14,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$14,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -18437,11 +18477,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$14,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$14,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -18483,11 +18523,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$14,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$14,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -18529,11 +18569,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$14,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$14,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -18575,11 +18615,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$14,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$14,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -18621,11 +18661,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$14,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$14,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -18667,11 +18707,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$14,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$14,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -18713,11 +18753,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$14,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$14,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -18759,11 +18799,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$14,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$14,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -18805,11 +18845,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$14,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$14,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -18851,11 +18891,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$14,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$14,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -18897,11 +18937,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$14,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$14,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -18943,11 +18983,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$14,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$14,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -18989,11 +19029,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$14,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$14,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -19035,11 +19075,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$14,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$14,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -19081,11 +19121,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$14,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$14,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -19127,11 +19167,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$14,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$14,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -19173,11 +19213,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$14,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$14,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -19219,11 +19259,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$14,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$14,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -19265,11 +19305,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$14,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$14,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -19311,11 +19351,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$14,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$14,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -19357,11 +19397,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$14,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$14,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -19403,11 +19443,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$14,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$14,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -19449,11 +19489,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$14,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$14,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -19495,11 +19535,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$14,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$14,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -19541,11 +19581,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$14,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$14,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -19587,11 +19627,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$14,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$14,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -19633,11 +19673,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$14,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$14,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -19679,11 +19719,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$14,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$14,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -19725,11 +19765,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$14,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$14,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -19771,11 +19811,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$14,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$14,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -19817,11 +19857,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$14,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$14,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -19863,11 +19903,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$14,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$14,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -19909,11 +19949,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$14,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$14,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -19955,11 +19995,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$14,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$14,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -20001,11 +20041,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$14,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$14,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -20047,11 +20087,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$14,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$14,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -20093,11 +20133,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$14,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$14,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -20139,11 +20179,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$14,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$14,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">
@@ -20374,11 +20414,11 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,-H5,C5-H5),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$15,-H5,C5-H5),"")</f>
         <v/>
       </c>
       <c r="J5" s="29">
-        <f>IFERROR(IF(F5&gt;=参数配置!$C$12,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F5&gt;=参数配置!$C$15,"全仓清仓",IF(H5&gt;C5,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K5" s="30">
@@ -20424,11 +20464,11 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,-H6,C6-H6),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$15,-H6,C6-H6),"")</f>
         <v/>
       </c>
       <c r="J6" s="29">
-        <f>IFERROR(IF(F6&gt;=参数配置!$C$12,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F6&gt;=参数配置!$C$15,"全仓清仓",IF(H6&gt;C6,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K6" s="30">
@@ -20470,11 +20510,11 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,-H7,C7-H7),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$15,-H7,C7-H7),"")</f>
         <v/>
       </c>
       <c r="J7" s="29">
-        <f>IFERROR(IF(F7&gt;=参数配置!$C$12,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F7&gt;=参数配置!$C$15,"全仓清仓",IF(H7&gt;C7,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K7" s="30">
@@ -20516,11 +20556,11 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,-H8,C8-H8),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$15,-H8,C8-H8),"")</f>
         <v/>
       </c>
       <c r="J8" s="29">
-        <f>IFERROR(IF(F8&gt;=参数配置!$C$12,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F8&gt;=参数配置!$C$15,"全仓清仓",IF(H8&gt;C8,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K8" s="30">
@@ -20562,11 +20602,11 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,-H9,C9-H9),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$15,-H9,C9-H9),"")</f>
         <v/>
       </c>
       <c r="J9" s="29">
-        <f>IFERROR(IF(F9&gt;=参数配置!$C$12,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F9&gt;=参数配置!$C$15,"全仓清仓",IF(H9&gt;C9,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K9" s="30">
@@ -20608,11 +20648,11 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,-H10,C10-H10),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$15,-H10,C10-H10),"")</f>
         <v/>
       </c>
       <c r="J10" s="29">
-        <f>IFERROR(IF(F10&gt;=参数配置!$C$12,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F10&gt;=参数配置!$C$15,"全仓清仓",IF(H10&gt;C10,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K10" s="30">
@@ -20654,11 +20694,11 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,-H11,C11-H11),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$15,-H11,C11-H11),"")</f>
         <v/>
       </c>
       <c r="J11" s="29">
-        <f>IFERROR(IF(F11&gt;=参数配置!$C$12,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F11&gt;=参数配置!$C$15,"全仓清仓",IF(H11&gt;C11,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K11" s="30">
@@ -20700,11 +20740,11 @@
         <v/>
       </c>
       <c r="I12" s="7">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,-H12,C12-H12),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$15,-H12,C12-H12),"")</f>
         <v/>
       </c>
       <c r="J12" s="29">
-        <f>IFERROR(IF(F12&gt;=参数配置!$C$12,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F12&gt;=参数配置!$C$15,"全仓清仓",IF(H12&gt;C12,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K12" s="30">
@@ -20746,11 +20786,11 @@
         <v/>
       </c>
       <c r="I13" s="7">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,-H13,C13-H13),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$15,-H13,C13-H13),"")</f>
         <v/>
       </c>
       <c r="J13" s="29">
-        <f>IFERROR(IF(F13&gt;=参数配置!$C$12,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F13&gt;=参数配置!$C$15,"全仓清仓",IF(H13&gt;C13,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K13" s="30">
@@ -20792,11 +20832,11 @@
         <v/>
       </c>
       <c r="I14" s="7">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,-H14,C14-H14),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$15,-H14,C14-H14),"")</f>
         <v/>
       </c>
       <c r="J14" s="29">
-        <f>IFERROR(IF(F14&gt;=参数配置!$C$12,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F14&gt;=参数配置!$C$15,"全仓清仓",IF(H14&gt;C14,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K14" s="30">
@@ -20838,11 +20878,11 @@
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,-H15,C15-H15),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$15,-H15,C15-H15),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
-        <f>IFERROR(IF(F15&gt;=参数配置!$C$12,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F15&gt;=参数配置!$C$15,"全仓清仓",IF(H15&gt;C15,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K15" s="30">
@@ -20884,11 +20924,11 @@
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,-H16,C16-H16),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$15,-H16,C16-H16),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
-        <f>IFERROR(IF(F16&gt;=参数配置!$C$12,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F16&gt;=参数配置!$C$15,"全仓清仓",IF(H16&gt;C16,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K16" s="30">
@@ -20930,11 +20970,11 @@
         <v/>
       </c>
       <c r="I17" s="7">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,-H17,C17-H17),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$15,-H17,C17-H17),"")</f>
         <v/>
       </c>
       <c r="J17" s="29">
-        <f>IFERROR(IF(F17&gt;=参数配置!$C$12,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F17&gt;=参数配置!$C$15,"全仓清仓",IF(H17&gt;C17,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K17" s="30">
@@ -20976,11 +21016,11 @@
         <v/>
       </c>
       <c r="I18" s="7">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,-H18,C18-H18),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$15,-H18,C18-H18),"")</f>
         <v/>
       </c>
       <c r="J18" s="29">
-        <f>IFERROR(IF(F18&gt;=参数配置!$C$12,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F18&gt;=参数配置!$C$15,"全仓清仓",IF(H18&gt;C18,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K18" s="30">
@@ -21022,11 +21062,11 @@
         <v/>
       </c>
       <c r="I19" s="7">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,-H19,C19-H19),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$15,-H19,C19-H19),"")</f>
         <v/>
       </c>
       <c r="J19" s="29">
-        <f>IFERROR(IF(F19&gt;=参数配置!$C$12,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F19&gt;=参数配置!$C$15,"全仓清仓",IF(H19&gt;C19,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K19" s="30">
@@ -21068,11 +21108,11 @@
         <v/>
       </c>
       <c r="I20" s="7">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,-H20,C20-H20),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$15,-H20,C20-H20),"")</f>
         <v/>
       </c>
       <c r="J20" s="29">
-        <f>IFERROR(IF(F20&gt;=参数配置!$C$12,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F20&gt;=参数配置!$C$15,"全仓清仓",IF(H20&gt;C20,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K20" s="30">
@@ -21114,11 +21154,11 @@
         <v/>
       </c>
       <c r="I21" s="7">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,-H21,C21-H21),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$15,-H21,C21-H21),"")</f>
         <v/>
       </c>
       <c r="J21" s="29">
-        <f>IFERROR(IF(F21&gt;=参数配置!$C$12,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F21&gt;=参数配置!$C$15,"全仓清仓",IF(H21&gt;C21,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K21" s="30">
@@ -21160,11 +21200,11 @@
         <v/>
       </c>
       <c r="I22" s="7">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,-H22,C22-H22),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$15,-H22,C22-H22),"")</f>
         <v/>
       </c>
       <c r="J22" s="29">
-        <f>IFERROR(IF(F22&gt;=参数配置!$C$12,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F22&gt;=参数配置!$C$15,"全仓清仓",IF(H22&gt;C22,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K22" s="30">
@@ -21206,11 +21246,11 @@
         <v/>
       </c>
       <c r="I23" s="7">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,-H23,C23-H23),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$15,-H23,C23-H23),"")</f>
         <v/>
       </c>
       <c r="J23" s="29">
-        <f>IFERROR(IF(F23&gt;=参数配置!$C$12,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F23&gt;=参数配置!$C$15,"全仓清仓",IF(H23&gt;C23,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K23" s="30">
@@ -21252,11 +21292,11 @@
         <v/>
       </c>
       <c r="I24" s="7">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,-H24,C24-H24),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$15,-H24,C24-H24),"")</f>
         <v/>
       </c>
       <c r="J24" s="29">
-        <f>IFERROR(IF(F24&gt;=参数配置!$C$12,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F24&gt;=参数配置!$C$15,"全仓清仓",IF(H24&gt;C24,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K24" s="30">
@@ -21298,11 +21338,11 @@
         <v/>
       </c>
       <c r="I25" s="7">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,-H25,C25-H25),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$15,-H25,C25-H25),"")</f>
         <v/>
       </c>
       <c r="J25" s="29">
-        <f>IFERROR(IF(F25&gt;=参数配置!$C$12,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F25&gt;=参数配置!$C$15,"全仓清仓",IF(H25&gt;C25,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K25" s="30">
@@ -21344,11 +21384,11 @@
         <v/>
       </c>
       <c r="I26" s="7">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,-H26,C26-H26),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$15,-H26,C26-H26),"")</f>
         <v/>
       </c>
       <c r="J26" s="29">
-        <f>IFERROR(IF(F26&gt;=参数配置!$C$12,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F26&gt;=参数配置!$C$15,"全仓清仓",IF(H26&gt;C26,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K26" s="30">
@@ -21390,11 +21430,11 @@
         <v/>
       </c>
       <c r="I27" s="7">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,-H27,C27-H27),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$15,-H27,C27-H27),"")</f>
         <v/>
       </c>
       <c r="J27" s="29">
-        <f>IFERROR(IF(F27&gt;=参数配置!$C$12,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F27&gt;=参数配置!$C$15,"全仓清仓",IF(H27&gt;C27,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K27" s="30">
@@ -21436,11 +21476,11 @@
         <v/>
       </c>
       <c r="I28" s="7">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,-H28,C28-H28),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$15,-H28,C28-H28),"")</f>
         <v/>
       </c>
       <c r="J28" s="29">
-        <f>IFERROR(IF(F28&gt;=参数配置!$C$12,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F28&gt;=参数配置!$C$15,"全仓清仓",IF(H28&gt;C28,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K28" s="30">
@@ -21482,11 +21522,11 @@
         <v/>
       </c>
       <c r="I29" s="7">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,-H29,C29-H29),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$15,-H29,C29-H29),"")</f>
         <v/>
       </c>
       <c r="J29" s="29">
-        <f>IFERROR(IF(F29&gt;=参数配置!$C$12,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F29&gt;=参数配置!$C$15,"全仓清仓",IF(H29&gt;C29,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K29" s="30">
@@ -21528,11 +21568,11 @@
         <v/>
       </c>
       <c r="I30" s="7">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,-H30,C30-H30),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$15,-H30,C30-H30),"")</f>
         <v/>
       </c>
       <c r="J30" s="29">
-        <f>IFERROR(IF(F30&gt;=参数配置!$C$12,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F30&gt;=参数配置!$C$15,"全仓清仓",IF(H30&gt;C30,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K30" s="30">
@@ -21574,11 +21614,11 @@
         <v/>
       </c>
       <c r="I31" s="7">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,-H31,C31-H31),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$15,-H31,C31-H31),"")</f>
         <v/>
       </c>
       <c r="J31" s="29">
-        <f>IFERROR(IF(F31&gt;=参数配置!$C$12,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F31&gt;=参数配置!$C$15,"全仓清仓",IF(H31&gt;C31,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K31" s="30">
@@ -21620,11 +21660,11 @@
         <v/>
       </c>
       <c r="I32" s="7">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,-H32,C32-H32),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$15,-H32,C32-H32),"")</f>
         <v/>
       </c>
       <c r="J32" s="29">
-        <f>IFERROR(IF(F32&gt;=参数配置!$C$12,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F32&gt;=参数配置!$C$15,"全仓清仓",IF(H32&gt;C32,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K32" s="30">
@@ -21666,11 +21706,11 @@
         <v/>
       </c>
       <c r="I33" s="7">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,-H33,C33-H33),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$15,-H33,C33-H33),"")</f>
         <v/>
       </c>
       <c r="J33" s="29">
-        <f>IFERROR(IF(F33&gt;=参数配置!$C$12,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F33&gt;=参数配置!$C$15,"全仓清仓",IF(H33&gt;C33,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K33" s="30">
@@ -21712,11 +21752,11 @@
         <v/>
       </c>
       <c r="I34" s="7">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,-H34,C34-H34),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$15,-H34,C34-H34),"")</f>
         <v/>
       </c>
       <c r="J34" s="29">
-        <f>IFERROR(IF(F34&gt;=参数配置!$C$12,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F34&gt;=参数配置!$C$15,"全仓清仓",IF(H34&gt;C34,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K34" s="30">
@@ -21758,11 +21798,11 @@
         <v/>
       </c>
       <c r="I35" s="7">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,-H35,C35-H35),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$15,-H35,C35-H35),"")</f>
         <v/>
       </c>
       <c r="J35" s="29">
-        <f>IFERROR(IF(F35&gt;=参数配置!$C$12,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F35&gt;=参数配置!$C$15,"全仓清仓",IF(H35&gt;C35,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K35" s="30">
@@ -21804,11 +21844,11 @@
         <v/>
       </c>
       <c r="I36" s="7">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,-H36,C36-H36),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$15,-H36,C36-H36),"")</f>
         <v/>
       </c>
       <c r="J36" s="29">
-        <f>IFERROR(IF(F36&gt;=参数配置!$C$12,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F36&gt;=参数配置!$C$15,"全仓清仓",IF(H36&gt;C36,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K36" s="30">
@@ -21850,11 +21890,11 @@
         <v/>
       </c>
       <c r="I37" s="7">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,-H37,C37-H37),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$15,-H37,C37-H37),"")</f>
         <v/>
       </c>
       <c r="J37" s="29">
-        <f>IFERROR(IF(F37&gt;=参数配置!$C$12,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F37&gt;=参数配置!$C$15,"全仓清仓",IF(H37&gt;C37,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K37" s="30">
@@ -21896,11 +21936,11 @@
         <v/>
       </c>
       <c r="I38" s="7">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,-H38,C38-H38),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$15,-H38,C38-H38),"")</f>
         <v/>
       </c>
       <c r="J38" s="29">
-        <f>IFERROR(IF(F38&gt;=参数配置!$C$12,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F38&gt;=参数配置!$C$15,"全仓清仓",IF(H38&gt;C38,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K38" s="30">
@@ -21942,11 +21982,11 @@
         <v/>
       </c>
       <c r="I39" s="7">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,-H39,C39-H39),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$15,-H39,C39-H39),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
-        <f>IFERROR(IF(F39&gt;=参数配置!$C$12,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F39&gt;=参数配置!$C$15,"全仓清仓",IF(H39&gt;C39,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K39" s="30">
@@ -21988,11 +22028,11 @@
         <v/>
       </c>
       <c r="I40" s="7">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,-H40,C40-H40),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$15,-H40,C40-H40),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
-        <f>IFERROR(IF(F40&gt;=参数配置!$C$12,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F40&gt;=参数配置!$C$15,"全仓清仓",IF(H40&gt;C40,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K40" s="30">
@@ -22034,11 +22074,11 @@
         <v/>
       </c>
       <c r="I41" s="7">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,-H41,C41-H41),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$15,-H41,C41-H41),"")</f>
         <v/>
       </c>
       <c r="J41" s="29">
-        <f>IFERROR(IF(F41&gt;=参数配置!$C$12,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F41&gt;=参数配置!$C$15,"全仓清仓",IF(H41&gt;C41,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K41" s="30">
@@ -22080,11 +22120,11 @@
         <v/>
       </c>
       <c r="I42" s="7">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,-H42,C42-H42),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$15,-H42,C42-H42),"")</f>
         <v/>
       </c>
       <c r="J42" s="29">
-        <f>IFERROR(IF(F42&gt;=参数配置!$C$12,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F42&gt;=参数配置!$C$15,"全仓清仓",IF(H42&gt;C42,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K42" s="30">
@@ -22126,11 +22166,11 @@
         <v/>
       </c>
       <c r="I43" s="7">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,-H43,C43-H43),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$15,-H43,C43-H43),"")</f>
         <v/>
       </c>
       <c r="J43" s="29">
-        <f>IFERROR(IF(F43&gt;=参数配置!$C$12,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F43&gt;=参数配置!$C$15,"全仓清仓",IF(H43&gt;C43,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K43" s="30">
@@ -22172,11 +22212,11 @@
         <v/>
       </c>
       <c r="I44" s="7">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,-H44,C44-H44),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$15,-H44,C44-H44),"")</f>
         <v/>
       </c>
       <c r="J44" s="29">
-        <f>IFERROR(IF(F44&gt;=参数配置!$C$12,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F44&gt;=参数配置!$C$15,"全仓清仓",IF(H44&gt;C44,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K44" s="30">
@@ -22218,11 +22258,11 @@
         <v/>
       </c>
       <c r="I45" s="7">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,-H45,C45-H45),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$15,-H45,C45-H45),"")</f>
         <v/>
       </c>
       <c r="J45" s="29">
-        <f>IFERROR(IF(F45&gt;=参数配置!$C$12,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F45&gt;=参数配置!$C$15,"全仓清仓",IF(H45&gt;C45,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K45" s="30">
@@ -22264,11 +22304,11 @@
         <v/>
       </c>
       <c r="I46" s="7">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,-H46,C46-H46),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$15,-H46,C46-H46),"")</f>
         <v/>
       </c>
       <c r="J46" s="29">
-        <f>IFERROR(IF(F46&gt;=参数配置!$C$12,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F46&gt;=参数配置!$C$15,"全仓清仓",IF(H46&gt;C46,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K46" s="30">
@@ -22310,11 +22350,11 @@
         <v/>
       </c>
       <c r="I47" s="7">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,-H47,C47-H47),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$15,-H47,C47-H47),"")</f>
         <v/>
       </c>
       <c r="J47" s="29">
-        <f>IFERROR(IF(F47&gt;=参数配置!$C$12,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F47&gt;=参数配置!$C$15,"全仓清仓",IF(H47&gt;C47,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K47" s="30">
@@ -22356,11 +22396,11 @@
         <v/>
       </c>
       <c r="I48" s="7">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,-H48,C48-H48),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$15,-H48,C48-H48),"")</f>
         <v/>
       </c>
       <c r="J48" s="29">
-        <f>IFERROR(IF(F48&gt;=参数配置!$C$12,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F48&gt;=参数配置!$C$15,"全仓清仓",IF(H48&gt;C48,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K48" s="30">
@@ -22402,11 +22442,11 @@
         <v/>
       </c>
       <c r="I49" s="7">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,-H49,C49-H49),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$15,-H49,C49-H49),"")</f>
         <v/>
       </c>
       <c r="J49" s="29">
-        <f>IFERROR(IF(F49&gt;=参数配置!$C$12,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F49&gt;=参数配置!$C$15,"全仓清仓",IF(H49&gt;C49,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K49" s="30">
@@ -22448,11 +22488,11 @@
         <v/>
       </c>
       <c r="I50" s="7">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,-H50,C50-H50),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$15,-H50,C50-H50),"")</f>
         <v/>
       </c>
       <c r="J50" s="29">
-        <f>IFERROR(IF(F50&gt;=参数配置!$C$12,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F50&gt;=参数配置!$C$15,"全仓清仓",IF(H50&gt;C50,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K50" s="30">
@@ -22494,11 +22534,11 @@
         <v/>
       </c>
       <c r="I51" s="7">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,-H51,C51-H51),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$15,-H51,C51-H51),"")</f>
         <v/>
       </c>
       <c r="J51" s="29">
-        <f>IFERROR(IF(F51&gt;=参数配置!$C$12,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F51&gt;=参数配置!$C$15,"全仓清仓",IF(H51&gt;C51,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K51" s="30">
@@ -22540,11 +22580,11 @@
         <v/>
       </c>
       <c r="I52" s="7">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,-H52,C52-H52),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$15,-H52,C52-H52),"")</f>
         <v/>
       </c>
       <c r="J52" s="29">
-        <f>IFERROR(IF(F52&gt;=参数配置!$C$12,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F52&gt;=参数配置!$C$15,"全仓清仓",IF(H52&gt;C52,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K52" s="30">
@@ -22586,11 +22626,11 @@
         <v/>
       </c>
       <c r="I53" s="7">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,-H53,C53-H53),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$15,-H53,C53-H53),"")</f>
         <v/>
       </c>
       <c r="J53" s="29">
-        <f>IFERROR(IF(F53&gt;=参数配置!$C$12,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F53&gt;=参数配置!$C$15,"全仓清仓",IF(H53&gt;C53,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K53" s="30">
@@ -22632,11 +22672,11 @@
         <v/>
       </c>
       <c r="I54" s="7">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,-H54,C54-H54),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$15,-H54,C54-H54),"")</f>
         <v/>
       </c>
       <c r="J54" s="29">
-        <f>IFERROR(IF(F54&gt;=参数配置!$C$12,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F54&gt;=参数配置!$C$15,"全仓清仓",IF(H54&gt;C54,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K54" s="30">
@@ -22678,11 +22718,11 @@
         <v/>
       </c>
       <c r="I55" s="7">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,-H55,C55-H55),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$15,-H55,C55-H55),"")</f>
         <v/>
       </c>
       <c r="J55" s="29">
-        <f>IFERROR(IF(F55&gt;=参数配置!$C$12,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F55&gt;=参数配置!$C$15,"全仓清仓",IF(H55&gt;C55,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K55" s="30">
@@ -22724,11 +22764,11 @@
         <v/>
       </c>
       <c r="I56" s="7">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,-H56,C56-H56),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$15,-H56,C56-H56),"")</f>
         <v/>
       </c>
       <c r="J56" s="29">
-        <f>IFERROR(IF(F56&gt;=参数配置!$C$12,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F56&gt;=参数配置!$C$15,"全仓清仓",IF(H56&gt;C56,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K56" s="30">
@@ -22770,11 +22810,11 @@
         <v/>
       </c>
       <c r="I57" s="7">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,-H57,C57-H57),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$15,-H57,C57-H57),"")</f>
         <v/>
       </c>
       <c r="J57" s="29">
-        <f>IFERROR(IF(F57&gt;=参数配置!$C$12,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F57&gt;=参数配置!$C$15,"全仓清仓",IF(H57&gt;C57,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K57" s="30">
@@ -22816,11 +22856,11 @@
         <v/>
       </c>
       <c r="I58" s="7">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,-H58,C58-H58),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$15,-H58,C58-H58),"")</f>
         <v/>
       </c>
       <c r="J58" s="29">
-        <f>IFERROR(IF(F58&gt;=参数配置!$C$12,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F58&gt;=参数配置!$C$15,"全仓清仓",IF(H58&gt;C58,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K58" s="30">
@@ -22862,11 +22902,11 @@
         <v/>
       </c>
       <c r="I59" s="7">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,-H59,C59-H59),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$15,-H59,C59-H59),"")</f>
         <v/>
       </c>
       <c r="J59" s="29">
-        <f>IFERROR(IF(F59&gt;=参数配置!$C$12,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F59&gt;=参数配置!$C$15,"全仓清仓",IF(H59&gt;C59,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K59" s="30">
@@ -22908,11 +22948,11 @@
         <v/>
       </c>
       <c r="I60" s="7">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,-H60,C60-H60),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$15,-H60,C60-H60),"")</f>
         <v/>
       </c>
       <c r="J60" s="29">
-        <f>IFERROR(IF(F60&gt;=参数配置!$C$12,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F60&gt;=参数配置!$C$15,"全仓清仓",IF(H60&gt;C60,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K60" s="30">
@@ -22954,11 +22994,11 @@
         <v/>
       </c>
       <c r="I61" s="7">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,-H61,C61-H61),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$15,-H61,C61-H61),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
-        <f>IFERROR(IF(F61&gt;=参数配置!$C$12,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F61&gt;=参数配置!$C$15,"全仓清仓",IF(H61&gt;C61,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K61" s="30">
@@ -23000,11 +23040,11 @@
         <v/>
       </c>
       <c r="I62" s="7">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,-H62,C62-H62),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$15,-H62,C62-H62),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
-        <f>IFERROR(IF(F62&gt;=参数配置!$C$12,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F62&gt;=参数配置!$C$15,"全仓清仓",IF(H62&gt;C62,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K62" s="30">
@@ -23046,11 +23086,11 @@
         <v/>
       </c>
       <c r="I63" s="7">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,-H63,C63-H63),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$15,-H63,C63-H63),"")</f>
         <v/>
       </c>
       <c r="J63" s="29">
-        <f>IFERROR(IF(F63&gt;=参数配置!$C$12,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F63&gt;=参数配置!$C$15,"全仓清仓",IF(H63&gt;C63,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K63" s="30">
@@ -23092,11 +23132,11 @@
         <v/>
       </c>
       <c r="I64" s="7">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,-H64,C64-H64),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$15,-H64,C64-H64),"")</f>
         <v/>
       </c>
       <c r="J64" s="29">
-        <f>IFERROR(IF(F64&gt;=参数配置!$C$12,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F64&gt;=参数配置!$C$15,"全仓清仓",IF(H64&gt;C64,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K64" s="30">
@@ -23138,11 +23178,11 @@
         <v/>
       </c>
       <c r="I65" s="7">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,-H65,C65-H65),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$15,-H65,C65-H65),"")</f>
         <v/>
       </c>
       <c r="J65" s="29">
-        <f>IFERROR(IF(F65&gt;=参数配置!$C$12,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F65&gt;=参数配置!$C$15,"全仓清仓",IF(H65&gt;C65,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K65" s="30">
@@ -23184,11 +23224,11 @@
         <v/>
       </c>
       <c r="I66" s="7">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,-H66,C66-H66),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$15,-H66,C66-H66),"")</f>
         <v/>
       </c>
       <c r="J66" s="29">
-        <f>IFERROR(IF(F66&gt;=参数配置!$C$12,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F66&gt;=参数配置!$C$15,"全仓清仓",IF(H66&gt;C66,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K66" s="30">
@@ -23230,11 +23270,11 @@
         <v/>
       </c>
       <c r="I67" s="7">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,-H67,C67-H67),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$15,-H67,C67-H67),"")</f>
         <v/>
       </c>
       <c r="J67" s="29">
-        <f>IFERROR(IF(F67&gt;=参数配置!$C$12,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F67&gt;=参数配置!$C$15,"全仓清仓",IF(H67&gt;C67,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K67" s="30">
@@ -23276,11 +23316,11 @@
         <v/>
       </c>
       <c r="I68" s="7">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,-H68,C68-H68),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$15,-H68,C68-H68),"")</f>
         <v/>
       </c>
       <c r="J68" s="29">
-        <f>IFERROR(IF(F68&gt;=参数配置!$C$12,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F68&gt;=参数配置!$C$15,"全仓清仓",IF(H68&gt;C68,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K68" s="30">
@@ -23322,11 +23362,11 @@
         <v/>
       </c>
       <c r="I69" s="7">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,-H69,C69-H69),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$15,-H69,C69-H69),"")</f>
         <v/>
       </c>
       <c r="J69" s="29">
-        <f>IFERROR(IF(F69&gt;=参数配置!$C$12,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F69&gt;=参数配置!$C$15,"全仓清仓",IF(H69&gt;C69,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K69" s="30">
@@ -23368,11 +23408,11 @@
         <v/>
       </c>
       <c r="I70" s="7">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,-H70,C70-H70),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$15,-H70,C70-H70),"")</f>
         <v/>
       </c>
       <c r="J70" s="29">
-        <f>IFERROR(IF(F70&gt;=参数配置!$C$12,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F70&gt;=参数配置!$C$15,"全仓清仓",IF(H70&gt;C70,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K70" s="30">
@@ -23414,11 +23454,11 @@
         <v/>
       </c>
       <c r="I71" s="7">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,-H71,C71-H71),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$15,-H71,C71-H71),"")</f>
         <v/>
       </c>
       <c r="J71" s="29">
-        <f>IFERROR(IF(F71&gt;=参数配置!$C$12,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F71&gt;=参数配置!$C$15,"全仓清仓",IF(H71&gt;C71,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K71" s="30">
@@ -23460,11 +23500,11 @@
         <v/>
       </c>
       <c r="I72" s="7">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,-H72,C72-H72),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$15,-H72,C72-H72),"")</f>
         <v/>
       </c>
       <c r="J72" s="29">
-        <f>IFERROR(IF(F72&gt;=参数配置!$C$12,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F72&gt;=参数配置!$C$15,"全仓清仓",IF(H72&gt;C72,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K72" s="30">
@@ -23506,11 +23546,11 @@
         <v/>
       </c>
       <c r="I73" s="7">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,-H73,C73-H73),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$15,-H73,C73-H73),"")</f>
         <v/>
       </c>
       <c r="J73" s="29">
-        <f>IFERROR(IF(F73&gt;=参数配置!$C$12,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F73&gt;=参数配置!$C$15,"全仓清仓",IF(H73&gt;C73,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K73" s="30">
@@ -23552,11 +23592,11 @@
         <v/>
       </c>
       <c r="I74" s="7">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,-H74,C74-H74),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$15,-H74,C74-H74),"")</f>
         <v/>
       </c>
       <c r="J74" s="29">
-        <f>IFERROR(IF(F74&gt;=参数配置!$C$12,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F74&gt;=参数配置!$C$15,"全仓清仓",IF(H74&gt;C74,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K74" s="30">
@@ -23598,11 +23638,11 @@
         <v/>
       </c>
       <c r="I75" s="7">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,-H75,C75-H75),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$15,-H75,C75-H75),"")</f>
         <v/>
       </c>
       <c r="J75" s="29">
-        <f>IFERROR(IF(F75&gt;=参数配置!$C$12,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F75&gt;=参数配置!$C$15,"全仓清仓",IF(H75&gt;C75,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K75" s="30">
@@ -23644,11 +23684,11 @@
         <v/>
       </c>
       <c r="I76" s="7">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,-H76,C76-H76),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$15,-H76,C76-H76),"")</f>
         <v/>
       </c>
       <c r="J76" s="29">
-        <f>IFERROR(IF(F76&gt;=参数配置!$C$12,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F76&gt;=参数配置!$C$15,"全仓清仓",IF(H76&gt;C76,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K76" s="30">
@@ -23690,11 +23730,11 @@
         <v/>
       </c>
       <c r="I77" s="7">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,-H77,C77-H77),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$15,-H77,C77-H77),"")</f>
         <v/>
       </c>
       <c r="J77" s="29">
-        <f>IFERROR(IF(F77&gt;=参数配置!$C$12,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F77&gt;=参数配置!$C$15,"全仓清仓",IF(H77&gt;C77,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K77" s="30">
@@ -23736,11 +23776,11 @@
         <v/>
       </c>
       <c r="I78" s="7">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,-H78,C78-H78),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$15,-H78,C78-H78),"")</f>
         <v/>
       </c>
       <c r="J78" s="29">
-        <f>IFERROR(IF(F78&gt;=参数配置!$C$12,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F78&gt;=参数配置!$C$15,"全仓清仓",IF(H78&gt;C78,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K78" s="30">
@@ -23782,11 +23822,11 @@
         <v/>
       </c>
       <c r="I79" s="7">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,-H79,C79-H79),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$15,-H79,C79-H79),"")</f>
         <v/>
       </c>
       <c r="J79" s="29">
-        <f>IFERROR(IF(F79&gt;=参数配置!$C$12,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F79&gt;=参数配置!$C$15,"全仓清仓",IF(H79&gt;C79,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K79" s="30">
@@ -23828,11 +23868,11 @@
         <v/>
       </c>
       <c r="I80" s="7">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,-H80,C80-H80),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$15,-H80,C80-H80),"")</f>
         <v/>
       </c>
       <c r="J80" s="29">
-        <f>IFERROR(IF(F80&gt;=参数配置!$C$12,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F80&gt;=参数配置!$C$15,"全仓清仓",IF(H80&gt;C80,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K80" s="30">
@@ -23874,11 +23914,11 @@
         <v/>
       </c>
       <c r="I81" s="7">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,-H81,C81-H81),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$15,-H81,C81-H81),"")</f>
         <v/>
       </c>
       <c r="J81" s="29">
-        <f>IFERROR(IF(F81&gt;=参数配置!$C$12,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F81&gt;=参数配置!$C$15,"全仓清仓",IF(H81&gt;C81,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K81" s="30">
@@ -23920,11 +23960,11 @@
         <v/>
       </c>
       <c r="I82" s="7">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,-H82,C82-H82),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$15,-H82,C82-H82),"")</f>
         <v/>
       </c>
       <c r="J82" s="29">
-        <f>IFERROR(IF(F82&gt;=参数配置!$C$12,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F82&gt;=参数配置!$C$15,"全仓清仓",IF(H82&gt;C82,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K82" s="30">
@@ -23966,11 +24006,11 @@
         <v/>
       </c>
       <c r="I83" s="7">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,-H83,C83-H83),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$15,-H83,C83-H83),"")</f>
         <v/>
       </c>
       <c r="J83" s="29">
-        <f>IFERROR(IF(F83&gt;=参数配置!$C$12,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F83&gt;=参数配置!$C$15,"全仓清仓",IF(H83&gt;C83,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K83" s="30">
@@ -24012,11 +24052,11 @@
         <v/>
       </c>
       <c r="I84" s="7">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,-H84,C84-H84),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$15,-H84,C84-H84),"")</f>
         <v/>
       </c>
       <c r="J84" s="29">
-        <f>IFERROR(IF(F84&gt;=参数配置!$C$12,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F84&gt;=参数配置!$C$15,"全仓清仓",IF(H84&gt;C84,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K84" s="30">
@@ -24058,11 +24098,11 @@
         <v/>
       </c>
       <c r="I85" s="7">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,-H85,C85-H85),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$15,-H85,C85-H85),"")</f>
         <v/>
       </c>
       <c r="J85" s="29">
-        <f>IFERROR(IF(F85&gt;=参数配置!$C$12,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F85&gt;=参数配置!$C$15,"全仓清仓",IF(H85&gt;C85,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K85" s="30">
@@ -24104,11 +24144,11 @@
         <v/>
       </c>
       <c r="I86" s="7">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,-H86,C86-H86),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$15,-H86,C86-H86),"")</f>
         <v/>
       </c>
       <c r="J86" s="29">
-        <f>IFERROR(IF(F86&gt;=参数配置!$C$12,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F86&gt;=参数配置!$C$15,"全仓清仓",IF(H86&gt;C86,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K86" s="30">
@@ -24150,11 +24190,11 @@
         <v/>
       </c>
       <c r="I87" s="7">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,-H87,C87-H87),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$15,-H87,C87-H87),"")</f>
         <v/>
       </c>
       <c r="J87" s="29">
-        <f>IFERROR(IF(F87&gt;=参数配置!$C$12,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F87&gt;=参数配置!$C$15,"全仓清仓",IF(H87&gt;C87,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K87" s="30">
@@ -24196,11 +24236,11 @@
         <v/>
       </c>
       <c r="I88" s="7">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,-H88,C88-H88),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$15,-H88,C88-H88),"")</f>
         <v/>
       </c>
       <c r="J88" s="29">
-        <f>IFERROR(IF(F88&gt;=参数配置!$C$12,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F88&gt;=参数配置!$C$15,"全仓清仓",IF(H88&gt;C88,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K88" s="30">
@@ -24242,11 +24282,11 @@
         <v/>
       </c>
       <c r="I89" s="7">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,-H89,C89-H89),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$15,-H89,C89-H89),"")</f>
         <v/>
       </c>
       <c r="J89" s="29">
-        <f>IFERROR(IF(F89&gt;=参数配置!$C$12,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F89&gt;=参数配置!$C$15,"全仓清仓",IF(H89&gt;C89,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K89" s="30">
@@ -24288,11 +24328,11 @@
         <v/>
       </c>
       <c r="I90" s="7">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,-H90,C90-H90),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$15,-H90,C90-H90),"")</f>
         <v/>
       </c>
       <c r="J90" s="29">
-        <f>IFERROR(IF(F90&gt;=参数配置!$C$12,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F90&gt;=参数配置!$C$15,"全仓清仓",IF(H90&gt;C90,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K90" s="30">
@@ -24334,11 +24374,11 @@
         <v/>
       </c>
       <c r="I91" s="7">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,-H91,C91-H91),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$15,-H91,C91-H91),"")</f>
         <v/>
       </c>
       <c r="J91" s="29">
-        <f>IFERROR(IF(F91&gt;=参数配置!$C$12,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F91&gt;=参数配置!$C$15,"全仓清仓",IF(H91&gt;C91,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K91" s="30">
@@ -24380,11 +24420,11 @@
         <v/>
       </c>
       <c r="I92" s="7">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,-H92,C92-H92),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$15,-H92,C92-H92),"")</f>
         <v/>
       </c>
       <c r="J92" s="29">
-        <f>IFERROR(IF(F92&gt;=参数配置!$C$12,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F92&gt;=参数配置!$C$15,"全仓清仓",IF(H92&gt;C92,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K92" s="30">
@@ -24426,11 +24466,11 @@
         <v/>
       </c>
       <c r="I93" s="7">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,-H93,C93-H93),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$15,-H93,C93-H93),"")</f>
         <v/>
       </c>
       <c r="J93" s="29">
-        <f>IFERROR(IF(F93&gt;=参数配置!$C$12,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F93&gt;=参数配置!$C$15,"全仓清仓",IF(H93&gt;C93,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K93" s="30">
@@ -24472,11 +24512,11 @@
         <v/>
       </c>
       <c r="I94" s="7">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,-H94,C94-H94),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$15,-H94,C94-H94),"")</f>
         <v/>
       </c>
       <c r="J94" s="29">
-        <f>IFERROR(IF(F94&gt;=参数配置!$C$12,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F94&gt;=参数配置!$C$15,"全仓清仓",IF(H94&gt;C94,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K94" s="30">
@@ -24518,11 +24558,11 @@
         <v/>
       </c>
       <c r="I95" s="7">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,-H95,C95-H95),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$15,-H95,C95-H95),"")</f>
         <v/>
       </c>
       <c r="J95" s="29">
-        <f>IFERROR(IF(F95&gt;=参数配置!$C$12,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F95&gt;=参数配置!$C$15,"全仓清仓",IF(H95&gt;C95,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K95" s="30">
@@ -24564,11 +24604,11 @@
         <v/>
       </c>
       <c r="I96" s="7">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,-H96,C96-H96),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$15,-H96,C96-H96),"")</f>
         <v/>
       </c>
       <c r="J96" s="29">
-        <f>IFERROR(IF(F96&gt;=参数配置!$C$12,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F96&gt;=参数配置!$C$15,"全仓清仓",IF(H96&gt;C96,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K96" s="30">
@@ -24610,11 +24650,11 @@
         <v/>
       </c>
       <c r="I97" s="7">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,-H97,C97-H97),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$15,-H97,C97-H97),"")</f>
         <v/>
       </c>
       <c r="J97" s="29">
-        <f>IFERROR(IF(F97&gt;=参数配置!$C$12,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F97&gt;=参数配置!$C$15,"全仓清仓",IF(H97&gt;C97,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K97" s="30">
@@ -24656,11 +24696,11 @@
         <v/>
       </c>
       <c r="I98" s="7">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,-H98,C98-H98),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$15,-H98,C98-H98),"")</f>
         <v/>
       </c>
       <c r="J98" s="29">
-        <f>IFERROR(IF(F98&gt;=参数配置!$C$12,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F98&gt;=参数配置!$C$15,"全仓清仓",IF(H98&gt;C98,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K98" s="30">
@@ -24702,11 +24742,11 @@
         <v/>
       </c>
       <c r="I99" s="7">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,-H99,C99-H99),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$15,-H99,C99-H99),"")</f>
         <v/>
       </c>
       <c r="J99" s="29">
-        <f>IFERROR(IF(F99&gt;=参数配置!$C$12,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F99&gt;=参数配置!$C$15,"全仓清仓",IF(H99&gt;C99,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K99" s="30">
@@ -24748,11 +24788,11 @@
         <v/>
       </c>
       <c r="I100" s="7">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,-H100,C100-H100),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$15,-H100,C100-H100),"")</f>
         <v/>
       </c>
       <c r="J100" s="29">
-        <f>IFERROR(IF(F100&gt;=参数配置!$C$12,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F100&gt;=参数配置!$C$15,"全仓清仓",IF(H100&gt;C100,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K100" s="30">
@@ -24794,11 +24834,11 @@
         <v/>
       </c>
       <c r="I101" s="7">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,-H101,C101-H101),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$15,-H101,C101-H101),"")</f>
         <v/>
       </c>
       <c r="J101" s="29">
-        <f>IFERROR(IF(F101&gt;=参数配置!$C$12,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F101&gt;=参数配置!$C$15,"全仓清仓",IF(H101&gt;C101,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K101" s="30">
@@ -24840,11 +24880,11 @@
         <v/>
       </c>
       <c r="I102" s="7">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,-H102,C102-H102),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$15,-H102,C102-H102),"")</f>
         <v/>
       </c>
       <c r="J102" s="29">
-        <f>IFERROR(IF(F102&gt;=参数配置!$C$12,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F102&gt;=参数配置!$C$15,"全仓清仓",IF(H102&gt;C102,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K102" s="30">
@@ -24886,11 +24926,11 @@
         <v/>
       </c>
       <c r="I103" s="7">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,-H103,C103-H103),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$15,-H103,C103-H103),"")</f>
         <v/>
       </c>
       <c r="J103" s="29">
-        <f>IFERROR(IF(F103&gt;=参数配置!$C$12,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F103&gt;=参数配置!$C$15,"全仓清仓",IF(H103&gt;C103,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K103" s="30">
@@ -24932,11 +24972,11 @@
         <v/>
       </c>
       <c r="I104" s="7">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,-H104,C104-H104),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$15,-H104,C104-H104),"")</f>
         <v/>
       </c>
       <c r="J104" s="29">
-        <f>IFERROR(IF(F104&gt;=参数配置!$C$12,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
+        <f>IFERROR(IF(F104&gt;=参数配置!$C$15,"全仓清仓",IF(H104&gt;C104,"卖出超额","正常定投")),"")</f>
         <v/>
       </c>
       <c r="K104" s="30">

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1098,8 +1098,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="33" t="n"/>
+      <c r="A6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
       <c r="C6" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A6,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1120,7 +1126,9 @@
         <f>IFERROR(IF(M6="增量阶段",H6,SUMPRODUCT(MAX(C6,0),1)+SUMPRODUCT(MAX(D6,0),1)+SUMPRODUCT(MAX(E6,0),1)+SUMPRODUCT(MAX(F6,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H6" s="17" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" s="7">
         <f>IFERROR(MAX(-C6,0)+MAX(-D6,0)+MAX(-E6,0)+MAX(-F6,0),"")</f>
         <v/>
@@ -6067,19 +6075,31 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$5*(B6-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>4.3754</v>
+      </c>
       <c r="F6" s="28">
         <f>IFERROR((D6-E6)/E6,"")</f>
         <v/>
       </c>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="H6" s="7">
         <f>IFERROR(G6*D6,"")</f>
         <v/>
@@ -6096,8 +6116,12 @@
         <f>IFERROR(I6,"")</f>
         <v/>
       </c>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="27" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>1467.9</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N6" s="31">
         <f>IFERROR(G6+M6,"")</f>
         <v/>
@@ -10860,19 +10884,31 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$6*(B6-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27" t="n">
+        <v>8.768000000000001</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>7.1015</v>
+      </c>
       <c r="F6" s="28">
         <f>IFERROR((D6-E6)/E6,"")</f>
         <v/>
       </c>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="H6" s="7">
         <f>IFERROR(G6*D6,"")</f>
         <v/>
@@ -10889,8 +10925,12 @@
         <f>IFERROR(I6,"")</f>
         <v/>
       </c>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="27" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>1753.6</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N6" s="31">
         <f>IFERROR(G6+M6,"")</f>
         <v/>
@@ -15653,19 +15693,31 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$7*(B6-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>1.5441</v>
+      </c>
       <c r="F6" s="28">
         <f>IFERROR((D6-E6)/E6,"")</f>
         <v/>
       </c>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="H6" s="7">
         <f>IFERROR(G6*D6,"")</f>
         <v/>
@@ -15682,8 +15734,12 @@
         <f>IFERROR(I6,"")</f>
         <v/>
       </c>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="27" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>619.2</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>400</v>
+      </c>
       <c r="N6" s="31">
         <f>IFERROR(G6+M6,"")</f>
         <v/>
@@ -20446,19 +20502,31 @@
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" s="7">
         <f>IFERROR(参数配置!$C$8*(B6-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>1.7612</v>
+      </c>
       <c r="F6" s="28">
         <f>IFERROR((D6-E6)/E6,"")</f>
         <v/>
       </c>
-      <c r="G6" s="27" t="n"/>
+      <c r="G6" s="27" t="n">
+        <v>1200</v>
+      </c>
       <c r="H6" s="7">
         <f>IFERROR(G6*D6,"")</f>
         <v/>
@@ -20475,8 +20543,12 @@
         <f>IFERROR(I6,"")</f>
         <v/>
       </c>
-      <c r="L6" s="17" t="n"/>
-      <c r="M6" s="27" t="n"/>
+      <c r="L6" s="17" t="n">
+        <v>2250.6</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="N6" s="31">
         <f>IFERROR(G6+M6,"")</f>
         <v/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1151,8 +1151,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="33" t="n"/>
+      <c r="A7" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="C7" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A7,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1173,7 +1179,9 @@
         <f>IFERROR(IF(M7="增量阶段",H7,SUMPRODUCT(MAX(C7,0),1)+SUMPRODUCT(MAX(D7,0),1)+SUMPRODUCT(MAX(E7,0),1)+SUMPRODUCT(MAX(F7,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H7" s="17" t="n"/>
+      <c r="H7" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" s="7">
         <f>IFERROR(MAX(-C7,0)+MAX(-D7,0)+MAX(-E7,0)+MAX(-F7,0),"")</f>
         <v/>
@@ -6137,19 +6145,31 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$5*(B7-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
+      <c r="D7" s="27" t="n">
+        <v>4.828</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>4.4239</v>
+      </c>
       <c r="F7" s="28">
         <f>IFERROR((D7-E7)/E7,"")</f>
         <v/>
       </c>
-      <c r="G7" s="27" t="n"/>
+      <c r="G7" s="27" t="n">
+        <v>600</v>
+      </c>
       <c r="H7" s="7">
         <f>IFERROR(G7*D7,"")</f>
         <v/>
@@ -6166,8 +6186,12 @@
         <f>IFERROR(I7,"")</f>
         <v/>
       </c>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="27" t="n"/>
+      <c r="L7" s="17" t="n">
+        <v>1448.4</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N7" s="31">
         <f>IFERROR(G7+M7,"")</f>
         <v/>
@@ -10946,19 +10970,31 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$6*(B7-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
+      <c r="D7" s="27" t="n">
+        <v>8.576000000000001</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>7.2287</v>
+      </c>
       <c r="F7" s="28">
         <f>IFERROR((D7-E7)/E7,"")</f>
         <v/>
       </c>
-      <c r="G7" s="27" t="n"/>
+      <c r="G7" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="H7" s="7">
         <f>IFERROR(G7*D7,"")</f>
         <v/>
@@ -10975,8 +11011,12 @@
         <f>IFERROR(I7,"")</f>
         <v/>
       </c>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="27" t="n"/>
+      <c r="L7" s="17" t="n">
+        <v>1715.2</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N7" s="31">
         <f>IFERROR(G7+M7,"")</f>
         <v/>
@@ -15755,19 +15795,31 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$7*(B7-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
+      <c r="D7" s="27" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>1.5507</v>
+      </c>
       <c r="F7" s="28">
         <f>IFERROR((D7-E7)/E7,"")</f>
         <v/>
       </c>
-      <c r="G7" s="27" t="n"/>
+      <c r="G7" s="27" t="n">
+        <v>700</v>
+      </c>
       <c r="H7" s="7">
         <f>IFERROR(G7*D7,"")</f>
         <v/>
@@ -15784,8 +15836,12 @@
         <f>IFERROR(I7,"")</f>
         <v/>
       </c>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="27" t="n"/>
+      <c r="L7" s="17" t="n">
+        <v>752</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>500</v>
+      </c>
       <c r="N7" s="31">
         <f>IFERROR(G7+M7,"")</f>
         <v/>
@@ -20564,19 +20620,31 @@
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>3</v>
+      </c>
       <c r="C7" s="7">
         <f>IFERROR(参数配置!$C$8*(B7-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
+      <c r="D7" s="27" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>1.7868</v>
+      </c>
       <c r="F7" s="28">
         <f>IFERROR((D7-E7)/E7,"")</f>
         <v/>
       </c>
-      <c r="G7" s="27" t="n"/>
+      <c r="G7" s="27" t="n">
+        <v>2300</v>
+      </c>
       <c r="H7" s="7">
         <f>IFERROR(G7*D7,"")</f>
         <v/>
@@ -20593,8 +20661,12 @@
         <f>IFERROR(I7,"")</f>
         <v/>
       </c>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="27" t="n"/>
+      <c r="L7" s="17" t="n">
+        <v>2336.4</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1100</v>
+      </c>
       <c r="N7" s="31">
         <f>IFERROR(G7+M7,"")</f>
         <v/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1204,8 +1204,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="33" t="n"/>
+      <c r="A8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
       <c r="C8" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A8,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1226,7 +1232,9 @@
         <f>IFERROR(IF(M8="增量阶段",H8,SUMPRODUCT(MAX(C8,0),1)+SUMPRODUCT(MAX(D8,0),1)+SUMPRODUCT(MAX(E8,0),1)+SUMPRODUCT(MAX(F8,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H8" s="17" t="n"/>
+      <c r="H8" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" s="7">
         <f>IFERROR(MAX(-C8,0)+MAX(-D8,0)+MAX(-E8,0)+MAX(-F8,0),"")</f>
         <v/>
@@ -6207,19 +6215,31 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$5*(B8-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>4.46819947052002</v>
+      </c>
       <c r="F8" s="28">
         <f>IFERROR((D8-E8)/E8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="27" t="n"/>
+      <c r="G8" s="27" t="n">
+        <v>900</v>
+      </c>
       <c r="H8" s="7">
         <f>IFERROR(G8*D8,"")</f>
         <v/>
@@ -6236,8 +6256,12 @@
         <f>IFERROR(I8,"")</f>
         <v/>
       </c>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="27" t="n"/>
+      <c r="L8" s="17" t="n">
+        <v>1473</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N8" s="31">
         <f>IFERROR(G8+M8,"")</f>
         <v/>
@@ -11032,19 +11056,31 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$6*(B8-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>7.342891065597534</v>
+      </c>
       <c r="F8" s="28">
         <f>IFERROR((D8-E8)/E8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="27" t="n"/>
+      <c r="G8" s="27" t="n">
+        <v>500</v>
+      </c>
       <c r="H8" s="7">
         <f>IFERROR(G8*D8,"")</f>
         <v/>
@@ -11061,8 +11097,12 @@
         <f>IFERROR(I8,"")</f>
         <v/>
       </c>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="27" t="n"/>
+      <c r="L8" s="17" t="n">
+        <v>2499.9</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N8" s="31">
         <f>IFERROR(G8+M8,"")</f>
         <v/>
@@ -15857,19 +15897,31 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$7*(B8-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>1.553168001651764</v>
+      </c>
       <c r="F8" s="28">
         <f>IFERROR((D8-E8)/E8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="27" t="n"/>
+      <c r="G8" s="27" t="n">
+        <v>1200</v>
+      </c>
       <c r="H8" s="7">
         <f>IFERROR(G8*D8,"")</f>
         <v/>
@@ -15886,8 +15938,12 @@
         <f>IFERROR(I8,"")</f>
         <v/>
       </c>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="27" t="n"/>
+      <c r="L8" s="17" t="n">
+        <v>740</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>500</v>
+      </c>
       <c r="N8" s="31">
         <f>IFERROR(G8+M8,"")</f>
         <v/>
@@ -20682,19 +20738,31 @@
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7">
         <f>IFERROR(参数配置!$C$8*(B8-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>1.814727995872498</v>
+      </c>
       <c r="F8" s="28">
         <f>IFERROR((D8-E8)/E8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="27" t="n"/>
+      <c r="G8" s="27" t="n">
+        <v>3400</v>
+      </c>
       <c r="H8" s="7">
         <f>IFERROR(G8*D8,"")</f>
         <v/>
@@ -20711,8 +20779,12 @@
         <f>IFERROR(I8,"")</f>
         <v/>
       </c>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="27" t="n"/>
+      <c r="L8" s="17" t="n">
+        <v>2214</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1000</v>
+      </c>
       <c r="N8" s="31">
         <f>IFERROR(G8+M8,"")</f>
         <v/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="中证500" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1257,8 +1257,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="33" t="n"/>
+      <c r="A9" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
       <c r="C9" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A9,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1279,7 +1285,9 @@
         <f>IFERROR(IF(M9="增量阶段",H9,SUMPRODUCT(MAX(C9,0),1)+SUMPRODUCT(MAX(D9,0),1)+SUMPRODUCT(MAX(E9,0),1)+SUMPRODUCT(MAX(F9,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H9" s="17" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="7">
         <f>IFERROR(MAX(-C9,0)+MAX(-D9,0)+MAX(-E9,0)+MAX(-F9,0),"")</f>
         <v/>
@@ -6277,19 +6285,31 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$5*(B9-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
+        <v>4.975</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>4.46819947052002</v>
+      </c>
       <c r="F9" s="28">
         <f>IFERROR((D9-E9)/E9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n"/>
+      <c r="G9" s="27" t="n">
+        <v>1200</v>
+      </c>
       <c r="H9" s="7">
         <f>IFERROR(G9*D9,"")</f>
         <v/>
@@ -6306,8 +6326,12 @@
         <f>IFERROR(I9,"")</f>
         <v/>
       </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="27" t="n"/>
+      <c r="L9" s="17" t="n">
+        <v>1492.5</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N9" s="31">
         <f>IFERROR(G9+M9,"")</f>
         <v/>
@@ -11118,19 +11142,31 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$6*(B9-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
+        <v>8.797000000000001</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>7.342891065597534</v>
+      </c>
       <c r="F9" s="28">
         <f>IFERROR((D9-E9)/E9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n"/>
+      <c r="G9" s="27" t="n">
+        <v>800</v>
+      </c>
       <c r="H9" s="7">
         <f>IFERROR(G9*D9,"")</f>
         <v/>
@@ -11147,8 +11183,12 @@
         <f>IFERROR(I9,"")</f>
         <v/>
       </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="27" t="n"/>
+      <c r="L9" s="17" t="n">
+        <v>879.7</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="N9" s="31">
         <f>IFERROR(G9+M9,"")</f>
         <v/>
@@ -15959,19 +15999,31 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$7*(B9-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>1.553168001651764</v>
+      </c>
       <c r="F9" s="28">
         <f>IFERROR((D9-E9)/E9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n"/>
+      <c r="G9" s="27" t="n">
+        <v>1700</v>
+      </c>
       <c r="H9" s="7">
         <f>IFERROR(G9*D9,"")</f>
         <v/>
@@ -15988,8 +16040,12 @@
         <f>IFERROR(I9,"")</f>
         <v/>
       </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="27" t="n"/>
+      <c r="L9" s="17" t="n">
+        <v>706</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>500</v>
+      </c>
       <c r="N9" s="31">
         <f>IFERROR(G9+M9,"")</f>
         <v/>
@@ -20800,19 +20856,31 @@
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>5</v>
+      </c>
       <c r="C9" s="7">
         <f>IFERROR(参数配置!$C$8*(B9-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>1.814727995872498</v>
+      </c>
       <c r="F9" s="28">
         <f>IFERROR((D9-E9)/E9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="27" t="n"/>
+      <c r="G9" s="27" t="n">
+        <v>4400</v>
+      </c>
       <c r="H9" s="7">
         <f>IFERROR(G9*D9,"")</f>
         <v/>
@@ -20829,8 +20897,12 @@
         <f>IFERROR(I9,"")</f>
         <v/>
       </c>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="27" t="n"/>
+      <c r="L9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" s="31">
         <f>IFERROR(G9+M9,"")</f>
         <v/>
@@ -20843,7 +20915,11 @@
         <f>IFERROR(-L9,"")</f>
         <v/>
       </c>
-      <c r="Q9" s="32" t="n"/>
+      <c r="Q9" s="32" t="inlineStr">
+        <is>
+          <t>停牌，本期暂停操作，目标市值照常增长</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="33" t="n"/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1310,8 +1310,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="33" t="n"/>
+      <c r="A10" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
       <c r="C10" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A10,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1332,7 +1338,9 @@
         <f>IFERROR(IF(M10="增量阶段",H10,SUMPRODUCT(MAX(C10,0),1)+SUMPRODUCT(MAX(D10,0),1)+SUMPRODUCT(MAX(E10,0),1)+SUMPRODUCT(MAX(F10,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H10" s="17" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="7">
         <f>IFERROR(MAX(-C10,0)+MAX(-D10,0)+MAX(-E10,0)+MAX(-F10,0),"")</f>
         <v/>
@@ -6347,19 +6355,31 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$5*(B10-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27" t="n">
+        <v>4.852</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>4.46819947052002</v>
+      </c>
       <c r="F10" s="28">
         <f>IFERROR((D10-E10)/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="27" t="n"/>
+      <c r="G10" s="27" t="n">
+        <v>1500</v>
+      </c>
       <c r="H10" s="7">
         <f>IFERROR(G10*D10,"")</f>
         <v/>
@@ -6376,8 +6396,12 @@
         <f>IFERROR(I10,"")</f>
         <v/>
       </c>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="27" t="n"/>
+      <c r="L10" s="17" t="n">
+        <v>1940.8</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>400</v>
+      </c>
       <c r="N10" s="31">
         <f>IFERROR(G10+M10,"")</f>
         <v/>
@@ -11204,19 +11228,31 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$6*(B10-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27" t="n">
+        <v>8.843999999999999</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>7.342891065597534</v>
+      </c>
       <c r="F10" s="28">
         <f>IFERROR((D10-E10)/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="27" t="n"/>
+      <c r="G10" s="27" t="n">
+        <v>900</v>
+      </c>
       <c r="H10" s="7">
         <f>IFERROR(G10*D10,"")</f>
         <v/>
@@ -11233,8 +11269,12 @@
         <f>IFERROR(I10,"")</f>
         <v/>
       </c>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="27" t="n"/>
+      <c r="L10" s="17" t="n">
+        <v>884.4</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>100</v>
+      </c>
       <c r="N10" s="31">
         <f>IFERROR(G10+M10,"")</f>
         <v/>
@@ -16061,19 +16101,31 @@
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$7*(B10-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27" t="n">
+        <v>1.382</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>1.553168001651764</v>
+      </c>
       <c r="F10" s="28">
         <f>IFERROR((D10-E10)/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="27" t="n"/>
+      <c r="G10" s="27" t="n">
+        <v>2200</v>
+      </c>
       <c r="H10" s="7">
         <f>IFERROR(G10*D10,"")</f>
         <v/>
@@ -16090,8 +16142,12 @@
         <f>IFERROR(I10,"")</f>
         <v/>
       </c>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="27" t="n"/>
+      <c r="L10" s="17" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>400</v>
+      </c>
       <c r="N10" s="31">
         <f>IFERROR(G10+M10,"")</f>
         <v/>
@@ -20922,19 +20978,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>6</v>
+      </c>
       <c r="C10" s="7">
         <f>IFERROR(参数配置!$C$8*(B10-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27" t="n">
+        <v>2.149</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>1.814727995872498</v>
+      </c>
       <c r="F10" s="28">
         <f>IFERROR((D10-E10)/E10,"")</f>
         <v/>
       </c>
-      <c r="G10" s="27" t="n"/>
+      <c r="G10" s="27" t="n">
+        <v>4400</v>
+      </c>
       <c r="H10" s="7">
         <f>IFERROR(G10*D10,"")</f>
         <v/>
@@ -20951,8 +21019,12 @@
         <f>IFERROR(I10,"")</f>
         <v/>
       </c>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="27" t="n"/>
+      <c r="L10" s="17" t="n">
+        <v>4727.8</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2200</v>
+      </c>
       <c r="N10" s="31">
         <f>IFERROR(G10+M10,"")</f>
         <v/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="中证500" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总看板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每期汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沪深300" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中证500" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="恒生指数" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="纳指100" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1363,8 +1363,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="33" t="n"/>
+      <c r="A11" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
       <c r="C11" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A11,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1385,7 +1391,9 @@
         <f>IFERROR(IF(M11="增量阶段",H11,SUMPRODUCT(MAX(C11,0),1)+SUMPRODUCT(MAX(D11,0),1)+SUMPRODUCT(MAX(E11,0),1)+SUMPRODUCT(MAX(F11,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H11" s="17" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I11" s="7">
         <f>IFERROR(MAX(-C11,0)+MAX(-D11,0)+MAX(-E11,0)+MAX(-F11,0),"")</f>
         <v/>
@@ -1408,8 +1416,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="33" t="n"/>
+      <c r="A12" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
       <c r="C12" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A12,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1430,7 +1444,9 @@
         <f>IFERROR(IF(M12="增量阶段",H12,SUMPRODUCT(MAX(C12,0),1)+SUMPRODUCT(MAX(D12,0),1)+SUMPRODUCT(MAX(E12,0),1)+SUMPRODUCT(MAX(F12,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H12" s="17" t="n"/>
+      <c r="H12" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I12" s="7">
         <f>IFERROR(MAX(-C12,0)+MAX(-D12,0)+MAX(-E12,0)+MAX(-F12,0),"")</f>
         <v/>
@@ -6417,19 +6433,31 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="15" t="n"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$5*(B11-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>4.643</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>4.598508</v>
+      </c>
       <c r="F11" s="28">
         <f>IFERROR((D11-E11)/E11,"")</f>
         <v/>
       </c>
-      <c r="G11" s="27" t="n"/>
+      <c r="G11" s="27" t="n">
+        <v>1900</v>
+      </c>
       <c r="H11" s="7">
         <f>IFERROR(G11*D11,"")</f>
         <v/>
@@ -6446,8 +6474,12 @@
         <f>IFERROR(I11,"")</f>
         <v/>
       </c>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="27" t="n"/>
+      <c r="L11" s="17" t="n">
+        <v>1857.2</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>400</v>
+      </c>
       <c r="N11" s="31">
         <f>IFERROR(G11+M11,"")</f>
         <v/>
@@ -6463,19 +6495,31 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n"/>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$5*(B12-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>4.691</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>4.6278</v>
+      </c>
       <c r="F12" s="28">
         <f>IFERROR((D12-E12)/E12,"")</f>
         <v/>
       </c>
-      <c r="G12" s="27" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>2300</v>
+      </c>
       <c r="H12" s="7">
         <f>IFERROR(G12*D12,"")</f>
         <v/>
@@ -6492,8 +6536,12 @@
         <f>IFERROR(I12,"")</f>
         <v/>
       </c>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="27" t="n"/>
+      <c r="L12" s="17" t="n">
+        <v>1407.3</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N12" s="31">
         <f>IFERROR(G12+M12,"")</f>
         <v/>
@@ -11290,19 +11338,31 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="15" t="n"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$6*(B11-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>7.728</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>7.549152</v>
+      </c>
       <c r="F11" s="28">
         <f>IFERROR((D11-E11)/E11,"")</f>
         <v/>
       </c>
-      <c r="G11" s="27" t="n"/>
+      <c r="G11" s="27" t="n">
+        <v>1000</v>
+      </c>
       <c r="H11" s="7">
         <f>IFERROR(G11*D11,"")</f>
         <v/>
@@ -11319,8 +11379,12 @@
         <f>IFERROR(I11,"")</f>
         <v/>
       </c>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="27" t="n"/>
+      <c r="L11" s="17" t="n">
+        <v>2318.4</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N11" s="31">
         <f>IFERROR(G11+M11,"")</f>
         <v/>
@@ -11336,19 +11400,31 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n"/>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$6*(B12-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>7.6165</v>
+      </c>
       <c r="F12" s="28">
         <f>IFERROR((D12-E12)/E12,"")</f>
         <v/>
       </c>
-      <c r="G12" s="27" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>1300</v>
+      </c>
       <c r="H12" s="7">
         <f>IFERROR(G12*D12,"")</f>
         <v/>
@@ -11365,8 +11441,12 @@
         <f>IFERROR(I12,"")</f>
         <v/>
       </c>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="27" t="n"/>
+      <c r="L12" s="17" t="n">
+        <v>1526</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N12" s="31">
         <f>IFERROR(G12+M12,"")</f>
         <v/>
@@ -16163,19 +16243,31 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="15" t="n"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$7*(B11-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>1.548248</v>
+      </c>
       <c r="F11" s="28">
         <f>IFERROR((D11-E11)/E11,"")</f>
         <v/>
       </c>
-      <c r="G11" s="27" t="n"/>
+      <c r="G11" s="27" t="n">
+        <v>2600</v>
+      </c>
       <c r="H11" s="7">
         <f>IFERROR(G11*D11,"")</f>
         <v/>
@@ -16192,8 +16284,12 @@
         <f>IFERROR(I11,"")</f>
         <v/>
       </c>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="27" t="n"/>
+      <c r="L11" s="17" t="n">
+        <v>438.6</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>300</v>
+      </c>
       <c r="N11" s="31">
         <f>IFERROR(G11+M11,"")</f>
         <v/>
@@ -16209,19 +16305,31 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n"/>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$7*(B12-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>1.5482</v>
+      </c>
       <c r="F12" s="28">
         <f>IFERROR((D12-E12)/E12,"")</f>
         <v/>
       </c>
-      <c r="G12" s="27" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>2900</v>
+      </c>
       <c r="H12" s="7">
         <f>IFERROR(G12*D12,"")</f>
         <v/>
@@ -16238,8 +16346,12 @@
         <f>IFERROR(I12,"")</f>
         <v/>
       </c>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="27" t="n"/>
+      <c r="L12" s="17" t="n">
+        <v>304.6</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N12" s="31">
         <f>IFERROR(G12+M12,"")</f>
         <v/>
@@ -21040,19 +21152,31 @@
       <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="15" t="n"/>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>7</v>
+      </c>
       <c r="C11" s="7">
         <f>IFERROR(参数配置!$C$8*(B11-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="D11" s="27" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>1.890264</v>
+      </c>
       <c r="F11" s="28">
         <f>IFERROR((D11-E11)/E11,"")</f>
         <v/>
       </c>
-      <c r="G11" s="27" t="n"/>
+      <c r="G11" s="27" t="n">
+        <v>6600</v>
+      </c>
       <c r="H11" s="7">
         <f>IFERROR(G11*D11,"")</f>
         <v/>
@@ -21069,8 +21193,12 @@
         <f>IFERROR(I11,"")</f>
         <v/>
       </c>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="27" t="n"/>
+      <c r="L11" s="17" t="n">
+        <v>2752.1</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1300</v>
+      </c>
       <c r="N11" s="31">
         <f>IFERROR(G11+M11,"")</f>
         <v/>
@@ -21086,19 +21214,31 @@
       <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n"/>
-      <c r="B12" s="15" t="n"/>
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>8</v>
+      </c>
       <c r="C12" s="7">
         <f>IFERROR(参数配置!$C$8*(B12-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>1.9067</v>
+      </c>
       <c r="F12" s="28">
         <f>IFERROR((D12-E12)/E12,"")</f>
         <v/>
       </c>
-      <c r="G12" s="27" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>7900</v>
+      </c>
       <c r="H12" s="7">
         <f>IFERROR(G12*D12,"")</f>
         <v/>
@@ -21115,8 +21255,12 @@
         <f>IFERROR(I12,"")</f>
         <v/>
       </c>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="27" t="n"/>
+      <c r="L12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" s="31">
         <f>IFERROR(G12+M12,"")</f>
         <v/>
@@ -21129,7 +21273,11 @@
         <f>IFERROR(-L12,"")</f>
         <v/>
       </c>
-      <c r="Q12" s="32" t="n"/>
+      <c r="Q12" s="32" t="inlineStr">
+        <is>
+          <t>停牌，本期暂停操作，目标市值照常增长</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="33" t="n"/>

--- a/strategies/constant_value/定投追踪记录.xlsx
+++ b/strategies/constant_value/定投追踪记录.xlsx
@@ -1469,8 +1469,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="33" t="n"/>
+      <c r="A13" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="C13" s="7">
         <f>IFERROR(SUMIF(沪深300!$B$5:$B$1000,A13,沪深300!$L$5:$L$1000),"")</f>
         <v/>
@@ -1491,7 +1497,9 @@
         <f>IFERROR(IF(M13="增量阶段",H13,SUMPRODUCT(MAX(C13,0),1)+SUMPRODUCT(MAX(D13,0),1)+SUMPRODUCT(MAX(E13,0),1)+SUMPRODUCT(MAX(F13,0),1)),"")</f>
         <v/>
       </c>
-      <c r="H13" s="17" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="I13" s="7">
         <f>IFERROR(MAX(-C13,0)+MAX(-D13,0)+MAX(-E13,0)+MAX(-F13,0),"")</f>
         <v/>
@@ -6557,19 +6565,31 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="15" t="n"/>
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>9</v>
+      </c>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$5*(B13-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>4.6531</v>
+      </c>
       <c r="F13" s="28">
         <f>IFERROR((D13-E13)/E13,"")</f>
         <v/>
       </c>
-      <c r="G13" s="27" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>2600</v>
+      </c>
       <c r="H13" s="7">
         <f>IFERROR(G13*D13,"")</f>
         <v/>
@@ -6586,8 +6606,12 @@
         <f>IFERROR(I13,"")</f>
         <v/>
       </c>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="27" t="n"/>
+      <c r="L13" s="17" t="n">
+        <v>944.8000000000001</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N13" s="31">
         <f>IFERROR(G13+M13,"")</f>
         <v/>
@@ -11462,19 +11486,31 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="15" t="n"/>
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>9</v>
+      </c>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$6*(B13-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>7.6852</v>
+      </c>
       <c r="F13" s="28">
         <f>IFERROR((D13-E13)/E13,"")</f>
         <v/>
       </c>
-      <c r="G13" s="27" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>1500</v>
+      </c>
       <c r="H13" s="7">
         <f>IFERROR(G13*D13,"")</f>
         <v/>
@@ -11491,8 +11527,12 @@
         <f>IFERROR(I13,"")</f>
         <v/>
       </c>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="27" t="n"/>
+      <c r="L13" s="17" t="n">
+        <v>1598</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>200</v>
+      </c>
       <c r="N13" s="31">
         <f>IFERROR(G13+M13,"")</f>
         <v/>
@@ -16367,19 +16407,31 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="15" t="n"/>
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>9</v>
+      </c>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$7*(B13-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>1.5466</v>
+      </c>
       <c r="F13" s="28">
         <f>IFERROR((D13-E13)/E13,"")</f>
         <v/>
       </c>
-      <c r="G13" s="27" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>3100</v>
+      </c>
       <c r="H13" s="7">
         <f>IFERROR(G13*D13,"")</f>
         <v/>
@@ -16396,8 +16448,12 @@
         <f>IFERROR(I13,"")</f>
         <v/>
       </c>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="27" t="n"/>
+      <c r="L13" s="17" t="n">
+        <v>739.5</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>500</v>
+      </c>
       <c r="N13" s="31">
         <f>IFERROR(G13+M13,"")</f>
         <v/>
@@ -21280,19 +21336,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="15" t="n"/>
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>9</v>
+      </c>
       <c r="C13" s="7">
         <f>IFERROR(参数配置!$C$8*(B13-$S$3),"")</f>
         <v/>
       </c>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>2.264</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>1.9307</v>
+      </c>
       <c r="F13" s="28">
         <f>IFERROR((D13-E13)/E13,"")</f>
         <v/>
       </c>
-      <c r="G13" s="27" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>7900</v>
+      </c>
       <c r="H13" s="7">
         <f>IFERROR(G13*D13,"")</f>
         <v/>
@@ -21309,8 +21377,12 @@
         <f>IFERROR(I13,"")</f>
         <v/>
       </c>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="27" t="n"/>
+      <c r="L13" s="17" t="n">
+        <v>3622.4</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1600</v>
+      </c>
       <c r="N13" s="31">
         <f>IFERROR(G13+M13,"")</f>
         <v/>
